--- a/資料/TB杭とSB杭の違い_SS7.xlsx
+++ b/資料/TB杭とSB杭の違い_SS7.xlsx
@@ -14,10 +14,13 @@
     <sheet name="鋼管部_試算" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="設計チェック" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="記号の説明" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="PDF対照表" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">PDF対照表!$5:$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">PDF対照表!$B$5:$G$60</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">比較一覧!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">比較一覧!$A$4:$H$50</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">比較一覧!$A$4:$I$50</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">記号の説明!$5:$5</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">設計チェック!$5:$5</definedName>
   </definedNames>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="732">
   <si>
     <t xml:space="preserve">TB杭とSB杭の違い ― 要点まとめ</t>
   </si>
@@ -72,6 +75,9 @@
     <t xml:space="preserve">設計上のポイント</t>
   </si>
   <si>
+    <t xml:space="preserve">根拠（比較一覧No.／PDF赤枠）</t>
+  </si>
+  <si>
     <t xml:space="preserve">根拠となる指針</t>
   </si>
   <si>
@@ -82,6 +88,10 @@
   </si>
   <si>
     <t xml:space="preserve">SS7ではどちらも「場所打ち鋼管コンクリート杭」と呼ぶため、TB・SBのどちらで計算しているか入力を必ず確認する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比較一覧No.2
+赤枠：T2・S3</t>
   </si>
   <si>
     <t xml:space="preserve">適用できるFc</t>
@@ -98,6 +108,10 @@
     <t xml:space="preserve">TBは範囲外でも計算が止まらない。Fcが協会の範囲内か、設計者が自分で確認する。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.7,8
+赤枠：T2・S3</t>
+  </si>
+  <si>
     <t xml:space="preserve">コンクリートの許容圧縮応力度（長期）</t>
   </si>
   <si>
@@ -112,6 +126,10 @@
     <t xml:space="preserve">泥水中ではSBの方が約11％小さい（4/4.5＝0.89）。短期はどちらも長期の2倍。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.9
+赤枠：T2・S2</t>
+  </si>
+  <si>
     <t xml:space="preserve">軸力の負担</t>
   </si>
   <si>
@@ -125,6 +143,10 @@
     <t xml:space="preserve">圧縮・引抜きの軸力が大きい杭頭では、SBはRC部だけで軸力が収まるかの確認が必要。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.18,19
+赤枠：T6・T7・S8</t>
+  </si>
+  <si>
     <t xml:space="preserve">引張側の許容軸力 rNt</t>
   </si>
   <si>
@@ -135,6 +157,10 @@
   </si>
   <si>
     <t xml:space="preserve">SBは引張側を0.75倍に低減する。引抜きを受ける杭で差が出やすい。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比較一覧No.22
+赤枠：T10・S11</t>
   </si>
   <si>
     <t xml:space="preserve">RC部の短期許容せん断力</t>
@@ -150,6 +176,10 @@
     <t xml:space="preserve">SBは帯筋量が短期許容せん断力に直接効く。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.27
+赤枠：T14・S15</t>
+  </si>
+  <si>
     <t xml:space="preserve">杭頭定着筋</t>
   </si>
   <si>
@@ -162,6 +192,10 @@
     <t xml:space="preserve">SBは設計応力が小さくても、鋼管の耐力で定着筋の量が決まる。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.30,33
+赤枠：T15・T17・S16</t>
+  </si>
+  <si>
     <t xml:space="preserve">杭頭の水平力（支圧）の検討</t>
   </si>
   <si>
@@ -174,6 +208,10 @@
     <t xml:space="preserve">TBは基礎スラブへの埋込長 l が、支圧と終局せん断耐力の両方に効く。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.34
+赤枠：T18</t>
+  </si>
+  <si>
     <t xml:space="preserve">曲げの復元力特性</t>
   </si>
   <si>
@@ -184,6 +222,10 @@
   </si>
   <si>
     <t xml:space="preserve">SBの鋼管の終局曲げ Mst は全塑性モーメントで、鋼管は軸力を負担しない前提。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比較一覧No.35,36,37,38,39,40
+赤枠：T19・T20・T21・T22・T23・T24・S18・S19・S20・S21・S22</t>
   </si>
   <si>
     <t xml:space="preserve">終局せん断耐力</t>
@@ -200,6 +242,10 @@
     <t xml:space="preserve">鋼管分の値は同じ（κ＝2なのでsA/2と同じ）。TBだけが杭頭接合部で頭打ちになる。</t>
   </si>
   <si>
+    <t xml:space="preserve">比較一覧No.44,45
+赤枠：T25・T27・T28・S23・S24</t>
+  </si>
+  <si>
     <t xml:space="preserve">■ 力の分担イメージ（杭頭の鋼管がある区間）</t>
   </si>
   <si>
@@ -343,13 +389,20 @@
     <t xml:space="preserve">比較一覧で使っている記号の意味</t>
   </si>
   <si>
+    <t xml:space="preserve">PDF対照表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF（赤枠入り）の枠IDごとに、PDFの頁・マニュアルの頁・内容・関連する比較一覧No.を一覧にしたもの</t>
+  </si>
+  <si>
     <t xml:space="preserve">※「記載なし（本資料の範囲）」は、ご提供の抜粋にその記述がないという意味です。プログラムや協会指針に規定がないことを意味しません。実設計では各協会の設計・施工指針とSS7の最新マニュアルを必ず確認してください。</t>
   </si>
   <si>
     <t xml:space="preserve">TB杭とSB杭の比較一覧（SS7 マニュアルより）</t>
   </si>
   <si>
-    <t xml:space="preserve">差異の見方：　◆相違＝考え方や式が違う　／　△一部相違＝一部だけ違う・書き方が違う　／　＝共通＝同じ扱い　　（表の見出しのフィルターで「差異」を絞り込めます）</t>
+    <t xml:space="preserve">差異の見方：　◆相違＝考え方や式が違う　／　△一部相違＝一部だけ違う・書き方が違う　／　＝共通＝同じ扱い　　（表の見出しのフィルターで「差異」を絞り込めます）
+「PDF該当箇所」の赤枠IDは、同じフォルダの「SS7マニュアル_TB杭SB杭_赤枠.pdf」に赤枠と同じIDで記入しています（T＝TB杭、S＝SB杭、C＝共通）。</t>
   </si>
   <si>
     <t xml:space="preserve">分類</t>
@@ -370,6 +423,10 @@
     <t xml:space="preserve">出典（式・頁）</t>
   </si>
   <si>
+    <t xml:space="preserve">PDF該当箇所
+赤枠ID（PDF頁／マニュアル頁）</t>
+  </si>
+  <si>
     <t xml:space="preserve">基本・適用</t>
   </si>
   <si>
@@ -391,6 +448,10 @@
     <t xml:space="preserve">7.7.5／7.7.6 見出し</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T1（PDF p.1／7-63）
+SB：S1（PDF p.4／7-66）</t>
+  </si>
+  <si>
     <t xml:space="preserve">根拠となる協会・指針</t>
   </si>
   <si>
@@ -401,6 +462,10 @@
   </si>
   <si>
     <t xml:space="preserve">p.7-63 注意／p.7-66 注意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T2（PDF p.1／7-63）
+SB：S3（PDF p.4／7-66）</t>
   </si>
   <si>
     <t xml:space="preserve">杭頭部の断面構成（SS7での部位名）</t>
@@ -420,6 +485,10 @@
     <t xml:space="preserve">7.7.5(1)2)／7.7.6(2)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T4（PDF p.1／7-63）、T6（PDF p.1／7-63）
+SB：S7（PDF p.5／7-67）</t>
+  </si>
+  <si>
     <t xml:space="preserve">断面算定の対象</t>
   </si>
   <si>
@@ -468,6 +537,9 @@
     <t xml:space="preserve">p.7-66 注意</t>
   </si>
   <si>
+    <t xml:space="preserve">SB：S3（PDF p.4／7-66）</t>
+  </si>
+  <si>
     <t xml:space="preserve">材料の許容応力度</t>
   </si>
   <si>
@@ -488,6 +560,10 @@
     <t xml:space="preserve">表7.16／表7.18</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T2（PDF p.1／7-63）
+SB：S2（PDF p.4／7-66）</t>
+  </si>
+  <si>
     <t xml:space="preserve">コンクリート 長期許容せん断応力度</t>
   </si>
   <si>
@@ -533,6 +609,10 @@
   </si>
   <si>
     <t xml:space="preserve">7.7.4 と同じ表7.15による。許容応力度を直接入力した場合は入力値×ξ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T3（PDF p.1／7-63）
+SB：S4（PDF p.4／7-66）</t>
   </si>
   <si>
     <t xml:space="preserve">鋼管の許容応力度</t>
@@ -553,6 +633,10 @@
     <t xml:space="preserve">表7.17／表7.19</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T4（PDF p.1／7-63）
+SB：S5（PDF p.4／7-66）</t>
+  </si>
+  <si>
     <t xml:space="preserve">鉄筋の許容応力度</t>
   </si>
   <si>
@@ -562,6 +646,10 @@
     <t xml:space="preserve">7.7.5(1)3)／7.7.6(1)3)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T5（PDF p.1／7-63）
+SB：S6（PDF p.4／7-66）</t>
+  </si>
+  <si>
     <t xml:space="preserve">ヤング係数比</t>
   </si>
   <si>
@@ -589,6 +677,10 @@
     <t xml:space="preserve">7.7.5(2)1)／7.7.6(2)1)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T6（PDF p.1／7-63）
+SB：S7（PDF p.5／7-67）</t>
+  </si>
+  <si>
     <t xml:space="preserve">鋼管内（鉄筋）コンクリート部と鋼管の両方。N が rNc を超える分、rNt を下回る分は鋼管が負担</t>
   </si>
   <si>
@@ -599,6 +691,10 @@
   </si>
   <si>
     <t xml:space="preserve">式(7.121)〜(7.126)／式(7.135)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T6（PDF p.1／7-63）、T7（PDF p.2／7-64）
+SB：S8（PDF p.5／7-67）</t>
   </si>
   <si>
     <t xml:space="preserve">検定式</t>
@@ -636,6 +732,10 @@
     <t xml:space="preserve">式(7.127)〜(7.129)／式(7.137)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T8（PDF p.2／7-64）
+SB：S9（PDF p.5／7-67）</t>
+  </si>
+  <si>
     <t xml:space="preserve">RC部の圧縮側許容軸力</t>
   </si>
   <si>
@@ -653,6 +753,10 @@
     <t xml:space="preserve">式(7.130)(7.131)／式(7.138)(7.139)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T9（PDF p.2／7-64）
+SB：S10（PDF p.5／7-67）</t>
+  </si>
+  <si>
     <t xml:space="preserve">RC部の引張側許容軸力 rNt</t>
   </si>
   <si>
@@ -662,6 +766,10 @@
     <t xml:space="preserve">式(7.132)／式(7.140)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T10（PDF p.2／7-64）
+SB：S11（PDF p.5／7-67）</t>
+  </si>
+  <si>
     <t xml:space="preserve">rN・rM（rNA・rMA）</t>
   </si>
   <si>
@@ -671,10 +779,18 @@
     <t xml:space="preserve">7.7.5(2)1)(vii)／7.7.6(2)1)(v)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T11（PDF p.2／7-64）
+SB：S12（PDF p.5／7-67）</t>
+  </si>
+  <si>
     <t xml:space="preserve">下部の鉄筋コンクリート部</t>
   </si>
   <si>
     <t xml:space="preserve">7.7.5(2)2)／7.7.6(2)2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T12（PDF p.3／7-65）
+SB：S13（PDF p.5／7-67）</t>
   </si>
   <si>
     <t xml:space="preserve">許容せん断力</t>
@@ -698,6 +814,10 @@
     <t xml:space="preserve">式(7.133)／式(7.141)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T13（PDF p.3／7-65）
+SB：S14（PDF p.6／7-68）</t>
+  </si>
+  <si>
     <t xml:space="preserve">鉄筋コンクリート部（長期）</t>
   </si>
   <si>
@@ -705,6 +825,10 @@
   </si>
   <si>
     <t xml:space="preserve">7.7.5(3)2)／7.7.6(3)2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T14（PDF p.3／7-65）
+SB：S15（PDF p.6／7-68）</t>
   </si>
   <si>
     <t xml:space="preserve">鉄筋コンクリート部（短期）</t>
@@ -741,6 +865,10 @@
     <t xml:space="preserve">図7.48／図7.49</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T16（PDF p.3／7-65）
+SB：S17（PDF p.6／7-68）</t>
+  </si>
+  <si>
     <t xml:space="preserve">杭頭定着筋の算定条件</t>
   </si>
   <si>
@@ -757,6 +885,10 @@
     <t xml:space="preserve">7.7.5(4)1)／7.7.6(4)1)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T15（PDF p.3／7-65）
+SB：S16（PDF p.6／7-68）</t>
+  </si>
+  <si>
     <t xml:space="preserve">杭頭主筋がある場合</t>
   </si>
   <si>
@@ -769,6 +901,10 @@
     <t xml:space="preserve">7.7.5(4)1)／図7.49</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T15（PDF p.3／7-65）
+SB：S17（PDF p.6／7-68）</t>
+  </si>
+  <si>
     <t xml:space="preserve">定着筋の選定計算</t>
   </si>
   <si>
@@ -788,6 +924,9 @@
   </si>
   <si>
     <t xml:space="preserve">p.7-65 注意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T17（PDF p.3／7-65）</t>
   </si>
   <si>
     <t xml:space="preserve">水平力に対する検討（支圧）</t>
@@ -804,6 +943,9 @@
     <t xml:space="preserve">式(7.134)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T18（PDF p.4／7-66）</t>
+  </si>
+  <si>
     <t xml:space="preserve">算定方法</t>
   </si>
   <si>
@@ -817,6 +959,10 @@
   </si>
   <si>
     <t xml:space="preserve">10.15.1(1)／10.15.1(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T19（PDF p.7／10-75）
+SB：S18（PDF p.10／10-78）</t>
   </si>
   <si>
     <t xml:space="preserve">骨格曲線の特性点</t>
@@ -835,6 +981,10 @@
     <t xml:space="preserve">10.15.1(1)2)／10.15.1(2)1)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T20（PDF p.7／10-75）
+SB：S19（PDF p.10／10-78）</t>
+  </si>
+  <si>
     <t xml:space="preserve">トリリニアへのモデル化</t>
   </si>
   <si>
@@ -847,6 +997,10 @@
     <t xml:space="preserve">図10.46／10.15.1(2)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T21（PDF p.8／10-76）、T22（PDF p.8／10-76）
+SB：S18（PDF p.10／10-78）</t>
+  </si>
+  <si>
     <t xml:space="preserve">降伏時の剛性低下率</t>
   </si>
   <si>
@@ -857,6 +1011,10 @@
   </si>
   <si>
     <t xml:space="preserve">式(10.234)／10.15.1(2)2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T23（PDF p.8／10-76）
+SB：S20（PDF p.10／10-78）</t>
   </si>
   <si>
     <t xml:space="preserve">材料の応力度−ひずみ関係</t>
@@ -870,6 +1028,9 @@
   </si>
   <si>
     <t xml:space="preserve">図10.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T24（PDF p.9／10-77）</t>
   </si>
   <si>
     <t xml:space="preserve">終局曲げモーメント</t>
@@ -890,6 +1051,9 @@
     <t xml:space="preserve">式(10.240)〜(10.246)</t>
   </si>
   <si>
+    <t xml:space="preserve">SB：S21（PDF p.11／10-79）、S22（PDF p.12／10-80）</t>
+  </si>
+  <si>
     <t xml:space="preserve">せん断の復元力特性</t>
   </si>
   <si>
@@ -902,6 +1066,9 @@
     <t xml:space="preserve">10.15.2 冒頭</t>
   </si>
   <si>
+    <t xml:space="preserve">共通：C1（PDF p.12／10-80）</t>
+  </si>
+  <si>
     <t xml:space="preserve">せん断ひび割れ耐力</t>
   </si>
   <si>
@@ -909,6 +1076,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.15.2(1)2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">共通：C2（PDF p.12／10-80）</t>
   </si>
   <si>
     <t xml:space="preserve">ひび割れ後の剛性低下率</t>
@@ -919,6 +1089,9 @@
   </si>
   <si>
     <t xml:space="preserve">式(10.248)／10.15.2(2)2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">共通：C3（PDF p.13／10-81）</t>
   </si>
   <si>
     <t xml:space="preserve">終局せん断耐力（鋼管部）</t>
@@ -940,6 +1113,10 @@
     <t xml:space="preserve">式(10.254)／式(10.255)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T27（PDF p.15／10-83）
+SB：S23（PDF p.15／10-83）</t>
+  </si>
+  <si>
     <t xml:space="preserve">終局せん断耐力（RC部）</t>
   </si>
   <si>
@@ -958,10 +1135,18 @@
     <t xml:space="preserve">式(10.249)(10.250)／式(10.256)</t>
   </si>
   <si>
+    <t xml:space="preserve">TB：T25（PDF p.13／10-81）、T28（PDF p.15／10-83）
+SB：S24（PDF p.15／10-83）</t>
+  </si>
+  <si>
     <t xml:space="preserve">高強度せん断補強筋を用いた場合</t>
   </si>
   <si>
     <t xml:space="preserve">10.15.2(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：T26（PDF p.14／10-82）、T28（PDF p.15／10-83）
+SB：S24（PDF p.15／10-83）</t>
   </si>
   <si>
     <t xml:space="preserve">差異の集計</t>
@@ -1655,6 +1840,504 @@
   </si>
   <si>
     <t xml:space="preserve">TBの終局せん断耐力：鋼管分（sA/2・Fs/√3）・杭頭接合部分（Fc・D・ℓ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF対照表（赤枠ID と マニュアルの記載箇所）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF「SS7マニュアル_TB杭SB杭_赤枠.pdf」の各頁に、下表の枠IDで赤枠を付けています。枠IDは赤枠の右横に表示しています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">枠ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF頁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マニュアル頁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記載内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">関連する比較一覧No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7.5 見出し・冒頭（断面算定の対象、検討ケース、設計用応力）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,4,5,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表7.16 コンクリートの許容圧縮応力度、KCTBの注意書き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,7,9,10,11,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">品質管理に関わる係数ξ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表7.17 鋼材の許容応力度（鋼管は内側リブ付き）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄筋の許容応力度、ヤング係数比</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)1) 鋼管コンクリート部：累加強度、(i) N＞rNc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,17,18,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(ii) rNc≧N≧rNt、(iii) rNt＞N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(iv) sM0・sN・sN'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(v) rNc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(vi) rNt＝−rf・rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(vii) rN・rM は 7.7.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) 鉄筋コンクリート部は 7.7.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)1) 鋼管部の許容せん断力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)2) 鉄筋コンクリート部は 7.7.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26,27,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)1) 杭頭定着筋の検討</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,31,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">図7.48 杭頭定着筋計算用杭径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意：定着筋は8本以上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) 水平力に対する検討（支圧）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7.6 見出し・冒頭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表7.18 コンクリートの許容応力度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,10,11,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意：SB耐震杭協会、Fc＝18〜36、普通コンクリートのみ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,7,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表7.19 鋼材の許容応力度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)1) 鋼管巻き鉄筋コンクリート部：単純累加強度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(i) ND＝rNA、MD≦sM0＋rMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(ii) sM0＝sZ・sft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(iii) rN0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(iv) rNt＝−0.75・rf・rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(v) rNA・rMA は 7.7.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)1) 鋼管巻き鉄筋コンクリート部の許容せん断力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)2) 鉄筋コンクリート部（長期・短期・高強度）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">図7.49 杭頭定着筋計算用杭径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15.1(1) 既製杭・場所打ち・TB杭：断面解析</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) 骨格曲線（9分割、Mu・My・Mc）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">図10.46 第2折線が降伏点を通過するモデル化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コンクリートを含む杭は「1)の方法」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">αy'＝αy/(3−2αy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3) 材料の応力度−ひずみ関係（TB杭）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15.1(2) SB杭：トリリニア自動計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) 曲げひび割れモーメント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) 曲げ降伏時の割線剛性低下率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3) 終局曲げモーメント Mu＝Mrc＋Mst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mst（全塑性）、鉄筋コンクリート部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15.2 せん断の復元力特性（冒頭）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)2) 場所打ち鋼管コンクリート：ひび割れ耐力は場所打ち杭と同様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)2) 場所打ち鋼管コンクリート杭：剛性低下率は場所打ち杭と同様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)1) 場所打ちコンクリート杭の終局せん断（荒川式）※TBのRC部が準用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高強度せん断補強筋を用いた場合 ※TBのRC部が準用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) TB杭 鋼管コンクリート部：Qu＝min(Qu1, Qu2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB杭 鉄筋コンクリート部は場所打ち杭と同様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45,46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3) SB杭 鋼管巻き鉄筋コンクリート部：Qu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB杭 鉄筋コンクリート部：Qu（式10.256）</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +2352,7 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1799,6 +2482,20 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1810,6 +2507,14 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
       <name val="Meiryo UI"/>
       <family val="2"/>
       <charset val="128"/>
@@ -1952,8 +2657,16 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1994,6 +2707,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF404040"/>
         <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FF9C0006"/>
       </patternFill>
     </fill>
     <fill>
@@ -2070,7 +2789,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2123,6 +2842,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2143,6 +2866,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2155,7 +2882,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2191,166 +2918,182 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="29" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2359,7 +3102,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2379,39 +3122,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="31" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="34" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2419,11 +3162,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2674,6 +3421,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -2855,13 +3606,14 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F49"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2882,6 +3634,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
@@ -2893,6 +3646,7 @@
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
@@ -2904,6 +3658,7 @@
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
@@ -2913,6 +3668,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
@@ -2930,451 +3686,514 @@
       <c r="F10" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="G10" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="D11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="E11" s="17" t="s">
         <v>16</v>
       </c>
+      <c r="F11" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="19" t="s">
+      <c r="C12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="D12" s="20" t="s">
         <v>20</v>
       </c>
+      <c r="E12" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="20" t="s">
+      <c r="C13" s="15" t="s">
         <v>24</v>
       </c>
+      <c r="D13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>28</v>
+      <c r="C14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>32</v>
+      <c r="C15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>36</v>
+      <c r="C16" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>40</v>
+      <c r="C17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="n">
+      <c r="C18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>48</v>
+      <c r="C19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>52</v>
+      <c r="C20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="9"/>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13"/>
-      <c r="C24" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>61</v>
+      <c r="B24" s="14"/>
+      <c r="C24" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13"/>
-      <c r="C25" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>65</v>
+      <c r="B25" s="14"/>
+      <c r="C25" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13"/>
-      <c r="C26" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>68</v>
+      <c r="B26" s="14"/>
+      <c r="C26" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13"/>
-      <c r="C27" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>72</v>
+      <c r="B27" s="14"/>
+      <c r="C27" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13"/>
-      <c r="C28" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>76</v>
+      <c r="B28" s="14"/>
+      <c r="C28" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C32" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
+      <c r="C32" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C33" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
+      <c r="C33" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C34" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
+      <c r="C34" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C35" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C36" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
+      <c r="C36" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C37" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
+      <c r="C37" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C38" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
+      <c r="C38" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C39" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
+      <c r="C39" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C40" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
+      <c r="C40" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C43" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
+      <c r="C43" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C44" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
+      <c r="C44" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C45" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
+      <c r="C45" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C46" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
+      <c r="C46" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C47" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-    </row>
-    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
+      <c r="C47" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+    </row>
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C48" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+    </row>
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D6:G6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="B50:G50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C43" r:id="rId1" location="'比較一覧'!A1" display="比較一覧"/>
@@ -3382,6 +4201,7 @@
     <hyperlink ref="C45" r:id="rId3" location="'鋼管部_試算'!A1" display="鋼管部_試算"/>
     <hyperlink ref="C46" r:id="rId4" location="'設計チェック'!A1" display="設計チェック"/>
     <hyperlink ref="C47" r:id="rId5" location="'記号の説明'!A1" display="記号の説明"/>
+    <hyperlink ref="C48" r:id="rId6" location="'PDF対照表'!A1" display="PDF対照表"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3399,7 +4219,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3409,11 +4229,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3421,1239 +4242,1390 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>107</v>
+        <v>120</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>114</v>
+      <c r="B5" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="B6" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="B18" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="35" t="s">
+      <c r="B19" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="39" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="35" t="s">
+      <c r="G19" s="18"/>
+      <c r="H19" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="39" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="35" t="s">
+      <c r="G20" s="18"/>
+      <c r="H20" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" s="39" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="G25" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="G26" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="18"/>
+      <c r="H27" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="18"/>
+      <c r="H28" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G30" s="18"/>
+      <c r="H30" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="I32" s="41" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="18"/>
+      <c r="H33" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35" s="18"/>
+      <c r="H35" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="I36" s="41" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" s="18"/>
+      <c r="H37" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="I37" s="41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="H38" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="18"/>
+      <c r="H40" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" s="18"/>
+      <c r="H41" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G42" s="18"/>
+      <c r="H42" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="I42" s="41" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G43" s="18"/>
+      <c r="H43" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="H44" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="I44" s="41" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="F45" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" s="18"/>
+      <c r="H45" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="I45" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="18"/>
+      <c r="H46" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="16" t="s">
+      <c r="B47" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="F47" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" s="18"/>
+      <c r="H47" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="F48" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="H48" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="I48" s="41" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F49" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="H49" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="D50" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="F14" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="35" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="H18" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="35" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="35" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" s="33" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="33" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="H24" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="H25" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="H26" s="33" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="35" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="17"/>
-      <c r="H28" s="35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="35" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="H31" s="33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32" s="17"/>
-      <c r="H32" s="35" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="F33" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" s="17"/>
-      <c r="H33" s="33" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="F34" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="H34" s="35" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G35" s="17"/>
-      <c r="H35" s="35" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="H36" s="35" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G37" s="17"/>
-      <c r="H37" s="35" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="H38" s="33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="F39" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G40" s="17"/>
-      <c r="H40" s="35" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="17"/>
-      <c r="H41" s="33" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="33" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="17"/>
-      <c r="H43" s="33" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="H44" s="33" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="F45" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G45" s="17"/>
-      <c r="H45" s="35" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="F46" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="35" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="F47" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G47" s="17"/>
-      <c r="H47" s="33" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="H48" s="33" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G49" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="H49" s="33" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="F50" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="G50" s="17"/>
-      <c r="H50" s="35" t="s">
-        <v>290</v>
+      <c r="E50" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" s="18"/>
+      <c r="H50" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="30" t="s">
-        <v>291</v>
+      <c r="A52" s="32" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="39" t="str">
+      <c r="C53" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="D53" s="45" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C53)&amp;" 項目"</f>
         <v>20 項目</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="D54" s="39" t="str">
+      <c r="C54" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="45" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C54)&amp;" 項目"</f>
         <v>7 項目</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="39" t="str">
+      <c r="C55" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="45" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C55)&amp;" 項目"</f>
         <v>19 項目</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
+      <c r="A57" s="35" t="s">
+        <v>340</v>
+      </c>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H50"/>
-  <mergeCells count="1">
-    <mergeCell ref="A57:H57"/>
+  <autoFilter ref="A4:I50"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A57:I57"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4682,23 +5654,23 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="42" t="s">
-        <v>293</v>
+      <c r="B2" s="48" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="43" t="s">
-        <v>295</v>
+      <c r="B4" s="49" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -4709,36 +5681,36 @@
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" s="45" t="n">
+      <c r="B7" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="D7" s="46" t="s">
-        <v>298</v>
+      <c r="D7" s="52" t="s">
+        <v>346</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="C8" s="45" t="n">
+      <c r="B8" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" s="51" t="n">
         <v>235</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>298</v>
+      <c r="D8" s="52" t="s">
+        <v>346</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>301</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4756,157 +5728,157 @@
         <v>10</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="47" t="n">
+      <c r="B12" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="53" t="n">
         <f aca="false">$C$7/4</f>
         <v>6</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="54" t="n">
         <f aca="false">$C$7/4</f>
         <v>6</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="54" t="n">
         <f aca="false">$C$7/4.5</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F12" s="49" t="s">
-        <v>307</v>
-      </c>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
+      <c r="F12" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="C13" s="47" t="n">
+      <c r="B13" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="C13" s="53" t="n">
         <f aca="false">2*C12</f>
         <v>12</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="54" t="n">
         <f aca="false">2*D12</f>
         <v>12</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="54" t="n">
         <f aca="false">2*E12</f>
         <v>10.6666666666667</v>
       </c>
-      <c r="F13" s="50" t="s">
-        <v>309</v>
-      </c>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
+      <c r="F13" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="D14" s="48" t="n">
+      <c r="B14" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="54" t="n">
         <f aca="false">MIN($C$7/40,3/4*(0.49+$C$7/100))</f>
         <v>0.5475</v>
       </c>
-      <c r="E14" s="48" t="n">
+      <c r="E14" s="54" t="n">
         <f aca="false">MIN($C$7/45,3/4*(0.49+$C$7/100))</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="F14" s="49" t="s">
-        <v>312</v>
-      </c>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
+      <c r="F14" s="55" t="s">
+        <v>360</v>
+      </c>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="D15" s="48" t="n">
+      <c r="B15" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>359</v>
+      </c>
+      <c r="D15" s="54" t="n">
         <f aca="false">1.5*D14</f>
         <v>0.82125</v>
       </c>
-      <c r="E15" s="48" t="n">
+      <c r="E15" s="54" t="n">
         <f aca="false">1.5*E14</f>
         <v>0.8</v>
       </c>
-      <c r="F15" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
+      <c r="F15" s="55" t="s">
+        <v>362</v>
+      </c>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="52" t="s">
-        <v>315</v>
-      </c>
-      <c r="C16" s="53" t="n">
+      <c r="B16" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="C16" s="59" t="n">
         <f aca="false">C12/C12</f>
         <v>1</v>
       </c>
-      <c r="D16" s="54" t="n">
+      <c r="D16" s="60" t="n">
         <f aca="false">D12/C12</f>
         <v>1</v>
       </c>
-      <c r="E16" s="54" t="n">
+      <c r="E16" s="60" t="n">
         <f aca="false">E12/C12</f>
         <v>0.888888888888889</v>
       </c>
-      <c r="F16" s="49" t="s">
-        <v>316</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
+      <c r="F16" s="55" t="s">
+        <v>364</v>
+      </c>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="C17" s="55" t="str">
+      <c r="B17" s="58" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="61" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=45),"範囲内（18〜45）","範囲外：SS7は計算を続けるので要確認")</f>
         <v>範囲内（18〜45）</v>
       </c>
-      <c r="D17" s="56" t="str">
+      <c r="D17" s="62" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=36),"範囲内（18〜36）","範囲外：SS7がメッセージを出力")</f>
         <v>範囲内（18〜36）</v>
       </c>
-      <c r="E17" s="56" t="str">
+      <c r="E17" s="62" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=36),"範囲内（18〜36）","範囲外：SS7がメッセージを出力")</f>
         <v>範囲内（18〜36）</v>
       </c>
-      <c r="F17" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
+      <c r="F17" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -4921,13 +5893,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -4935,48 +5907,48 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="C21" s="57" t="n">
+      <c r="B21" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C21" s="63" t="n">
         <f aca="false">$C$8/1.5</f>
         <v>156.666666666667</v>
       </c>
-      <c r="D21" s="57" t="n">
+      <c r="D21" s="63" t="n">
         <f aca="false">1.5*C21</f>
         <v>235</v>
       </c>
-      <c r="E21" s="58" t="s">
-        <v>322</v>
-      </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
+      <c r="E21" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" s="57" t="n">
+      <c r="B22" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="C22" s="63" t="n">
         <f aca="false">$C$8/(1.5*SQRT(3))</f>
         <v>90.4515421730414</v>
       </c>
-      <c r="D22" s="57" t="n">
+      <c r="D22" s="63" t="n">
         <f aca="false">1.5*C22</f>
         <v>135.677313259562</v>
       </c>
-      <c r="E22" s="58" t="s">
-        <v>324</v>
-      </c>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
+      <c r="E22" s="64" t="s">
+        <v>372</v>
+      </c>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="59" t="s">
-        <v>325</v>
+      <c r="B24" s="65" t="s">
+        <v>373</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -4988,330 +5960,330 @@
     </row>
     <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="60" t="n">
+      <c r="B26" s="66" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="61" t="n">
+      <c r="C26" s="67" t="n">
         <f aca="false">B26/4</f>
         <v>4.5</v>
       </c>
-      <c r="D26" s="62" t="n">
+      <c r="D26" s="68" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",B26/4)</f>
         <v>4.5</v>
       </c>
-      <c r="E26" s="62" t="n">
+      <c r="E26" s="68" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",B26/4.5)</f>
         <v>4</v>
       </c>
-      <c r="F26" s="63" t="n">
+      <c r="F26" s="69" t="n">
         <f aca="false">IF(B26&gt;36,"—",C26-E26)</f>
         <v>0.5</v>
       </c>
-      <c r="G26" s="62" t="n">
+      <c r="G26" s="68" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",MIN(B26/40,3/4*(0.49+B26/100)))</f>
         <v>0.45</v>
       </c>
-      <c r="H26" s="62" t="n">
+      <c r="H26" s="68" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",MIN(B26/45,3/4*(0.49+B26/100)))</f>
         <v>0.4</v>
       </c>
-      <c r="I26" s="64" t="str">
+      <c r="I26" s="70" t="str">
         <f aca="false">IF(B26&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B26/40&lt;=3/4*(0.49+B26/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B26/45&lt;=3/4*(0.49+B26/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：Fc/40　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="60" t="n">
+      <c r="B27" s="66" t="n">
         <v>21</v>
       </c>
-      <c r="C27" s="61" t="n">
+      <c r="C27" s="67" t="n">
         <f aca="false">B27/4</f>
         <v>5.25</v>
       </c>
-      <c r="D27" s="62" t="n">
+      <c r="D27" s="68" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",B27/4)</f>
         <v>5.25</v>
       </c>
-      <c r="E27" s="62" t="n">
+      <c r="E27" s="68" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",B27/4.5)</f>
         <v>4.66666666666667</v>
       </c>
-      <c r="F27" s="63" t="n">
+      <c r="F27" s="69" t="n">
         <f aca="false">IF(B27&gt;36,"—",C27-E27)</f>
         <v>0.583333333333333</v>
       </c>
-      <c r="G27" s="62" t="n">
+      <c r="G27" s="68" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",MIN(B27/40,3/4*(0.49+B27/100)))</f>
         <v>0.525</v>
       </c>
-      <c r="H27" s="62" t="n">
+      <c r="H27" s="68" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",MIN(B27/45,3/4*(0.49+B27/100)))</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="I27" s="64" t="str">
+      <c r="I27" s="70" t="str">
         <f aca="false">IF(B27&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B27/40&lt;=3/4*(0.49+B27/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B27/45&lt;=3/4*(0.49+B27/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：Fc/40　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="60" t="n">
+      <c r="B28" s="66" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="61" t="n">
+      <c r="C28" s="67" t="n">
         <f aca="false">B28/4</f>
         <v>6</v>
       </c>
-      <c r="D28" s="62" t="n">
+      <c r="D28" s="68" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",B28/4)</f>
         <v>6</v>
       </c>
-      <c r="E28" s="62" t="n">
+      <c r="E28" s="68" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",B28/4.5)</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F28" s="63" t="n">
+      <c r="F28" s="69" t="n">
         <f aca="false">IF(B28&gt;36,"—",C28-E28)</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="G28" s="62" t="n">
+      <c r="G28" s="68" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",MIN(B28/40,3/4*(0.49+B28/100)))</f>
         <v>0.5475</v>
       </c>
-      <c r="H28" s="62" t="n">
+      <c r="H28" s="68" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",MIN(B28/45,3/4*(0.49+B28/100)))</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="I28" s="64" t="str">
+      <c r="I28" s="70" t="str">
         <f aca="false">IF(B28&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B28/40&lt;=3/4*(0.49+B28/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B28/45&lt;=3/4*(0.49+B28/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="60" t="n">
+      <c r="B29" s="66" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="61" t="n">
+      <c r="C29" s="67" t="n">
         <f aca="false">B29/4</f>
         <v>6.75</v>
       </c>
-      <c r="D29" s="62" t="n">
+      <c r="D29" s="68" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",B29/4)</f>
         <v>6.75</v>
       </c>
-      <c r="E29" s="62" t="n">
+      <c r="E29" s="68" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",B29/4.5)</f>
         <v>6</v>
       </c>
-      <c r="F29" s="63" t="n">
+      <c r="F29" s="69" t="n">
         <f aca="false">IF(B29&gt;36,"—",C29-E29)</f>
         <v>0.75</v>
       </c>
-      <c r="G29" s="62" t="n">
+      <c r="G29" s="68" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",MIN(B29/40,3/4*(0.49+B29/100)))</f>
         <v>0.57</v>
       </c>
-      <c r="H29" s="62" t="n">
+      <c r="H29" s="68" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",MIN(B29/45,3/4*(0.49+B29/100)))</f>
         <v>0.57</v>
       </c>
-      <c r="I29" s="64" t="str">
+      <c r="I29" s="70" t="str">
         <f aca="false">IF(B29&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B29/40&lt;=3/4*(0.49+B29/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B29/45&lt;=3/4*(0.49+B29/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="60" t="n">
+      <c r="B30" s="66" t="n">
         <v>30</v>
       </c>
-      <c r="C30" s="61" t="n">
+      <c r="C30" s="67" t="n">
         <f aca="false">B30/4</f>
         <v>7.5</v>
       </c>
-      <c r="D30" s="62" t="n">
+      <c r="D30" s="68" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",B30/4)</f>
         <v>7.5</v>
       </c>
-      <c r="E30" s="62" t="n">
+      <c r="E30" s="68" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",B30/4.5)</f>
         <v>6.66666666666667</v>
       </c>
-      <c r="F30" s="63" t="n">
+      <c r="F30" s="69" t="n">
         <f aca="false">IF(B30&gt;36,"—",C30-E30)</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="68" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",MIN(B30/40,3/4*(0.49+B30/100)))</f>
         <v>0.5925</v>
       </c>
-      <c r="H30" s="62" t="n">
+      <c r="H30" s="68" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",MIN(B30/45,3/4*(0.49+B30/100)))</f>
         <v>0.5925</v>
       </c>
-      <c r="I30" s="64" t="str">
+      <c r="I30" s="70" t="str">
         <f aca="false">IF(B30&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B30/40&lt;=3/4*(0.49+B30/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B30/45&lt;=3/4*(0.49+B30/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="60" t="n">
+      <c r="B31" s="66" t="n">
         <v>33</v>
       </c>
-      <c r="C31" s="61" t="n">
+      <c r="C31" s="67" t="n">
         <f aca="false">B31/4</f>
         <v>8.25</v>
       </c>
-      <c r="D31" s="62" t="n">
+      <c r="D31" s="68" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",B31/4)</f>
         <v>8.25</v>
       </c>
-      <c r="E31" s="62" t="n">
+      <c r="E31" s="68" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",B31/4.5)</f>
         <v>7.33333333333333</v>
       </c>
-      <c r="F31" s="63" t="n">
+      <c r="F31" s="69" t="n">
         <f aca="false">IF(B31&gt;36,"—",C31-E31)</f>
         <v>0.916666666666667</v>
       </c>
-      <c r="G31" s="62" t="n">
+      <c r="G31" s="68" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",MIN(B31/40,3/4*(0.49+B31/100)))</f>
         <v>0.615</v>
       </c>
-      <c r="H31" s="62" t="n">
+      <c r="H31" s="68" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",MIN(B31/45,3/4*(0.49+B31/100)))</f>
         <v>0.615</v>
       </c>
-      <c r="I31" s="64" t="str">
+      <c r="I31" s="70" t="str">
         <f aca="false">IF(B31&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B31/40&lt;=3/4*(0.49+B31/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B31/45&lt;=3/4*(0.49+B31/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="60" t="n">
+      <c r="B32" s="66" t="n">
         <v>36</v>
       </c>
-      <c r="C32" s="61" t="n">
+      <c r="C32" s="67" t="n">
         <f aca="false">B32/4</f>
         <v>9</v>
       </c>
-      <c r="D32" s="62" t="n">
+      <c r="D32" s="68" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",B32/4)</f>
         <v>9</v>
       </c>
-      <c r="E32" s="62" t="n">
+      <c r="E32" s="68" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",B32/4.5)</f>
         <v>8</v>
       </c>
-      <c r="F32" s="63" t="n">
+      <c r="F32" s="69" t="n">
         <f aca="false">IF(B32&gt;36,"—",C32-E32)</f>
         <v>1</v>
       </c>
-      <c r="G32" s="62" t="n">
+      <c r="G32" s="68" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",MIN(B32/40,3/4*(0.49+B32/100)))</f>
         <v>0.6375</v>
       </c>
-      <c r="H32" s="62" t="n">
+      <c r="H32" s="68" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",MIN(B32/45,3/4*(0.49+B32/100)))</f>
         <v>0.6375</v>
       </c>
-      <c r="I32" s="64" t="str">
+      <c r="I32" s="70" t="str">
         <f aca="false">IF(B32&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B32/40&lt;=3/4*(0.49+B32/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B32/45&lt;=3/4*(0.49+B32/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="60" t="n">
+      <c r="B33" s="66" t="n">
         <v>40</v>
       </c>
-      <c r="C33" s="61" t="n">
+      <c r="C33" s="67" t="n">
         <f aca="false">B33/4</f>
         <v>10</v>
       </c>
-      <c r="D33" s="62" t="str">
+      <c r="D33" s="68" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",B33/4)</f>
         <v>範囲外</v>
       </c>
-      <c r="E33" s="62" t="str">
+      <c r="E33" s="68" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",B33/4.5)</f>
         <v>範囲外</v>
       </c>
-      <c r="F33" s="63" t="str">
+      <c r="F33" s="69" t="str">
         <f aca="false">IF(B33&gt;36,"—",C33-E33)</f>
         <v>—</v>
       </c>
-      <c r="G33" s="62" t="str">
+      <c r="G33" s="68" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",MIN(B33/40,3/4*(0.49+B33/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="H33" s="62" t="str">
+      <c r="H33" s="68" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",MIN(B33/45,3/4*(0.49+B33/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="I33" s="64" t="str">
+      <c r="I33" s="70" t="str">
         <f aca="false">IF(B33&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B33/40&lt;=3/4*(0.49+B33/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B33/45&lt;=3/4*(0.49+B33/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>SB協会の範囲外（Fc＞36）</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="60" t="n">
+      <c r="B34" s="66" t="n">
         <v>45</v>
       </c>
-      <c r="C34" s="61" t="n">
+      <c r="C34" s="67" t="n">
         <f aca="false">B34/4</f>
         <v>11.25</v>
       </c>
-      <c r="D34" s="62" t="str">
+      <c r="D34" s="68" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",B34/4)</f>
         <v>範囲外</v>
       </c>
-      <c r="E34" s="62" t="str">
+      <c r="E34" s="68" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",B34/4.5)</f>
         <v>範囲外</v>
       </c>
-      <c r="F34" s="63" t="str">
+      <c r="F34" s="69" t="str">
         <f aca="false">IF(B34&gt;36,"—",C34-E34)</f>
         <v>—</v>
       </c>
-      <c r="G34" s="62" t="str">
+      <c r="G34" s="68" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",MIN(B34/40,3/4*(0.49+B34/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="H34" s="62" t="str">
+      <c r="H34" s="68" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",MIN(B34/45,3/4*(0.49+B34/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="I34" s="64" t="str">
+      <c r="I34" s="70" t="str">
         <f aca="false">IF(B34&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B34/40&lt;=3/4*(0.49+B34/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B34/45&lt;=3/4*(0.49+B34/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>SB協会の範囲外（Fc＞36）</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5365,23 +6337,23 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="42" t="s">
-        <v>335</v>
+      <c r="B2" s="48" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>336</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="43" t="s">
-        <v>337</v>
+      <c r="B4" s="49" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -5390,126 +6362,126 @@
       <c r="G6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="C7" s="65" t="n">
+      <c r="B7" s="50" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7" s="71" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="F7" s="66" t="s">
-        <v>340</v>
-      </c>
-      <c r="G7" s="66"/>
+      <c r="D7" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>388</v>
+      </c>
+      <c r="G7" s="72"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="C8" s="65" t="n">
+      <c r="B8" s="50" t="s">
+        <v>389</v>
+      </c>
+      <c r="C8" s="71" t="n">
         <v>16</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="F8" s="66" t="s">
-        <v>340</v>
-      </c>
-      <c r="G8" s="66"/>
+      <c r="D8" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>388</v>
+      </c>
+      <c r="G8" s="72"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="44" t="s">
-        <v>342</v>
-      </c>
-      <c r="C9" s="67" t="n">
+      <c r="B9" s="50" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="F9" s="66" t="s">
-        <v>343</v>
-      </c>
-      <c r="G9" s="66"/>
+      <c r="D9" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="F9" s="72" t="s">
+        <v>391</v>
+      </c>
+      <c r="G9" s="72"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="C10" s="65" t="n">
+      <c r="B10" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="C10" s="71" t="n">
         <v>235</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" s="66" t="s">
-        <v>344</v>
-      </c>
-      <c r="G10" s="66"/>
+      <c r="D10" s="52" t="s">
+        <v>346</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>392</v>
+      </c>
+      <c r="G10" s="72"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="44" t="s">
-        <v>345</v>
-      </c>
-      <c r="C11" s="67" t="n">
+      <c r="B11" s="50" t="s">
+        <v>393</v>
+      </c>
+      <c r="C11" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="68" t="s">
+      <c r="D11" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="F11" s="72" t="s">
+        <v>395</v>
+      </c>
+      <c r="G11" s="72"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="50" t="s">
+        <v>396</v>
+      </c>
+      <c r="C12" s="71" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="52" t="s">
         <v>346</v>
       </c>
-      <c r="F11" s="66" t="s">
-        <v>347</v>
-      </c>
-      <c r="G11" s="66"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="44" t="s">
-        <v>348</v>
-      </c>
-      <c r="C12" s="65" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="F12" s="66" t="s">
-        <v>349</v>
-      </c>
-      <c r="G12" s="66"/>
+      <c r="F12" s="72" t="s">
+        <v>397</v>
+      </c>
+      <c r="G12" s="72"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="44" t="s">
-        <v>350</v>
-      </c>
-      <c r="C13" s="65" t="n">
+      <c r="B13" s="50" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="71" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="F13" s="66" t="s">
-        <v>349</v>
-      </c>
-      <c r="G13" s="66"/>
+      <c r="D13" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>397</v>
+      </c>
+      <c r="G13" s="72"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="69" t="s">
-        <v>351</v>
-      </c>
-      <c r="C14" s="67" t="n">
+      <c r="B14" s="75" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="F14" s="70" t="s">
-        <v>352</v>
-      </c>
-      <c r="G14" s="70"/>
+      <c r="D14" s="52"/>
+      <c r="F14" s="76" t="s">
+        <v>400</v>
+      </c>
+      <c r="G14" s="76"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -5522,154 +6494,154 @@
         <v>9</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>355</v>
+        <v>403</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="25" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="71" t="n">
+      <c r="B17" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="C17" s="77" t="n">
         <f aca="false">C7-2*C9</f>
         <v>1198</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>357</v>
-      </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
+      <c r="D17" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="E17" s="78" t="s">
+        <v>405</v>
+      </c>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="C18" s="71" t="n">
+      <c r="B18" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="C18" s="77" t="n">
         <f aca="false">C8-C9</f>
         <v>15</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="E18" s="72" t="s">
-        <v>359</v>
-      </c>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
+      <c r="D18" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="E18" s="78" t="s">
+        <v>407</v>
+      </c>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="C19" s="71" t="n">
+      <c r="B19" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="C19" s="77" t="n">
         <f aca="false">C17-2*C18</f>
         <v>1168</v>
       </c>
-      <c r="D19" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="E19" s="72" t="s">
-        <v>361</v>
-      </c>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
+      <c r="D19" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="E19" s="78" t="s">
+        <v>409</v>
+      </c>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="25" t="s">
-        <v>362</v>
-      </c>
-      <c r="C20" s="73" t="n">
+      <c r="B20" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C20" s="79" t="n">
         <f aca="false">PI()/4*(C17^2-C19^2)</f>
         <v>55747.5616379509</v>
       </c>
-      <c r="D20" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="E20" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
+      <c r="D20" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="E20" s="78" t="s">
+        <v>412</v>
+      </c>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="C21" s="73" t="n">
+      <c r="B21" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="C21" s="79" t="n">
         <f aca="false">PI()/32*(C17^4-C19^4)/C17</f>
         <v>16283523.0572836</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="E21" s="72" t="s">
-        <v>367</v>
-      </c>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
+      <c r="D21" s="45" t="s">
+        <v>414</v>
+      </c>
+      <c r="E21" s="78" t="s">
+        <v>415</v>
+      </c>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="25" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" s="74" t="n">
+      <c r="B22" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="C22" s="80" t="n">
         <f aca="false">C10/1.5</f>
         <v>156.666666666667</v>
       </c>
-      <c r="D22" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="E22" s="72" t="s">
-        <v>369</v>
-      </c>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
+      <c r="D22" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="E22" s="78" t="s">
+        <v>417</v>
+      </c>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="C23" s="74" t="n">
+      <c r="B23" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C23" s="80" t="n">
         <f aca="false">C10/(1.5*SQRT(3))</f>
         <v>90.4515421730414</v>
       </c>
-      <c r="D23" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="E23" s="72" t="s">
-        <v>371</v>
-      </c>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
+      <c r="D23" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="E23" s="78" t="s">
+        <v>419</v>
+      </c>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="C24" s="74" t="n">
+      <c r="B24" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="C24" s="80" t="n">
         <f aca="false">C10*C11</f>
         <v>235</v>
       </c>
-      <c r="D24" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="E24" s="72" t="s">
-        <v>373</v>
-      </c>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
+      <c r="D24" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="E24" s="78" t="s">
+        <v>421</v>
+      </c>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -5688,233 +6660,233 @@
         <v>11</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>355</v>
+        <v>403</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="22" t="s">
-        <v>377</v>
-      </c>
-      <c r="C28" s="75" t="n">
+      <c r="B28" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="C28" s="81" t="n">
         <f aca="false">C21*C22/1000000</f>
         <v>2551.08527897442</v>
       </c>
-      <c r="D28" s="76" t="n">
+      <c r="D28" s="82" t="n">
         <f aca="false">C21*C22/1000000</f>
         <v>2551.08527897442</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F28" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>380</v>
+      <c r="E28" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="F28" s="55" t="s">
+        <v>427</v>
+      </c>
+      <c r="G28" s="55" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="22" t="s">
-        <v>381</v>
-      </c>
-      <c r="C29" s="75" t="n">
+      <c r="B29" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="81" t="n">
         <f aca="false">1.5*C28</f>
         <v>3826.62791846163</v>
       </c>
-      <c r="D29" s="76" t="n">
+      <c r="D29" s="82" t="n">
         <f aca="false">1.5*D28</f>
         <v>3826.62791846163</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>382</v>
-      </c>
-      <c r="G29" s="50" t="s">
-        <v>383</v>
+      <c r="E29" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="G29" s="56" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="22" t="s">
-        <v>384</v>
-      </c>
-      <c r="C30" s="75" t="n">
+      <c r="B30" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="C30" s="81" t="n">
         <f aca="false">C20/2*C23/1000</f>
         <v>2521.22646126967</v>
       </c>
-      <c r="D30" s="76" t="n">
+      <c r="D30" s="82" t="n">
         <f aca="false">C20/2*C23/1000</f>
         <v>2521.22646126967</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F30" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="G30" s="50" t="s">
-        <v>387</v>
+      <c r="E30" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="F30" s="55" t="s">
+        <v>434</v>
+      </c>
+      <c r="G30" s="56" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22" t="s">
-        <v>388</v>
-      </c>
-      <c r="C31" s="75" t="n">
+      <c r="B31" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="C31" s="81" t="n">
         <f aca="false">1.5*C30</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="D31" s="76" t="n">
+      <c r="D31" s="82" t="n">
         <f aca="false">1.5*D30</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>382</v>
-      </c>
-      <c r="G31" s="50" t="s">
-        <v>387</v>
+      <c r="E31" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="F31" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="G31" s="56" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="22" t="s">
-        <v>389</v>
-      </c>
-      <c r="C32" s="75" t="n">
+      <c r="B32" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="C32" s="81" t="n">
         <f aca="false">C20/2*C24/SQRT(3)/1000</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="D32" s="76" t="n">
+      <c r="D32" s="82" t="n">
         <f aca="false">C20*(C24/SQRT(3))*(1/C14)/1000</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>390</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>391</v>
+      <c r="E32" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>438</v>
+      </c>
+      <c r="G32" s="55" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="22" t="s">
-        <v>392</v>
-      </c>
-      <c r="C33" s="75" t="n">
+      <c r="B33" s="24" t="s">
+        <v>440</v>
+      </c>
+      <c r="C33" s="81" t="n">
         <f aca="false">C12*C7*C13/1000</f>
         <v>2880</v>
       </c>
-      <c r="D33" s="77" t="s">
-        <v>311</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F33" s="49" t="s">
-        <v>393</v>
-      </c>
-      <c r="G33" s="49" t="s">
-        <v>394</v>
+      <c r="D33" s="83" t="s">
+        <v>359</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>441</v>
+      </c>
+      <c r="G33" s="55" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="C34" s="78" t="n">
+      <c r="B34" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="C34" s="84" t="n">
         <f aca="false">MIN(C32,C33)</f>
         <v>2880</v>
       </c>
-      <c r="D34" s="79" t="n">
+      <c r="D34" s="85" t="n">
         <f aca="false">D32</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F34" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="G34" s="50"/>
+      <c r="E34" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="G34" s="56"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="52" t="s">
-        <v>397</v>
-      </c>
-      <c r="C35" s="75" t="str">
+      <c r="B35" s="58" t="s">
+        <v>445</v>
+      </c>
+      <c r="C35" s="81" t="str">
         <f aca="false">IF(C33&lt;C32,"杭頭接合部で決定","鋼管で決定")</f>
         <v>杭頭接合部で決定</v>
       </c>
-      <c r="D35" s="77" t="s">
-        <v>398</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="49" t="s">
-        <v>399</v>
+      <c r="D35" s="83" t="s">
+        <v>446</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="55" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22" t="s">
-        <v>400</v>
-      </c>
-      <c r="C36" s="80" t="s">
-        <v>401</v>
-      </c>
-      <c r="D36" s="76" t="n">
+      <c r="B36" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="C36" s="86" t="s">
+        <v>449</v>
+      </c>
+      <c r="D36" s="82" t="n">
         <f aca="false">(C17-C18)^2*C18*C24/1000000</f>
         <v>4933.198725</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>402</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>403</v>
+      <c r="E36" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>450</v>
+      </c>
+      <c r="G36" s="55" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="66" t="s">
-        <v>404</v>
-      </c>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
+      <c r="B38" s="72" t="s">
+        <v>452</v>
+      </c>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="70" t="s">
-        <v>405</v>
-      </c>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
+      <c r="B39" s="76" t="s">
+        <v>453</v>
+      </c>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="70" t="s">
-        <v>406</v>
-      </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
+      <c r="B40" s="76" t="s">
+        <v>454</v>
+      </c>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -5972,8 +6944,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
-        <v>407</v>
+      <c r="A1" s="48" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5982,12 +6954,12 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>408</v>
+      <c r="A3" s="49" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="30" t="str">
+      <c r="C4" s="32" t="str">
         <f aca="false">"集計　未："&amp;COUNTIF($E$6:$E$25,"未")&amp;" 件　／　済："&amp;COUNTIF($E$6:$E$25,"済")&amp;" 件　／　対象外："&amp;COUNTIF($E$6:$E$25,"対象外")&amp;" 件"</f>
         <v>集計　未：19 件　／　済：1 件　／　対象外：0 件</v>
       </c>
@@ -5997,382 +6969,382 @@
         <v>8</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>410</v>
+        <v>458</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>415</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="82" t="s">
-        <v>416</v>
-      </c>
-      <c r="F6" s="83" t="s">
-        <v>417</v>
+      <c r="B6" s="87" t="s">
+        <v>462</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>463</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="88" t="s">
+        <v>464</v>
+      </c>
+      <c r="F6" s="89" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>419</v>
-      </c>
-      <c r="E7" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F7" s="83"/>
+      <c r="B7" s="87" t="s">
+        <v>462</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>467</v>
+      </c>
+      <c r="E7" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F7" s="89"/>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F8" s="83"/>
+      <c r="B8" s="87" t="s">
+        <v>462</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F8" s="89"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="E9" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F9" s="83"/>
+      <c r="B9" s="87" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E9" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F9" s="89"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>424</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F10" s="83"/>
+      <c r="B10" s="87" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F10" s="89"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>425</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="E11" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F11" s="83"/>
+      <c r="B11" s="87" t="s">
+        <v>462</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F11" s="89"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>428</v>
-      </c>
-      <c r="E12" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F12" s="83"/>
+      <c r="B12" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>476</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F12" s="89"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>430</v>
-      </c>
-      <c r="E13" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F13" s="83"/>
+      <c r="B13" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="E13" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F13" s="89"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>238</v>
-      </c>
-      <c r="E14" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F14" s="83"/>
+      <c r="B14" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F14" s="89"/>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>433</v>
-      </c>
-      <c r="E15" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F15" s="83"/>
+      <c r="B15" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>481</v>
+      </c>
+      <c r="E15" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F15" s="89"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="D16" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="E16" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F16" s="83"/>
+      <c r="B16" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F16" s="89"/>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="n">
+      <c r="A17" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>435</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>436</v>
-      </c>
-      <c r="E17" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F17" s="83"/>
+      <c r="B17" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>484</v>
+      </c>
+      <c r="E17" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F17" s="89"/>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>438</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F18" s="83"/>
+      <c r="B18" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F18" s="89"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="n">
+      <c r="A19" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F19" s="83"/>
+      <c r="B19" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F19" s="89"/>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
+      <c r="A20" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>440</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>441</v>
-      </c>
-      <c r="E20" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F20" s="83"/>
+      <c r="B20" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="D20" s="56" t="s">
+        <v>489</v>
+      </c>
+      <c r="E20" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F20" s="89"/>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="D21" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="E21" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F21" s="83"/>
+      <c r="B21" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>490</v>
+      </c>
+      <c r="D21" s="56" t="s">
+        <v>491</v>
+      </c>
+      <c r="E21" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F21" s="89"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="n">
+      <c r="A22" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="D22" s="50" t="s">
-        <v>445</v>
-      </c>
-      <c r="E22" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F22" s="83"/>
+      <c r="B22" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="D22" s="56" t="s">
+        <v>493</v>
+      </c>
+      <c r="E22" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F22" s="89"/>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="n">
+      <c r="A23" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>446</v>
-      </c>
-      <c r="D23" s="49" t="s">
-        <v>447</v>
-      </c>
-      <c r="E23" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F23" s="83"/>
+      <c r="B23" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>494</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>495</v>
+      </c>
+      <c r="E23" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F23" s="89"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="n">
+      <c r="A24" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>449</v>
-      </c>
-      <c r="E24" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F24" s="83"/>
+      <c r="B24" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>497</v>
+      </c>
+      <c r="E24" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F24" s="89"/>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="n">
+      <c r="A25" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>451</v>
-      </c>
-      <c r="E25" s="82" t="s">
-        <v>420</v>
-      </c>
-      <c r="F25" s="83"/>
+      <c r="B25" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>498</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>499</v>
+      </c>
+      <c r="E25" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F25" s="89"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E6:E25">
@@ -6415,365 +7387,365 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="42" t="s">
-        <v>97</v>
+      <c r="B2" s="48" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="86" t="s">
-        <v>452</v>
+      <c r="B3" s="92" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>457</v>
-      </c>
-      <c r="D6" s="88" t="s">
-        <v>414</v>
+      <c r="B6" s="93" t="s">
+        <v>504</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" s="94" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="87" t="s">
-        <v>458</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D7" s="88" t="s">
-        <v>414</v>
+      <c r="B7" s="93" t="s">
+        <v>506</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>507</v>
+      </c>
+      <c r="D7" s="94" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="D8" s="84" t="s">
-        <v>426</v>
+      <c r="B8" s="93" t="s">
+        <v>508</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="93" t="s">
+        <v>510</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="D9" s="91" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="93" t="s">
+        <v>512</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="D10" s="94" t="s">
         <v>462</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="D9" s="85" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="87" t="s">
-        <v>464</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="D10" s="88" t="s">
-        <v>414</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="87" t="s">
-        <v>466</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="D11" s="84" t="s">
-        <v>426</v>
+      <c r="B11" s="93" t="s">
+        <v>514</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="87" t="s">
-        <v>468</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="D12" s="85" t="s">
-        <v>437</v>
+      <c r="B12" s="93" t="s">
+        <v>516</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="87" t="s">
-        <v>470</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>471</v>
-      </c>
-      <c r="D13" s="84" t="s">
-        <v>426</v>
+      <c r="B13" s="93" t="s">
+        <v>518</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>519</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="87" t="s">
-        <v>472</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>473</v>
-      </c>
-      <c r="D14" s="84" t="s">
-        <v>426</v>
+      <c r="B14" s="93" t="s">
+        <v>520</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="D14" s="90" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="93" t="s">
+        <v>522</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>523</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="93" t="s">
+        <v>524</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>525</v>
+      </c>
+      <c r="D16" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="93" t="s">
+        <v>526</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="93" t="s">
+        <v>529</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="D18" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="93" t="s">
+        <v>531</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="D19" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="93" t="s">
+        <v>533</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="93" t="s">
+        <v>534</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>535</v>
+      </c>
+      <c r="D21" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="93" t="s">
+        <v>536</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="D22" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="93" t="s">
+        <v>538</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="D23" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="93" t="s">
+        <v>540</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>541</v>
+      </c>
+      <c r="D24" s="91" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="93" t="s">
+        <v>542</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>543</v>
+      </c>
+      <c r="D25" s="91" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="93" t="s">
+        <v>544</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="D26" s="90" t="s">
         <v>474</v>
       </c>
-      <c r="C15" s="25" t="s">
-        <v>475</v>
-      </c>
-      <c r="D15" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="87" t="s">
-        <v>476</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>477</v>
-      </c>
-      <c r="D16" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="87" t="s">
-        <v>478</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="87" t="s">
-        <v>481</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>482</v>
-      </c>
-      <c r="D18" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="87" t="s">
-        <v>483</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="D19" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="87" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="93" t="s">
+        <v>546</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="D27" s="90" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="93" t="s">
+        <v>548</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>549</v>
+      </c>
+      <c r="D28" s="94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="93" t="s">
+        <v>550</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="D29" s="90" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="93" t="s">
+        <v>552</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="D30" s="91" t="s">
         <v>485</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="87" t="s">
-        <v>486</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="D21" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="87" t="s">
-        <v>488</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>489</v>
-      </c>
-      <c r="D22" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="87" t="s">
-        <v>490</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="D23" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="87" t="s">
-        <v>492</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>493</v>
-      </c>
-      <c r="D24" s="85" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="87" t="s">
-        <v>494</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>495</v>
-      </c>
-      <c r="D25" s="85" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="87" t="s">
-        <v>496</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>497</v>
-      </c>
-      <c r="D26" s="84" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="87" t="s">
-        <v>498</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>499</v>
-      </c>
-      <c r="D27" s="84" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="87" t="s">
-        <v>500</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>501</v>
-      </c>
-      <c r="D28" s="88" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="87" t="s">
-        <v>502</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="D29" s="84" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="87" t="s">
-        <v>504</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>505</v>
-      </c>
-      <c r="D30" s="85" t="s">
-        <v>437</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="87" t="s">
-        <v>506</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>507</v>
-      </c>
-      <c r="D31" s="88" t="s">
-        <v>414</v>
+      <c r="B31" s="93" t="s">
+        <v>554</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="D31" s="94" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="87" t="s">
-        <v>508</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>509</v>
-      </c>
-      <c r="D32" s="85" t="s">
-        <v>437</v>
+      <c r="B32" s="93" t="s">
+        <v>556</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="D32" s="91" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="87" t="s">
-        <v>510</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>511</v>
-      </c>
-      <c r="D33" s="85" t="s">
-        <v>437</v>
+      <c r="B33" s="93" t="s">
+        <v>558</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>559</v>
+      </c>
+      <c r="D33" s="91" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="87" t="s">
-        <v>512</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>513</v>
-      </c>
-      <c r="D34" s="85" t="s">
-        <v>437</v>
+      <c r="B34" s="93" t="s">
+        <v>560</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>561</v>
+      </c>
+      <c r="D34" s="91" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="87" t="s">
-        <v>514</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>515</v>
-      </c>
-      <c r="D35" s="88" t="s">
-        <v>414</v>
+      <c r="B35" s="93" t="s">
+        <v>562</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>563</v>
+      </c>
+      <c r="D35" s="94" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="87" t="s">
-        <v>516</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="D36" s="84" t="s">
-        <v>426</v>
+      <c r="B36" s="93" t="s">
+        <v>564</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>565</v>
+      </c>
+      <c r="D36" s="90" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -6785,4 +7757,1164 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFC00000"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="B2:G60"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="92" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="95" t="s">
+        <v>573</v>
+      </c>
+      <c r="C6" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>575</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="95" t="s">
+        <v>577</v>
+      </c>
+      <c r="C7" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="95" t="s">
+        <v>580</v>
+      </c>
+      <c r="C8" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="95" t="s">
+        <v>583</v>
+      </c>
+      <c r="C9" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="95" t="s">
+        <v>586</v>
+      </c>
+      <c r="C10" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="95" t="s">
+        <v>589</v>
+      </c>
+      <c r="C11" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="95" t="s">
+        <v>592</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>594</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="95" t="s">
+        <v>596</v>
+      </c>
+      <c r="C13" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>597</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="95" t="s">
+        <v>599</v>
+      </c>
+      <c r="C14" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>600</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="95" t="s">
+        <v>602</v>
+      </c>
+      <c r="C15" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>603</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="95" t="s">
+        <v>605</v>
+      </c>
+      <c r="C16" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>606</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="95" t="s">
+        <v>608</v>
+      </c>
+      <c r="C17" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>610</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="95" t="s">
+        <v>612</v>
+      </c>
+      <c r="C18" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>613</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="95" t="s">
+        <v>615</v>
+      </c>
+      <c r="C19" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>616</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="95" t="s">
+        <v>618</v>
+      </c>
+      <c r="C20" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="95" t="s">
+        <v>621</v>
+      </c>
+      <c r="C21" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>622</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="C22" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>625</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="95" t="s">
+        <v>627</v>
+      </c>
+      <c r="C23" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>629</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="95" t="s">
+        <v>631</v>
+      </c>
+      <c r="C24" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>632</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="95" t="s">
+        <v>633</v>
+      </c>
+      <c r="C25" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>634</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="95" t="s">
+        <v>636</v>
+      </c>
+      <c r="C26" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>637</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="95" t="s">
+        <v>639</v>
+      </c>
+      <c r="C27" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="95" t="s">
+        <v>640</v>
+      </c>
+      <c r="C28" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>641</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="95" t="s">
+        <v>643</v>
+      </c>
+      <c r="C29" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="95" t="s">
+        <v>644</v>
+      </c>
+      <c r="C30" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>646</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="95" t="s">
+        <v>648</v>
+      </c>
+      <c r="C31" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>649</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="95" t="s">
+        <v>650</v>
+      </c>
+      <c r="C32" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="95" t="s">
+        <v>652</v>
+      </c>
+      <c r="C33" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>653</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="95" t="s">
+        <v>654</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>655</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="95" t="s">
+        <v>656</v>
+      </c>
+      <c r="C35" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>657</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="95" t="s">
+        <v>658</v>
+      </c>
+      <c r="C36" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>610</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="95" t="s">
+        <v>659</v>
+      </c>
+      <c r="C37" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>661</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="95" t="s">
+        <v>662</v>
+      </c>
+      <c r="C38" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="95" t="s">
+        <v>664</v>
+      </c>
+      <c r="C39" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="95" t="s">
+        <v>666</v>
+      </c>
+      <c r="C40" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>667</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="95" t="s">
+        <v>669</v>
+      </c>
+      <c r="C41" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>671</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="95" t="s">
+        <v>673</v>
+      </c>
+      <c r="C42" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="F42" s="30" t="s">
+        <v>674</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="95" t="s">
+        <v>676</v>
+      </c>
+      <c r="C43" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>678</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="95" t="s">
+        <v>680</v>
+      </c>
+      <c r="C44" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>681</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="95" t="s">
+        <v>682</v>
+      </c>
+      <c r="C45" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="F45" s="30" t="s">
+        <v>683</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="95" t="s">
+        <v>685</v>
+      </c>
+      <c r="C46" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="F46" s="30" t="s">
+        <v>687</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="95" t="s">
+        <v>689</v>
+      </c>
+      <c r="C47" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="F47" s="30" t="s">
+        <v>691</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="95" t="s">
+        <v>693</v>
+      </c>
+      <c r="C48" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="F48" s="30" t="s">
+        <v>694</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="95" t="s">
+        <v>695</v>
+      </c>
+      <c r="C49" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="F49" s="30" t="s">
+        <v>696</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="95" t="s">
+        <v>697</v>
+      </c>
+      <c r="C50" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>698</v>
+      </c>
+      <c r="F50" s="30" t="s">
+        <v>699</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="95" t="s">
+        <v>701</v>
+      </c>
+      <c r="C51" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="F51" s="30" t="s">
+        <v>703</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="95" t="s">
+        <v>704</v>
+      </c>
+      <c r="C52" s="94" t="s">
+        <v>462</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="F52" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="95" t="s">
+        <v>707</v>
+      </c>
+      <c r="C53" s="94" t="s">
+        <v>462</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="F53" s="30" t="s">
+        <v>708</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="95" t="s">
+        <v>710</v>
+      </c>
+      <c r="C54" s="94" t="s">
+        <v>462</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="F54" s="30" t="s">
+        <v>712</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="95" t="s">
+        <v>714</v>
+      </c>
+      <c r="C55" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="F55" s="30" t="s">
+        <v>715</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="95" t="s">
+        <v>717</v>
+      </c>
+      <c r="C56" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>718</v>
+      </c>
+      <c r="F56" s="27" t="s">
+        <v>719</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="95" t="s">
+        <v>721</v>
+      </c>
+      <c r="C57" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>722</v>
+      </c>
+      <c r="F57" s="30" t="s">
+        <v>723</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="95" t="s">
+        <v>725</v>
+      </c>
+      <c r="C58" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>722</v>
+      </c>
+      <c r="F58" s="30" t="s">
+        <v>726</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="95" t="s">
+        <v>728</v>
+      </c>
+      <c r="C59" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>722</v>
+      </c>
+      <c r="F59" s="30" t="s">
+        <v>729</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="95" t="s">
+        <v>730</v>
+      </c>
+      <c r="C60" s="91" t="s">
+        <v>485</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>722</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>731</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>727</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B5:G60"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/資料/TB杭とSB杭の違い_SS7.xlsx
+++ b/資料/TB杭とSB杭の違い_SS7.xlsx
@@ -9,20 +9,21 @@
   </bookViews>
   <sheets>
     <sheet name="要点まとめ" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="比較一覧" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="許容応力度_試算" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="鋼管部_試算" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="設計チェック" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="記号の説明" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="PDF対照表" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="軸力負担の比較" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="比較一覧" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="許容応力度_試算" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="鋼管部_試算" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="設計チェック" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="記号の説明" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="PDF対照表" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">PDF対照表!$5:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">PDF対照表!$B$5:$G$60</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">比較一覧!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">比較一覧!$A$4:$I$50</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">記号の説明!$5:$5</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">設計チェック!$5:$5</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">PDF対照表!$5:$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">PDF対照表!$B$5:$G$60</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">比較一覧!$4:$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">比較一覧!$A$4:$I$50</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">記号の説明!$5:$5</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">設計チェック!$5:$5</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="800">
   <si>
     <t xml:space="preserve">TB杭とSB杭の違い ― 要点まとめ</t>
   </si>
@@ -389,6 +390,12 @@
     <t xml:space="preserve">比較一覧で使っている記号の意味</t>
   </si>
   <si>
+    <t xml:space="preserve">軸力負担の比較</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB杭とSB杭の「鋼管が軸力を負担するか」の違いに絞った比較表と比較図</t>
+  </si>
+  <si>
     <t xml:space="preserve">PDF対照表</t>
   </si>
   <si>
@@ -396,6 +403,223 @@
   </si>
   <si>
     <t xml:space="preserve">※「記載なし（本資料の範囲）」は、ご提供の抜粋にその記述がないという意味です。プログラムや協会指針に規定がないことを意味しません。実設計では各協会の設計・施工指針とSS7の最新マニュアルを必ず確認してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杭頭の鋼管は「軸力」を負担するか？ ― TB杭（KCTB）と SB耐震杭の比較</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管のリブの有無と、鋼管が軸力を負担するかどうかに絞った比較表です（SS7マニュアル 7.7.5／7.7.6／10.15 より）。表の下に比較図を貼り付けています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB杭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管の内側にリブあり → 鋼管も軸力を負担する（中のRCの許容範囲を超えた分）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB杭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リブの規定なし → 鋼管は軸力を負担しない（曲げ・せん断のみ。軸力はRC部だけ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 比較表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB杭（KCTB 場所打ち鋼管コンクリート杭）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB杭（SB耐震杭）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポイント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF赤枠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管の内面リブ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり
+（「鋼管は内側にリブがついたものとします」）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規定なし
+（マニュアルに記述なし）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リブはコンクリートと鋼管の間で力を伝える「ずれ止め」として働く（式の組み立てからの解釈）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杭頭部の部位名（SS7）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管コンクリート部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管巻き鉄筋コンクリート部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6／S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管の軸力負担</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○ 負担する
+（RCの許容範囲を超えた分を鋼管が負担）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">× 負担しない
+（鋼管の軸力＝0）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いちばん大きな違い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6・T7／S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCの軸力負担</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○ 負担する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○ 負担する（軸力はRCだけ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">曲げの負担</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管＋RC（累加）
+M ≦ sM0＋rM など</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管 sM0 ＋ RC rMA（累加）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どちらも鋼管が曲げを負担</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7・T8／S8・S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">せん断の負担（許容）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管のみ
+Qa＝sA/2・sfs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同じ式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T13／S14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">算定方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRC規準と同様の累加強度方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRC規準・鋼管コンクリート規準と同様の単純累加強度方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">検定のケース数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3ケース（軸力の大きさで分ける）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ケース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">検定式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N＞rNc：N ≦ rNc＋sN、M＝sM
+rNc≧N≧rNt：N＝rN、M ≦ sM0＋rM
+rNt＞N：N ≧ rNt＋sN、M＝sM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ND＝rNA（rN0 ≧ ND ≧ rNt）
+MD ≦ sM0＋rMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBは式に鋼管の軸力 sN が入る。SBは入らない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引張側の許容軸力 rNt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt＝−rf・rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt＝−0.75・rf・rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBは0.75倍に低減</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10／S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">許容できる軸力の幅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCの範囲（rNt〜rNc）＋鋼管の分だけ広い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCの範囲（rNt〜rN0）だけ。引張側も0.75倍で狭い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">範囲を超えるとSBはNG（鋼管の余裕なし）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6・T7／S8・S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終局曲げの評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">断面解析で鋼管とRCを一体で評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mu＝Mrc＋Mst
+（Mstは全塑性、鋼管は軸力を負担しない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T19／S21・S22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設計上の影響</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大きな圧縮・引抜き軸力でも鋼管の分だけ余裕がある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">軸力はRC部だけで収める必要があり、引抜きは0.75倍低減でさらに厳しい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">軸力の大きい杭頭（塔状建物、外周の杭など）で差が出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○：負担する（緑）　×：負担しない（赤）　「PDF赤枠」は赤枠入りPDFの枠ID（T＝TB杭、S＝SB杭）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※「リブの有無 → 軸力を負担するか」の対応は、SS7の式の組み立てからの解釈です。SB杭の鋼管にリブが無いとはマニュアルに明記されていません。実際の仕様は各協会の設計・施工指針で確認してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 比較図</t>
   </si>
   <si>
     <t xml:space="preserve">TB杭とSB杭の比較一覧（SS7 マニュアルより）</t>
@@ -695,9 +919,6 @@
   <si>
     <t xml:space="preserve">TB：T6（PDF p.1／7-63）、T7（PDF p.2／7-64）
 SB：S8（PDF p.5／7-67）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">検定式</t>
   </si>
   <si>
     <t xml:space="preserve">(i) N＞rNc のとき：N ≦ rNc＋sN、M＝sM
@@ -1447,9 +1668,6 @@
 (7.133)／(7.141)</t>
   </si>
   <si>
-    <t xml:space="preserve">同じ式</t>
-  </si>
-  <si>
     <t xml:space="preserve">鋼管部の許容せん断力 Qa（短期）</t>
   </si>
   <si>
@@ -1891,9 +2109,6 @@
   </si>
   <si>
     <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T4</t>
   </si>
   <si>
     <t xml:space="preserve">表7.17 鋼材の許容応力度（鋼管は内側リブ付き）</t>
@@ -2352,7 +2567,7 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2528,6 +2743,54 @@
       <charset val="128"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
       <name val="Meiryo UI"/>
@@ -2666,7 +2929,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2717,14 +2980,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CBAD"/>
         <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -2789,7 +3058,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="112">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2934,23 +3203,91 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2958,15 +3295,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2974,19 +3311,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2994,7 +3327,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3010,15 +3343,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="37" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3034,11 +3367,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="38" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3046,7 +3379,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3054,7 +3387,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3070,11 +3403,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3082,7 +3415,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3102,7 +3435,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3122,39 +3455,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="40" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="41" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="41" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="40" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3170,7 +3503,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3370,7 +3703,7 @@
       <rgbColor rgb="FF7F6000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF993366"/>
@@ -3379,7 +3712,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFFFC7CE"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -3389,11 +3722,11 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF2F75B5"/>
@@ -3418,10 +3751,52 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>201960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>729720</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>144360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="177840" y="9001080"/>
+          <a:ext cx="10953360" cy="6886080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -3606,7 +3981,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G50"/>
+  <dimension ref="B2:G51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4152,7 +4527,7 @@
       <c r="G47" s="31"/>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C48" s="34" t="s">
+      <c r="C48" s="32" t="s">
         <v>110</v>
       </c>
       <c r="D48" s="33" t="s">
@@ -4162,18 +4537,29 @@
       <c r="F48" s="33"/>
       <c r="G48" s="33"/>
     </row>
-    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="35" t="s">
+    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C49" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
+      <c r="D49" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+    </row>
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="B7:C7"/>
@@ -4193,7 +4579,8 @@
     <mergeCell ref="D46:G46"/>
     <mergeCell ref="D47:G47"/>
     <mergeCell ref="D48:G48"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="B51:G51"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C43" r:id="rId1" location="'比較一覧'!A1" display="比較一覧"/>
@@ -4201,7 +4588,8 @@
     <hyperlink ref="C45" r:id="rId3" location="'鋼管部_試算'!A1" display="鋼管部_試算"/>
     <hyperlink ref="C46" r:id="rId4" location="'設計チェック'!A1" display="設計チェック"/>
     <hyperlink ref="C47" r:id="rId5" location="'記号の説明'!A1" display="記号の説明"/>
-    <hyperlink ref="C48" r:id="rId6" location="'PDF対照表'!A1" display="PDF対照表"/>
+    <hyperlink ref="C48" r:id="rId6" location="'軸力負担の比較'!A1" display="軸力負担の比較"/>
+    <hyperlink ref="C49" r:id="rId7" location="'PDF対照表'!A1" display="PDF対照表"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4214,6 +4602,394 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFC00000"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="B2:G27"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+    </row>
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="45" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="F18" s="44"/>
+      <c r="G18" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="42" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="44"/>
+      <c r="G22" s="45" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B25:G25"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="26" man="true" max="16383" min="0"/>
+  </rowBreaks>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1F3864"/>
@@ -4234,7 +5010,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4243,85 +5019,85 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
+      <c r="A3" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>121</v>
+        <v>191</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="38" t="s">
-        <v>122</v>
+      <c r="B5" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>126</v>
+        <v>196</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>129</v>
+        <v>198</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="38" t="s">
-        <v>122</v>
+      <c r="B6" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>15</v>
@@ -4329,567 +5105,567 @@
       <c r="E6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="42" t="s">
-        <v>131</v>
+      <c r="F6" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>134</v>
+        <v>203</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>122</v>
+      <c r="B7" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>131</v>
+        <v>208</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>140</v>
+        <v>209</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>122</v>
+      <c r="B8" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>126</v>
+        <v>213</v>
+      </c>
+      <c r="F8" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G8" s="18"/>
-      <c r="H8" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>129</v>
+      <c r="H8" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>122</v>
+      <c r="B9" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>126</v>
+        <v>216</v>
+      </c>
+      <c r="F9" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G9" s="18"/>
-      <c r="H9" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>129</v>
+      <c r="H9" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>122</v>
+      <c r="B10" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>126</v>
+        <v>218</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G10" s="18"/>
-      <c r="H10" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>129</v>
+      <c r="H10" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>122</v>
+      <c r="B11" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>131</v>
+        <v>221</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>134</v>
+        <v>222</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>122</v>
+      <c r="B12" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>131</v>
+        <v>224</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>156</v>
+        <v>225</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>157</v>
+      <c r="B13" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>131</v>
+        <v>231</v>
+      </c>
+      <c r="F13" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>163</v>
+        <v>232</v>
+      </c>
+      <c r="H13" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>157</v>
+      <c r="B14" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>165</v>
+        <v>236</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="F14" s="42" t="s">
-        <v>131</v>
+        <v>237</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>163</v>
+        <v>238</v>
+      </c>
+      <c r="H14" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="38" t="s">
-        <v>157</v>
+      <c r="B15" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>169</v>
+        <v>240</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>171</v>
+        <v>241</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>163</v>
+        <v>243</v>
+      </c>
+      <c r="H15" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" s="58" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>157</v>
+      <c r="B16" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>126</v>
+        <v>245</v>
+      </c>
+      <c r="F16" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="H16" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="I16" s="41" t="s">
-        <v>163</v>
+        <v>246</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>157</v>
+      <c r="B17" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>126</v>
+        <v>249</v>
+      </c>
+      <c r="F17" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>179</v>
+      <c r="H17" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>157</v>
+      <c r="B18" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>126</v>
+        <v>253</v>
+      </c>
+      <c r="F18" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>185</v>
+        <v>254</v>
+      </c>
+      <c r="H18" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="38" t="s">
-        <v>157</v>
+      <c r="B19" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>186</v>
+        <v>257</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>126</v>
+        <v>258</v>
+      </c>
+      <c r="F19" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G19" s="18"/>
-      <c r="H19" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>189</v>
+      <c r="H19" s="57" t="s">
+        <v>259</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>157</v>
+      <c r="B20" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>126</v>
+        <v>262</v>
+      </c>
+      <c r="F20" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="I20" s="41" t="s">
-        <v>189</v>
+      <c r="H20" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="38" t="s">
-        <v>193</v>
+      <c r="B21" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="F21" s="43" t="s">
-        <v>171</v>
+        <v>267</v>
+      </c>
+      <c r="F21" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>199</v>
+        <v>268</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>193</v>
+      <c r="B22" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>131</v>
+        <v>272</v>
+      </c>
+      <c r="F22" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>204</v>
+        <v>273</v>
+      </c>
+      <c r="H22" s="55" t="s">
+        <v>274</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="38" t="s">
-        <v>193</v>
+      <c r="B23" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>131</v>
+        <v>277</v>
+      </c>
+      <c r="F23" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="I23" s="41" t="s">
-        <v>204</v>
+        <v>278</v>
+      </c>
+      <c r="H23" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>193</v>
+      <c r="B24" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>171</v>
+        <v>282</v>
+      </c>
+      <c r="F24" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="I24" s="41" t="s">
-        <v>215</v>
+        <v>283</v>
+      </c>
+      <c r="H24" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="38" t="s">
-        <v>193</v>
+      <c r="B25" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>126</v>
+        <v>288</v>
+      </c>
+      <c r="F25" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="I25" s="41" t="s">
-        <v>221</v>
+        <v>289</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>193</v>
+      <c r="B26" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>35</v>
@@ -4897,720 +5673,720 @@
       <c r="E26" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="42" t="s">
-        <v>131</v>
+      <c r="F26" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="I26" s="41" t="s">
-        <v>225</v>
+        <v>293</v>
+      </c>
+      <c r="H26" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>193</v>
+      <c r="B27" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>226</v>
+        <v>296</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>126</v>
+        <v>297</v>
+      </c>
+      <c r="F27" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G27" s="18"/>
-      <c r="H27" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="I27" s="41" t="s">
-        <v>229</v>
+      <c r="H27" s="57" t="s">
+        <v>298</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>193</v>
+      <c r="B28" s="55" t="s">
+        <v>264</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>126</v>
+        <v>297</v>
+      </c>
+      <c r="F28" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G28" s="18"/>
-      <c r="H28" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="I28" s="41" t="s">
-        <v>232</v>
+      <c r="H28" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="38" t="s">
-        <v>233</v>
+      <c r="B29" s="55" t="s">
+        <v>303</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>235</v>
+        <v>305</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>126</v>
+        <v>306</v>
+      </c>
+      <c r="F29" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="I29" s="41" t="s">
-        <v>239</v>
+        <v>307</v>
+      </c>
+      <c r="H29" s="55" t="s">
+        <v>308</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="38" t="s">
-        <v>233</v>
+      <c r="B30" s="55" t="s">
+        <v>303</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="F30" s="43" t="s">
-        <v>171</v>
+        <v>311</v>
+      </c>
+      <c r="F30" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G30" s="18"/>
-      <c r="H30" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>243</v>
+      <c r="H30" s="57" t="s">
+        <v>312</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="38" t="s">
-        <v>233</v>
+      <c r="B31" s="55" t="s">
+        <v>303</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="F31" s="42" t="s">
-        <v>131</v>
+        <v>315</v>
+      </c>
+      <c r="F31" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="I31" s="41" t="s">
-        <v>243</v>
+        <v>316</v>
+      </c>
+      <c r="H31" s="55" t="s">
+        <v>317</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>233</v>
+      <c r="B32" s="55" t="s">
+        <v>303</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>248</v>
+        <v>318</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>126</v>
+        <v>319</v>
+      </c>
+      <c r="F32" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G32" s="18"/>
-      <c r="H32" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="I32" s="41" t="s">
-        <v>243</v>
+      <c r="H32" s="57" t="s">
+        <v>312</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>250</v>
+      <c r="B33" s="55" t="s">
+        <v>320</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>252</v>
+        <v>322</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>126</v>
+        <v>322</v>
+      </c>
+      <c r="F33" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G33" s="18"/>
-      <c r="H33" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="I33" s="41" t="s">
-        <v>254</v>
+      <c r="H33" s="55" t="s">
+        <v>323</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>250</v>
+      <c r="B34" s="55" t="s">
+        <v>320</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="F34" s="42" t="s">
-        <v>131</v>
+        <v>327</v>
+      </c>
+      <c r="F34" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="H34" s="40" t="s">
-        <v>259</v>
-      </c>
-      <c r="I34" s="41" t="s">
-        <v>260</v>
+        <v>328</v>
+      </c>
+      <c r="H34" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="38" t="s">
-        <v>250</v>
+      <c r="B35" s="55" t="s">
+        <v>320</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="F35" s="43" t="s">
-        <v>171</v>
+        <v>333</v>
+      </c>
+      <c r="F35" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G35" s="18"/>
-      <c r="H35" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="I35" s="41" t="s">
-        <v>265</v>
+      <c r="H35" s="57" t="s">
+        <v>334</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>250</v>
+      <c r="B36" s="55" t="s">
+        <v>320</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="F36" s="43" t="s">
-        <v>171</v>
+        <v>338</v>
+      </c>
+      <c r="F36" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="H36" s="40" t="s">
-        <v>259</v>
-      </c>
-      <c r="I36" s="41" t="s">
-        <v>260</v>
+        <v>339</v>
+      </c>
+      <c r="H36" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="38" t="s">
-        <v>250</v>
+      <c r="B37" s="55" t="s">
+        <v>320</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="43" t="s">
-        <v>171</v>
+      <c r="F37" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G37" s="18"/>
-      <c r="H37" s="40" t="s">
-        <v>272</v>
-      </c>
-      <c r="I37" s="41" t="s">
-        <v>273</v>
+      <c r="H37" s="57" t="s">
+        <v>342</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="38" t="s">
-        <v>250</v>
+      <c r="B38" s="55" t="s">
+        <v>320</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>275</v>
+        <v>345</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="42" t="s">
-        <v>131</v>
+      <c r="F38" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="H38" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="I38" s="41" t="s">
-        <v>278</v>
+        <v>346</v>
+      </c>
+      <c r="H38" s="55" t="s">
+        <v>347</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="38" t="s">
+      <c r="B39" s="55" t="s">
         <v>54</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>279</v>
+        <v>349</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>131</v>
+        <v>351</v>
+      </c>
+      <c r="F39" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="H39" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="I39" s="41" t="s">
-        <v>284</v>
+        <v>352</v>
+      </c>
+      <c r="H39" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="55" t="s">
         <v>54</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>285</v>
+        <v>355</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>131</v>
+        <v>357</v>
+      </c>
+      <c r="F40" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G40" s="18"/>
-      <c r="H40" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="I40" s="41" t="s">
-        <v>289</v>
+      <c r="H40" s="57" t="s">
+        <v>358</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="38" t="s">
+      <c r="B41" s="55" t="s">
         <v>54</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>291</v>
+        <v>361</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="F41" s="42" t="s">
-        <v>131</v>
+        <v>362</v>
+      </c>
+      <c r="F41" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G41" s="18"/>
-      <c r="H41" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="I41" s="41" t="s">
-        <v>294</v>
+      <c r="H41" s="55" t="s">
+        <v>363</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="55" t="s">
         <v>54</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>296</v>
+        <v>366</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>131</v>
+        <v>367</v>
+      </c>
+      <c r="F42" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G42" s="18"/>
-      <c r="H42" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="I42" s="41" t="s">
-        <v>299</v>
+      <c r="H42" s="55" t="s">
+        <v>368</v>
+      </c>
+      <c r="I42" s="58" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="38" t="s">
+      <c r="B43" s="55" t="s">
         <v>54</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="F43" s="42" t="s">
-        <v>131</v>
+        <v>372</v>
+      </c>
+      <c r="F43" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G43" s="18"/>
-      <c r="H43" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="I43" s="41" t="s">
-        <v>304</v>
+      <c r="H43" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="I43" s="58" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="55" t="s">
         <v>54</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>305</v>
+        <v>375</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="F44" s="42" t="s">
-        <v>131</v>
+        <v>377</v>
+      </c>
+      <c r="F44" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="H44" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="I44" s="41" t="s">
-        <v>310</v>
+        <v>378</v>
+      </c>
+      <c r="H44" s="55" t="s">
+        <v>379</v>
+      </c>
+      <c r="I44" s="58" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="38" t="s">
-        <v>311</v>
+      <c r="B45" s="55" t="s">
+        <v>381</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>312</v>
+        <v>382</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>313</v>
+        <v>383</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>126</v>
+        <v>383</v>
+      </c>
+      <c r="F45" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G45" s="18"/>
-      <c r="H45" s="40" t="s">
-        <v>314</v>
+      <c r="H45" s="57" t="s">
+        <v>384</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>315</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="38" t="s">
-        <v>311</v>
+      <c r="B46" s="55" t="s">
+        <v>381</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>316</v>
+        <v>386</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>317</v>
+        <v>387</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="F46" s="39" t="s">
-        <v>126</v>
+        <v>387</v>
+      </c>
+      <c r="F46" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G46" s="18"/>
-      <c r="H46" s="40" t="s">
-        <v>318</v>
+      <c r="H46" s="57" t="s">
+        <v>388</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>319</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="38" t="s">
-        <v>311</v>
+      <c r="B47" s="55" t="s">
+        <v>381</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>126</v>
+        <v>391</v>
+      </c>
+      <c r="F47" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G47" s="18"/>
-      <c r="H47" s="38" t="s">
-        <v>322</v>
+      <c r="H47" s="55" t="s">
+        <v>392</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>323</v>
+        <v>393</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="38" t="s">
-        <v>311</v>
+      <c r="B48" s="55" t="s">
+        <v>381</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>324</v>
+        <v>394</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>325</v>
+        <v>395</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="F48" s="42" t="s">
-        <v>131</v>
+        <v>396</v>
+      </c>
+      <c r="F48" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="H48" s="38" t="s">
-        <v>328</v>
-      </c>
-      <c r="I48" s="41" t="s">
-        <v>329</v>
+        <v>397</v>
+      </c>
+      <c r="H48" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="I48" s="58" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="38" t="s">
-        <v>311</v>
+      <c r="B49" s="55" t="s">
+        <v>381</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="F49" s="42" t="s">
-        <v>131</v>
+        <v>402</v>
+      </c>
+      <c r="F49" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="H49" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="I49" s="41" t="s">
-        <v>335</v>
+        <v>403</v>
+      </c>
+      <c r="H49" s="55" t="s">
+        <v>404</v>
+      </c>
+      <c r="I49" s="58" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="38" t="s">
-        <v>311</v>
+      <c r="B50" s="55" t="s">
+        <v>381</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F50" s="39" t="s">
-        <v>126</v>
+        <v>218</v>
+      </c>
+      <c r="F50" s="56" t="s">
+        <v>197</v>
       </c>
       <c r="G50" s="18"/>
-      <c r="H50" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="I50" s="41" t="s">
-        <v>338</v>
+      <c r="H50" s="57" t="s">
+        <v>407</v>
+      </c>
+      <c r="I50" s="58" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="32" t="s">
-        <v>339</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="D53" s="45" t="str">
+      <c r="C53" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="62" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C53)&amp;" 項目"</f>
         <v>20 項目</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="D54" s="45" t="str">
+      <c r="C54" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="D54" s="62" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C54)&amp;" 項目"</f>
         <v>7 項目</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="45" t="str">
+      <c r="C55" s="64" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" s="62" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C55)&amp;" 項目"</f>
         <v>19 項目</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="35" t="s">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="B57" s="35"/>
       <c r="C57" s="35"/>
@@ -5638,7 +6414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF548235"/>
@@ -5654,23 +6430,23 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="48" t="s">
-        <v>341</v>
+      <c r="B2" s="36" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="49" t="s">
-        <v>343</v>
+      <c r="B4" s="65" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -5681,36 +6457,36 @@
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="50" t="s">
-        <v>345</v>
-      </c>
-      <c r="C7" s="51" t="n">
+      <c r="B7" s="66" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="67" t="n">
         <v>24</v>
       </c>
-      <c r="D7" s="52" t="s">
-        <v>346</v>
+      <c r="D7" s="68" t="s">
+        <v>416</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>347</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="51" t="n">
+      <c r="B8" s="66" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" s="67" t="n">
         <v>235</v>
       </c>
-      <c r="D8" s="52" t="s">
-        <v>346</v>
+      <c r="D8" s="68" t="s">
+        <v>416</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>349</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -5728,13 +6504,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>351</v>
+        <v>421</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>352</v>
+        <v>422</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>353</v>
+        <v>423</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -5742,143 +6518,143 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="C12" s="53" t="n">
+        <v>424</v>
+      </c>
+      <c r="C12" s="69" t="n">
         <f aca="false">$C$7/4</f>
         <v>6</v>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="70" t="n">
         <f aca="false">$C$7/4</f>
         <v>6</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="70" t="n">
         <f aca="false">$C$7/4.5</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F12" s="55" t="s">
-        <v>355</v>
-      </c>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
+      <c r="F12" s="71" t="s">
+        <v>425</v>
+      </c>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="C13" s="53" t="n">
+        <v>426</v>
+      </c>
+      <c r="C13" s="69" t="n">
         <f aca="false">2*C12</f>
         <v>12</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="70" t="n">
         <f aca="false">2*D12</f>
         <v>12</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="70" t="n">
         <f aca="false">2*E12</f>
         <v>10.6666666666667</v>
       </c>
-      <c r="F13" s="56" t="s">
-        <v>357</v>
-      </c>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
+      <c r="F13" s="72" t="s">
+        <v>427</v>
+      </c>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="D14" s="54" t="n">
+        <v>428</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="D14" s="70" t="n">
         <f aca="false">MIN($C$7/40,3/4*(0.49+$C$7/100))</f>
         <v>0.5475</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="70" t="n">
         <f aca="false">MIN($C$7/45,3/4*(0.49+$C$7/100))</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="F14" s="55" t="s">
-        <v>360</v>
-      </c>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
+      <c r="F14" s="71" t="s">
+        <v>430</v>
+      </c>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="D15" s="54" t="n">
+        <v>431</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="D15" s="70" t="n">
         <f aca="false">1.5*D14</f>
         <v>0.82125</v>
       </c>
-      <c r="E15" s="54" t="n">
+      <c r="E15" s="70" t="n">
         <f aca="false">1.5*E14</f>
         <v>0.8</v>
       </c>
-      <c r="F15" s="55" t="s">
-        <v>362</v>
-      </c>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
+      <c r="F15" s="71" t="s">
+        <v>432</v>
+      </c>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="58" t="s">
-        <v>363</v>
-      </c>
-      <c r="C16" s="59" t="n">
+      <c r="B16" s="74" t="s">
+        <v>433</v>
+      </c>
+      <c r="C16" s="75" t="n">
         <f aca="false">C12/C12</f>
         <v>1</v>
       </c>
-      <c r="D16" s="60" t="n">
+      <c r="D16" s="76" t="n">
         <f aca="false">D12/C12</f>
         <v>1</v>
       </c>
-      <c r="E16" s="60" t="n">
+      <c r="E16" s="76" t="n">
         <f aca="false">E12/C12</f>
         <v>0.888888888888889</v>
       </c>
-      <c r="F16" s="55" t="s">
-        <v>364</v>
-      </c>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
+      <c r="F16" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="58" t="s">
-        <v>365</v>
-      </c>
-      <c r="C17" s="61" t="str">
+      <c r="B17" s="74" t="s">
+        <v>435</v>
+      </c>
+      <c r="C17" s="77" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=45),"範囲内（18〜45）","範囲外：SS7は計算を続けるので要確認")</f>
         <v>範囲内（18〜45）</v>
       </c>
-      <c r="D17" s="62" t="str">
+      <c r="D17" s="78" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=36),"範囲内（18〜36）","範囲外：SS7がメッセージを出力")</f>
         <v>範囲内（18〜36）</v>
       </c>
-      <c r="E17" s="62" t="str">
+      <c r="E17" s="78" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=36),"範囲内（18〜36）","範囲外：SS7がメッセージを出力")</f>
         <v>範囲内（18〜36）</v>
       </c>
-      <c r="F17" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
+      <c r="F17" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>366</v>
+        <v>436</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -5893,13 +6669,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>367</v>
+        <v>437</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>353</v>
+        <v>423</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -5908,47 +6684,47 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="C21" s="63" t="n">
+        <v>439</v>
+      </c>
+      <c r="C21" s="79" t="n">
         <f aca="false">$C$8/1.5</f>
         <v>156.666666666667</v>
       </c>
-      <c r="D21" s="63" t="n">
+      <c r="D21" s="79" t="n">
         <f aca="false">1.5*C21</f>
         <v>235</v>
       </c>
-      <c r="E21" s="64" t="s">
-        <v>370</v>
-      </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
+      <c r="E21" s="80" t="s">
+        <v>440</v>
+      </c>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="C22" s="63" t="n">
+        <v>441</v>
+      </c>
+      <c r="C22" s="79" t="n">
         <f aca="false">$C$8/(1.5*SQRT(3))</f>
         <v>90.4515421730414</v>
       </c>
-      <c r="D22" s="63" t="n">
+      <c r="D22" s="79" t="n">
         <f aca="false">1.5*C22</f>
         <v>135.677313259562</v>
       </c>
-      <c r="E22" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
+      <c r="E22" s="80" t="s">
+        <v>442</v>
+      </c>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="65" t="s">
-        <v>373</v>
+      <c r="B24" s="81" t="s">
+        <v>443</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -5960,330 +6736,330 @@
     </row>
     <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>374</v>
+        <v>444</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>375</v>
+        <v>445</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>377</v>
+        <v>447</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>378</v>
+        <v>448</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>379</v>
+        <v>449</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>381</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="66" t="n">
+      <c r="B26" s="82" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="83" t="n">
         <f aca="false">B26/4</f>
         <v>4.5</v>
       </c>
-      <c r="D26" s="68" t="n">
+      <c r="D26" s="84" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",B26/4)</f>
         <v>4.5</v>
       </c>
-      <c r="E26" s="68" t="n">
+      <c r="E26" s="84" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",B26/4.5)</f>
         <v>4</v>
       </c>
-      <c r="F26" s="69" t="n">
+      <c r="F26" s="85" t="n">
         <f aca="false">IF(B26&gt;36,"—",C26-E26)</f>
         <v>0.5</v>
       </c>
-      <c r="G26" s="68" t="n">
+      <c r="G26" s="84" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",MIN(B26/40,3/4*(0.49+B26/100)))</f>
         <v>0.45</v>
       </c>
-      <c r="H26" s="68" t="n">
+      <c r="H26" s="84" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",MIN(B26/45,3/4*(0.49+B26/100)))</f>
         <v>0.4</v>
       </c>
-      <c r="I26" s="70" t="str">
+      <c r="I26" s="86" t="str">
         <f aca="false">IF(B26&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B26/40&lt;=3/4*(0.49+B26/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B26/45&lt;=3/4*(0.49+B26/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：Fc/40　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="66" t="n">
+      <c r="B27" s="82" t="n">
         <v>21</v>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="83" t="n">
         <f aca="false">B27/4</f>
         <v>5.25</v>
       </c>
-      <c r="D27" s="68" t="n">
+      <c r="D27" s="84" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",B27/4)</f>
         <v>5.25</v>
       </c>
-      <c r="E27" s="68" t="n">
+      <c r="E27" s="84" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",B27/4.5)</f>
         <v>4.66666666666667</v>
       </c>
-      <c r="F27" s="69" t="n">
+      <c r="F27" s="85" t="n">
         <f aca="false">IF(B27&gt;36,"—",C27-E27)</f>
         <v>0.583333333333333</v>
       </c>
-      <c r="G27" s="68" t="n">
+      <c r="G27" s="84" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",MIN(B27/40,3/4*(0.49+B27/100)))</f>
         <v>0.525</v>
       </c>
-      <c r="H27" s="68" t="n">
+      <c r="H27" s="84" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",MIN(B27/45,3/4*(0.49+B27/100)))</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="I27" s="70" t="str">
+      <c r="I27" s="86" t="str">
         <f aca="false">IF(B27&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B27/40&lt;=3/4*(0.49+B27/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B27/45&lt;=3/4*(0.49+B27/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：Fc/40　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="66" t="n">
+      <c r="B28" s="82" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="67" t="n">
+      <c r="C28" s="83" t="n">
         <f aca="false">B28/4</f>
         <v>6</v>
       </c>
-      <c r="D28" s="68" t="n">
+      <c r="D28" s="84" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",B28/4)</f>
         <v>6</v>
       </c>
-      <c r="E28" s="68" t="n">
+      <c r="E28" s="84" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",B28/4.5)</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F28" s="69" t="n">
+      <c r="F28" s="85" t="n">
         <f aca="false">IF(B28&gt;36,"—",C28-E28)</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="G28" s="68" t="n">
+      <c r="G28" s="84" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",MIN(B28/40,3/4*(0.49+B28/100)))</f>
         <v>0.5475</v>
       </c>
-      <c r="H28" s="68" t="n">
+      <c r="H28" s="84" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",MIN(B28/45,3/4*(0.49+B28/100)))</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="I28" s="70" t="str">
+      <c r="I28" s="86" t="str">
         <f aca="false">IF(B28&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B28/40&lt;=3/4*(0.49+B28/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B28/45&lt;=3/4*(0.49+B28/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="66" t="n">
+      <c r="B29" s="82" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="67" t="n">
+      <c r="C29" s="83" t="n">
         <f aca="false">B29/4</f>
         <v>6.75</v>
       </c>
-      <c r="D29" s="68" t="n">
+      <c r="D29" s="84" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",B29/4)</f>
         <v>6.75</v>
       </c>
-      <c r="E29" s="68" t="n">
+      <c r="E29" s="84" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",B29/4.5)</f>
         <v>6</v>
       </c>
-      <c r="F29" s="69" t="n">
+      <c r="F29" s="85" t="n">
         <f aca="false">IF(B29&gt;36,"—",C29-E29)</f>
         <v>0.75</v>
       </c>
-      <c r="G29" s="68" t="n">
+      <c r="G29" s="84" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",MIN(B29/40,3/4*(0.49+B29/100)))</f>
         <v>0.57</v>
       </c>
-      <c r="H29" s="68" t="n">
+      <c r="H29" s="84" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",MIN(B29/45,3/4*(0.49+B29/100)))</f>
         <v>0.57</v>
       </c>
-      <c r="I29" s="70" t="str">
+      <c r="I29" s="86" t="str">
         <f aca="false">IF(B29&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B29/40&lt;=3/4*(0.49+B29/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B29/45&lt;=3/4*(0.49+B29/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="66" t="n">
+      <c r="B30" s="82" t="n">
         <v>30</v>
       </c>
-      <c r="C30" s="67" t="n">
+      <c r="C30" s="83" t="n">
         <f aca="false">B30/4</f>
         <v>7.5</v>
       </c>
-      <c r="D30" s="68" t="n">
+      <c r="D30" s="84" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",B30/4)</f>
         <v>7.5</v>
       </c>
-      <c r="E30" s="68" t="n">
+      <c r="E30" s="84" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",B30/4.5)</f>
         <v>6.66666666666667</v>
       </c>
-      <c r="F30" s="69" t="n">
+      <c r="F30" s="85" t="n">
         <f aca="false">IF(B30&gt;36,"—",C30-E30)</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G30" s="68" t="n">
+      <c r="G30" s="84" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",MIN(B30/40,3/4*(0.49+B30/100)))</f>
         <v>0.5925</v>
       </c>
-      <c r="H30" s="68" t="n">
+      <c r="H30" s="84" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",MIN(B30/45,3/4*(0.49+B30/100)))</f>
         <v>0.5925</v>
       </c>
-      <c r="I30" s="70" t="str">
+      <c r="I30" s="86" t="str">
         <f aca="false">IF(B30&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B30/40&lt;=3/4*(0.49+B30/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B30/45&lt;=3/4*(0.49+B30/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="66" t="n">
+      <c r="B31" s="82" t="n">
         <v>33</v>
       </c>
-      <c r="C31" s="67" t="n">
+      <c r="C31" s="83" t="n">
         <f aca="false">B31/4</f>
         <v>8.25</v>
       </c>
-      <c r="D31" s="68" t="n">
+      <c r="D31" s="84" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",B31/4)</f>
         <v>8.25</v>
       </c>
-      <c r="E31" s="68" t="n">
+      <c r="E31" s="84" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",B31/4.5)</f>
         <v>7.33333333333333</v>
       </c>
-      <c r="F31" s="69" t="n">
+      <c r="F31" s="85" t="n">
         <f aca="false">IF(B31&gt;36,"—",C31-E31)</f>
         <v>0.916666666666667</v>
       </c>
-      <c r="G31" s="68" t="n">
+      <c r="G31" s="84" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",MIN(B31/40,3/4*(0.49+B31/100)))</f>
         <v>0.615</v>
       </c>
-      <c r="H31" s="68" t="n">
+      <c r="H31" s="84" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",MIN(B31/45,3/4*(0.49+B31/100)))</f>
         <v>0.615</v>
       </c>
-      <c r="I31" s="70" t="str">
+      <c r="I31" s="86" t="str">
         <f aca="false">IF(B31&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B31/40&lt;=3/4*(0.49+B31/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B31/45&lt;=3/4*(0.49+B31/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="66" t="n">
+      <c r="B32" s="82" t="n">
         <v>36</v>
       </c>
-      <c r="C32" s="67" t="n">
+      <c r="C32" s="83" t="n">
         <f aca="false">B32/4</f>
         <v>9</v>
       </c>
-      <c r="D32" s="68" t="n">
+      <c r="D32" s="84" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",B32/4)</f>
         <v>9</v>
       </c>
-      <c r="E32" s="68" t="n">
+      <c r="E32" s="84" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",B32/4.5)</f>
         <v>8</v>
       </c>
-      <c r="F32" s="69" t="n">
+      <c r="F32" s="85" t="n">
         <f aca="false">IF(B32&gt;36,"—",C32-E32)</f>
         <v>1</v>
       </c>
-      <c r="G32" s="68" t="n">
+      <c r="G32" s="84" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",MIN(B32/40,3/4*(0.49+B32/100)))</f>
         <v>0.6375</v>
       </c>
-      <c r="H32" s="68" t="n">
+      <c r="H32" s="84" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",MIN(B32/45,3/4*(0.49+B32/100)))</f>
         <v>0.6375</v>
       </c>
-      <c r="I32" s="70" t="str">
+      <c r="I32" s="86" t="str">
         <f aca="false">IF(B32&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B32/40&lt;=3/4*(0.49+B32/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B32/45&lt;=3/4*(0.49+B32/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="66" t="n">
+      <c r="B33" s="82" t="n">
         <v>40</v>
       </c>
-      <c r="C33" s="67" t="n">
+      <c r="C33" s="83" t="n">
         <f aca="false">B33/4</f>
         <v>10</v>
       </c>
-      <c r="D33" s="68" t="str">
+      <c r="D33" s="84" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",B33/4)</f>
         <v>範囲外</v>
       </c>
-      <c r="E33" s="68" t="str">
+      <c r="E33" s="84" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",B33/4.5)</f>
         <v>範囲外</v>
       </c>
-      <c r="F33" s="69" t="str">
+      <c r="F33" s="85" t="str">
         <f aca="false">IF(B33&gt;36,"—",C33-E33)</f>
         <v>—</v>
       </c>
-      <c r="G33" s="68" t="str">
+      <c r="G33" s="84" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",MIN(B33/40,3/4*(0.49+B33/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="H33" s="68" t="str">
+      <c r="H33" s="84" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",MIN(B33/45,3/4*(0.49+B33/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="I33" s="70" t="str">
+      <c r="I33" s="86" t="str">
         <f aca="false">IF(B33&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B33/40&lt;=3/4*(0.49+B33/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B33/45&lt;=3/4*(0.49+B33/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>SB協会の範囲外（Fc＞36）</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="66" t="n">
+      <c r="B34" s="82" t="n">
         <v>45</v>
       </c>
-      <c r="C34" s="67" t="n">
+      <c r="C34" s="83" t="n">
         <f aca="false">B34/4</f>
         <v>11.25</v>
       </c>
-      <c r="D34" s="68" t="str">
+      <c r="D34" s="84" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",B34/4)</f>
         <v>範囲外</v>
       </c>
-      <c r="E34" s="68" t="str">
+      <c r="E34" s="84" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",B34/4.5)</f>
         <v>範囲外</v>
       </c>
-      <c r="F34" s="69" t="str">
+      <c r="F34" s="85" t="str">
         <f aca="false">IF(B34&gt;36,"—",C34-E34)</f>
         <v>—</v>
       </c>
-      <c r="G34" s="68" t="str">
+      <c r="G34" s="84" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",MIN(B34/40,3/4*(0.49+B34/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="H34" s="68" t="str">
+      <c r="H34" s="84" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",MIN(B34/45,3/4*(0.49+B34/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="I34" s="70" t="str">
+      <c r="I34" s="86" t="str">
         <f aca="false">IF(B34&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B34/40&lt;=3/4*(0.49+B34/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B34/45&lt;=3/4*(0.49+B34/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>SB協会の範囲外（Fc＞36）</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>382</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -6319,7 +7095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF548235"/>
@@ -6337,23 +7113,23 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="48" t="s">
-        <v>383</v>
+      <c r="B2" s="36" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>384</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="49" t="s">
-        <v>385</v>
+      <c r="B4" s="65" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -6362,126 +7138,126 @@
       <c r="G6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="50" t="s">
-        <v>386</v>
-      </c>
-      <c r="C7" s="71" t="n">
+      <c r="B7" s="66" t="s">
+        <v>456</v>
+      </c>
+      <c r="C7" s="87" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="F7" s="72" t="s">
-        <v>388</v>
-      </c>
-      <c r="G7" s="72"/>
+      <c r="D7" s="68" t="s">
+        <v>457</v>
+      </c>
+      <c r="F7" s="88" t="s">
+        <v>458</v>
+      </c>
+      <c r="G7" s="88"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="50" t="s">
-        <v>389</v>
-      </c>
-      <c r="C8" s="71" t="n">
+      <c r="B8" s="66" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="D8" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="F8" s="72" t="s">
-        <v>388</v>
-      </c>
-      <c r="G8" s="72"/>
+      <c r="D8" s="68" t="s">
+        <v>457</v>
+      </c>
+      <c r="F8" s="88" t="s">
+        <v>458</v>
+      </c>
+      <c r="G8" s="88"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="50" t="s">
-        <v>390</v>
-      </c>
-      <c r="C9" s="73" t="n">
+      <c r="B9" s="66" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="F9" s="72" t="s">
-        <v>391</v>
-      </c>
-      <c r="G9" s="72"/>
+      <c r="D9" s="68" t="s">
+        <v>457</v>
+      </c>
+      <c r="F9" s="88" t="s">
+        <v>461</v>
+      </c>
+      <c r="G9" s="88"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="C10" s="71" t="n">
+      <c r="B10" s="66" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10" s="87" t="n">
         <v>235</v>
       </c>
-      <c r="D10" s="52" t="s">
-        <v>346</v>
-      </c>
-      <c r="F10" s="72" t="s">
-        <v>392</v>
-      </c>
-      <c r="G10" s="72"/>
+      <c r="D10" s="68" t="s">
+        <v>416</v>
+      </c>
+      <c r="F10" s="88" t="s">
+        <v>462</v>
+      </c>
+      <c r="G10" s="88"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="50" t="s">
-        <v>393</v>
-      </c>
-      <c r="C11" s="73" t="n">
+      <c r="B11" s="66" t="s">
+        <v>463</v>
+      </c>
+      <c r="C11" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="74" t="s">
-        <v>394</v>
-      </c>
-      <c r="F11" s="72" t="s">
-        <v>395</v>
-      </c>
-      <c r="G11" s="72"/>
+      <c r="D11" s="90" t="s">
+        <v>464</v>
+      </c>
+      <c r="F11" s="88" t="s">
+        <v>465</v>
+      </c>
+      <c r="G11" s="88"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="50" t="s">
-        <v>396</v>
-      </c>
-      <c r="C12" s="71" t="n">
+      <c r="B12" s="66" t="s">
+        <v>466</v>
+      </c>
+      <c r="C12" s="87" t="n">
         <v>24</v>
       </c>
-      <c r="D12" s="52" t="s">
-        <v>346</v>
-      </c>
-      <c r="F12" s="72" t="s">
-        <v>397</v>
-      </c>
-      <c r="G12" s="72"/>
+      <c r="D12" s="68" t="s">
+        <v>416</v>
+      </c>
+      <c r="F12" s="88" t="s">
+        <v>467</v>
+      </c>
+      <c r="G12" s="88"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="50" t="s">
-        <v>398</v>
-      </c>
-      <c r="C13" s="71" t="n">
+      <c r="B13" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="C13" s="87" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="F13" s="72" t="s">
-        <v>397</v>
-      </c>
-      <c r="G13" s="72"/>
+      <c r="D13" s="68" t="s">
+        <v>457</v>
+      </c>
+      <c r="F13" s="88" t="s">
+        <v>467</v>
+      </c>
+      <c r="G13" s="88"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="75" t="s">
-        <v>399</v>
-      </c>
-      <c r="C14" s="73" t="n">
+      <c r="B14" s="91" t="s">
+        <v>469</v>
+      </c>
+      <c r="C14" s="89" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="F14" s="76" t="s">
-        <v>400</v>
-      </c>
-      <c r="G14" s="76"/>
+      <c r="D14" s="68"/>
+      <c r="F14" s="92" t="s">
+        <v>470</v>
+      </c>
+      <c r="G14" s="92"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>401</v>
+        <v>471</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -6494,10 +7270,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>402</v>
+        <v>472</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>403</v>
+        <v>473</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -6505,143 +7281,143 @@
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="27" t="s">
-        <v>404</v>
-      </c>
-      <c r="C17" s="77" t="n">
+        <v>474</v>
+      </c>
+      <c r="C17" s="93" t="n">
         <f aca="false">C7-2*C9</f>
         <v>1198</v>
       </c>
-      <c r="D17" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="E17" s="78" t="s">
-        <v>405</v>
-      </c>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
+      <c r="D17" s="62" t="s">
+        <v>457</v>
+      </c>
+      <c r="E17" s="94" t="s">
+        <v>475</v>
+      </c>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="C18" s="77" t="n">
+        <v>476</v>
+      </c>
+      <c r="C18" s="93" t="n">
         <f aca="false">C8-C9</f>
         <v>15</v>
       </c>
-      <c r="D18" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="E18" s="78" t="s">
-        <v>407</v>
-      </c>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
+      <c r="D18" s="62" t="s">
+        <v>457</v>
+      </c>
+      <c r="E18" s="94" t="s">
+        <v>477</v>
+      </c>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="27" t="s">
-        <v>408</v>
-      </c>
-      <c r="C19" s="77" t="n">
+        <v>478</v>
+      </c>
+      <c r="C19" s="93" t="n">
         <f aca="false">C17-2*C18</f>
         <v>1168</v>
       </c>
-      <c r="D19" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="E19" s="78" t="s">
-        <v>409</v>
-      </c>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
+      <c r="D19" s="62" t="s">
+        <v>457</v>
+      </c>
+      <c r="E19" s="94" t="s">
+        <v>479</v>
+      </c>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="27" t="s">
-        <v>410</v>
-      </c>
-      <c r="C20" s="79" t="n">
+        <v>480</v>
+      </c>
+      <c r="C20" s="95" t="n">
         <f aca="false">PI()/4*(C17^2-C19^2)</f>
         <v>55747.5616379509</v>
       </c>
-      <c r="D20" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E20" s="78" t="s">
-        <v>412</v>
-      </c>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
+      <c r="D20" s="62" t="s">
+        <v>481</v>
+      </c>
+      <c r="E20" s="94" t="s">
+        <v>482</v>
+      </c>
+      <c r="F20" s="94"/>
+      <c r="G20" s="94"/>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="27" t="s">
-        <v>413</v>
-      </c>
-      <c r="C21" s="79" t="n">
+        <v>483</v>
+      </c>
+      <c r="C21" s="95" t="n">
         <f aca="false">PI()/32*(C17^4-C19^4)/C17</f>
         <v>16283523.0572836</v>
       </c>
-      <c r="D21" s="45" t="s">
-        <v>414</v>
-      </c>
-      <c r="E21" s="78" t="s">
-        <v>415</v>
-      </c>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
+      <c r="D21" s="62" t="s">
+        <v>484</v>
+      </c>
+      <c r="E21" s="94" t="s">
+        <v>485</v>
+      </c>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="27" t="s">
-        <v>416</v>
-      </c>
-      <c r="C22" s="80" t="n">
+        <v>486</v>
+      </c>
+      <c r="C22" s="96" t="n">
         <f aca="false">C10/1.5</f>
         <v>156.666666666667</v>
       </c>
-      <c r="D22" s="45" t="s">
-        <v>346</v>
-      </c>
-      <c r="E22" s="78" t="s">
-        <v>417</v>
-      </c>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
+      <c r="D22" s="62" t="s">
+        <v>416</v>
+      </c>
+      <c r="E22" s="94" t="s">
+        <v>487</v>
+      </c>
+      <c r="F22" s="94"/>
+      <c r="G22" s="94"/>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="27" t="s">
-        <v>418</v>
-      </c>
-      <c r="C23" s="80" t="n">
+        <v>488</v>
+      </c>
+      <c r="C23" s="96" t="n">
         <f aca="false">C10/(1.5*SQRT(3))</f>
         <v>90.4515421730414</v>
       </c>
-      <c r="D23" s="45" t="s">
-        <v>346</v>
-      </c>
-      <c r="E23" s="78" t="s">
-        <v>419</v>
-      </c>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
+      <c r="D23" s="62" t="s">
+        <v>416</v>
+      </c>
+      <c r="E23" s="94" t="s">
+        <v>489</v>
+      </c>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="C24" s="80" t="n">
+        <v>490</v>
+      </c>
+      <c r="C24" s="96" t="n">
         <f aca="false">C10*C11</f>
         <v>235</v>
       </c>
-      <c r="D24" s="45" t="s">
-        <v>346</v>
-      </c>
-      <c r="E24" s="78" t="s">
-        <v>421</v>
-      </c>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
+      <c r="D24" s="62" t="s">
+        <v>416</v>
+      </c>
+      <c r="E24" s="94" t="s">
+        <v>491</v>
+      </c>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>422</v>
+        <v>492</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -6660,233 +7436,233 @@
         <v>11</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>403</v>
+        <v>473</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>423</v>
+        <v>493</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>424</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="24" t="s">
-        <v>425</v>
-      </c>
-      <c r="C28" s="81" t="n">
+        <v>495</v>
+      </c>
+      <c r="C28" s="97" t="n">
         <f aca="false">C21*C22/1000000</f>
         <v>2551.08527897442</v>
       </c>
-      <c r="D28" s="82" t="n">
+      <c r="D28" s="98" t="n">
         <f aca="false">C21*C22/1000000</f>
         <v>2551.08527897442</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="F28" s="55" t="s">
-        <v>427</v>
-      </c>
-      <c r="G28" s="55" t="s">
-        <v>428</v>
+        <v>496</v>
+      </c>
+      <c r="F28" s="71" t="s">
+        <v>497</v>
+      </c>
+      <c r="G28" s="71" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="24" t="s">
-        <v>429</v>
-      </c>
-      <c r="C29" s="81" t="n">
+        <v>499</v>
+      </c>
+      <c r="C29" s="97" t="n">
         <f aca="false">1.5*C28</f>
         <v>3826.62791846163</v>
       </c>
-      <c r="D29" s="82" t="n">
+      <c r="D29" s="98" t="n">
         <f aca="false">1.5*D28</f>
         <v>3826.62791846163</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="F29" s="56" t="s">
-        <v>430</v>
-      </c>
-      <c r="G29" s="56" t="s">
-        <v>431</v>
+        <v>496</v>
+      </c>
+      <c r="F29" s="72" t="s">
+        <v>500</v>
+      </c>
+      <c r="G29" s="72" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>432</v>
-      </c>
-      <c r="C30" s="81" t="n">
+        <v>502</v>
+      </c>
+      <c r="C30" s="97" t="n">
         <f aca="false">C20/2*C23/1000</f>
         <v>2521.22646126967</v>
       </c>
-      <c r="D30" s="82" t="n">
+      <c r="D30" s="98" t="n">
         <f aca="false">C20/2*C23/1000</f>
         <v>2521.22646126967</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="F30" s="55" t="s">
-        <v>434</v>
-      </c>
-      <c r="G30" s="56" t="s">
-        <v>435</v>
+        <v>503</v>
+      </c>
+      <c r="F30" s="71" t="s">
+        <v>504</v>
+      </c>
+      <c r="G30" s="72" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="C31" s="81" t="n">
+        <v>505</v>
+      </c>
+      <c r="C31" s="97" t="n">
         <f aca="false">1.5*C30</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="D31" s="82" t="n">
+      <c r="D31" s="98" t="n">
         <f aca="false">1.5*D30</f>
         <v>3781.8396919045</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="F31" s="56" t="s">
-        <v>430</v>
-      </c>
-      <c r="G31" s="56" t="s">
-        <v>435</v>
+        <v>503</v>
+      </c>
+      <c r="F31" s="72" t="s">
+        <v>500</v>
+      </c>
+      <c r="G31" s="72" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="24" t="s">
-        <v>437</v>
-      </c>
-      <c r="C32" s="81" t="n">
+        <v>506</v>
+      </c>
+      <c r="C32" s="97" t="n">
         <f aca="false">C20/2*C24/SQRT(3)/1000</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="D32" s="82" t="n">
+      <c r="D32" s="98" t="n">
         <f aca="false">C20*(C24/SQRT(3))*(1/C14)/1000</f>
         <v>3781.8396919045</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="F32" s="55" t="s">
-        <v>438</v>
-      </c>
-      <c r="G32" s="55" t="s">
-        <v>439</v>
+        <v>503</v>
+      </c>
+      <c r="F32" s="71" t="s">
+        <v>507</v>
+      </c>
+      <c r="G32" s="71" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="24" t="s">
-        <v>440</v>
-      </c>
-      <c r="C33" s="81" t="n">
+        <v>509</v>
+      </c>
+      <c r="C33" s="97" t="n">
         <f aca="false">C12*C7*C13/1000</f>
         <v>2880</v>
       </c>
-      <c r="D33" s="83" t="s">
-        <v>359</v>
+      <c r="D33" s="99" t="s">
+        <v>429</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="F33" s="55" t="s">
-        <v>441</v>
-      </c>
-      <c r="G33" s="55" t="s">
-        <v>442</v>
+        <v>503</v>
+      </c>
+      <c r="F33" s="71" t="s">
+        <v>510</v>
+      </c>
+      <c r="G33" s="71" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="24" t="s">
-        <v>443</v>
-      </c>
-      <c r="C34" s="84" t="n">
+        <v>512</v>
+      </c>
+      <c r="C34" s="100" t="n">
         <f aca="false">MIN(C32,C33)</f>
         <v>2880</v>
       </c>
-      <c r="D34" s="85" t="n">
+      <c r="D34" s="101" t="n">
         <f aca="false">D32</f>
         <v>3781.8396919045</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="F34" s="55" t="s">
-        <v>444</v>
-      </c>
-      <c r="G34" s="56"/>
+        <v>503</v>
+      </c>
+      <c r="F34" s="71" t="s">
+        <v>513</v>
+      </c>
+      <c r="G34" s="72"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="58" t="s">
-        <v>445</v>
-      </c>
-      <c r="C35" s="81" t="str">
+      <c r="B35" s="74" t="s">
+        <v>514</v>
+      </c>
+      <c r="C35" s="97" t="str">
         <f aca="false">IF(C33&lt;C32,"杭頭接合部で決定","鋼管で決定")</f>
         <v>杭頭接合部で決定</v>
       </c>
-      <c r="D35" s="83" t="s">
-        <v>446</v>
+      <c r="D35" s="99" t="s">
+        <v>515</v>
       </c>
       <c r="E35" s="14"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="55" t="s">
-        <v>447</v>
+      <c r="F35" s="72"/>
+      <c r="G35" s="71" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="C36" s="86" t="s">
-        <v>449</v>
-      </c>
-      <c r="D36" s="82" t="n">
+        <v>517</v>
+      </c>
+      <c r="C36" s="102" t="s">
+        <v>518</v>
+      </c>
+      <c r="D36" s="98" t="n">
         <f aca="false">(C17-C18)^2*C18*C24/1000000</f>
         <v>4933.198725</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="F36" s="55" t="s">
-        <v>450</v>
-      </c>
-      <c r="G36" s="55" t="s">
-        <v>451</v>
+        <v>496</v>
+      </c>
+      <c r="F36" s="71" t="s">
+        <v>519</v>
+      </c>
+      <c r="G36" s="71" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="72" t="s">
-        <v>452</v>
-      </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
+      <c r="B38" s="88" t="s">
+        <v>521</v>
+      </c>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="88"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="76" t="s">
-        <v>453</v>
-      </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
+      <c r="B39" s="92" t="s">
+        <v>522</v>
+      </c>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="76" t="s">
-        <v>454</v>
-      </c>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
+      <c r="B40" s="92" t="s">
+        <v>523</v>
+      </c>
+      <c r="C40" s="92"/>
+      <c r="D40" s="92"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6926,7 +7702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFC65911"/>
@@ -6944,8 +7720,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
-        <v>455</v>
+      <c r="A1" s="36" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6954,8 +7730,8 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
-        <v>456</v>
+      <c r="A3" s="65" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6969,382 +7745,382 @@
         <v>8</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>457</v>
+        <v>526</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>458</v>
+        <v>527</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>459</v>
+        <v>528</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>460</v>
+        <v>529</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="87" t="s">
-        <v>462</v>
+      <c r="B6" s="103" t="s">
+        <v>531</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>463</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="88" t="s">
-        <v>464</v>
-      </c>
-      <c r="F6" s="89" t="s">
-        <v>465</v>
+        <v>532</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="104" t="s">
+        <v>533</v>
+      </c>
+      <c r="F6" s="105" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="87" t="s">
-        <v>462</v>
+      <c r="B7" s="103" t="s">
+        <v>531</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>466</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>467</v>
-      </c>
-      <c r="E7" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F7" s="89"/>
+        <v>535</v>
+      </c>
+      <c r="D7" s="71" t="s">
+        <v>536</v>
+      </c>
+      <c r="E7" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F7" s="105"/>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="87" t="s">
-        <v>462</v>
+      <c r="B8" s="103" t="s">
+        <v>531</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>469</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="E8" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F8" s="89"/>
+        <v>538</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F8" s="105"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="87" t="s">
-        <v>462</v>
+      <c r="B9" s="103" t="s">
+        <v>531</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>470</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>471</v>
-      </c>
-      <c r="E9" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F9" s="89"/>
+        <v>539</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>540</v>
+      </c>
+      <c r="E9" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F9" s="105"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="87" t="s">
-        <v>462</v>
+      <c r="B10" s="103" t="s">
+        <v>531</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>472</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F10" s="89"/>
+        <v>541</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F10" s="105"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="87" t="s">
-        <v>462</v>
+      <c r="B11" s="103" t="s">
+        <v>531</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F11" s="89"/>
+        <v>542</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>323</v>
+      </c>
+      <c r="E11" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F11" s="105"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="90" t="s">
-        <v>474</v>
+      <c r="B12" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>475</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>476</v>
-      </c>
-      <c r="E12" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F12" s="89"/>
+        <v>544</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>545</v>
+      </c>
+      <c r="E12" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F12" s="105"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="90" t="s">
-        <v>474</v>
+      <c r="B13" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>477</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>478</v>
-      </c>
-      <c r="E13" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F13" s="89"/>
+        <v>546</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>547</v>
+      </c>
+      <c r="E13" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F13" s="105"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="90" t="s">
-        <v>474</v>
+      <c r="B14" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>479</v>
-      </c>
-      <c r="D14" s="55" t="s">
-        <v>272</v>
-      </c>
-      <c r="E14" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F14" s="89"/>
+        <v>548</v>
+      </c>
+      <c r="D14" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="E14" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F14" s="105"/>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="90" t="s">
-        <v>474</v>
+      <c r="B15" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>480</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>481</v>
-      </c>
-      <c r="E15" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F15" s="89"/>
+        <v>549</v>
+      </c>
+      <c r="D15" s="71" t="s">
+        <v>550</v>
+      </c>
+      <c r="E15" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F15" s="105"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="90" t="s">
-        <v>474</v>
+      <c r="B16" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>482</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F16" s="89"/>
+        <v>551</v>
+      </c>
+      <c r="D16" s="72" t="s">
+        <v>347</v>
+      </c>
+      <c r="E16" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F16" s="105"/>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="90" t="s">
-        <v>474</v>
+      <c r="B17" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>483</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>484</v>
-      </c>
-      <c r="E17" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F17" s="89"/>
+        <v>552</v>
+      </c>
+      <c r="D17" s="72" t="s">
+        <v>553</v>
+      </c>
+      <c r="E17" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F17" s="105"/>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="91" t="s">
-        <v>485</v>
+      <c r="B18" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>486</v>
-      </c>
-      <c r="D18" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="E18" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F18" s="89"/>
+        <v>555</v>
+      </c>
+      <c r="D18" s="71" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F18" s="105"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="91" t="s">
-        <v>485</v>
+      <c r="B19" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>487</v>
-      </c>
-      <c r="D19" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F19" s="89"/>
+        <v>556</v>
+      </c>
+      <c r="D19" s="71" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F19" s="105"/>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="91" t="s">
-        <v>485</v>
+      <c r="B20" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="D20" s="56" t="s">
-        <v>489</v>
-      </c>
-      <c r="E20" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F20" s="89"/>
+        <v>557</v>
+      </c>
+      <c r="D20" s="72" t="s">
+        <v>558</v>
+      </c>
+      <c r="E20" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F20" s="105"/>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="91" t="s">
-        <v>485</v>
+      <c r="B21" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>490</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>491</v>
-      </c>
-      <c r="E21" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F21" s="89"/>
+        <v>559</v>
+      </c>
+      <c r="D21" s="72" t="s">
+        <v>560</v>
+      </c>
+      <c r="E21" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F21" s="105"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="91" t="s">
-        <v>485</v>
+      <c r="B22" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>492</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>493</v>
-      </c>
-      <c r="E22" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F22" s="89"/>
+        <v>561</v>
+      </c>
+      <c r="D22" s="72" t="s">
+        <v>562</v>
+      </c>
+      <c r="E22" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F22" s="105"/>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="91" t="s">
-        <v>485</v>
+      <c r="B23" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>494</v>
-      </c>
-      <c r="D23" s="55" t="s">
-        <v>495</v>
-      </c>
-      <c r="E23" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F23" s="89"/>
+        <v>563</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>564</v>
+      </c>
+      <c r="E23" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F23" s="105"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="91" t="s">
-        <v>485</v>
+      <c r="B24" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="D24" s="55" t="s">
-        <v>497</v>
-      </c>
-      <c r="E24" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F24" s="89"/>
+        <v>565</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>566</v>
+      </c>
+      <c r="E24" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F24" s="105"/>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="91" t="s">
-        <v>485</v>
+      <c r="B25" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>498</v>
-      </c>
-      <c r="D25" s="56" t="s">
-        <v>499</v>
-      </c>
-      <c r="E25" s="88" t="s">
-        <v>468</v>
-      </c>
-      <c r="F25" s="89"/>
+        <v>567</v>
+      </c>
+      <c r="D25" s="72" t="s">
+        <v>568</v>
+      </c>
+      <c r="E25" s="104" t="s">
+        <v>537</v>
+      </c>
+      <c r="F25" s="105"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E6:E25">
@@ -7371,7 +8147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF7F7F7F"/>
@@ -7387,365 +8163,365 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="36" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="92" t="s">
-        <v>500</v>
+      <c r="B3" s="108" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>501</v>
+        <v>570</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>502</v>
+        <v>571</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>503</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="93" t="s">
-        <v>504</v>
+      <c r="B6" s="109" t="s">
+        <v>573</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="D6" s="94" t="s">
-        <v>462</v>
+        <v>574</v>
+      </c>
+      <c r="D6" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="93" t="s">
-        <v>506</v>
+      <c r="B7" s="109" t="s">
+        <v>575</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>507</v>
-      </c>
-      <c r="D7" s="94" t="s">
-        <v>462</v>
+        <v>576</v>
+      </c>
+      <c r="D7" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="93" t="s">
-        <v>508</v>
+      <c r="B8" s="109" t="s">
+        <v>577</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>509</v>
-      </c>
-      <c r="D8" s="90" t="s">
-        <v>474</v>
+        <v>578</v>
+      </c>
+      <c r="D8" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="93" t="s">
-        <v>510</v>
+      <c r="B9" s="109" t="s">
+        <v>579</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>511</v>
-      </c>
-      <c r="D9" s="91" t="s">
-        <v>485</v>
+        <v>580</v>
+      </c>
+      <c r="D9" s="107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="93" t="s">
-        <v>512</v>
+      <c r="B10" s="109" t="s">
+        <v>581</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>513</v>
-      </c>
-      <c r="D10" s="94" t="s">
-        <v>462</v>
+        <v>582</v>
+      </c>
+      <c r="D10" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="93" t="s">
-        <v>514</v>
+      <c r="B11" s="109" t="s">
+        <v>583</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>515</v>
-      </c>
-      <c r="D11" s="90" t="s">
-        <v>474</v>
+        <v>584</v>
+      </c>
+      <c r="D11" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="93" t="s">
-        <v>516</v>
+      <c r="B12" s="109" t="s">
+        <v>585</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>517</v>
-      </c>
-      <c r="D12" s="91" t="s">
-        <v>485</v>
+        <v>586</v>
+      </c>
+      <c r="D12" s="107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="93" t="s">
-        <v>518</v>
+      <c r="B13" s="109" t="s">
+        <v>587</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>519</v>
-      </c>
-      <c r="D13" s="90" t="s">
-        <v>474</v>
+        <v>588</v>
+      </c>
+      <c r="D13" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="93" t="s">
-        <v>520</v>
+      <c r="B14" s="109" t="s">
+        <v>589</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>521</v>
-      </c>
-      <c r="D14" s="90" t="s">
-        <v>474</v>
+        <v>590</v>
+      </c>
+      <c r="D14" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="93" t="s">
-        <v>522</v>
+      <c r="B15" s="109" t="s">
+        <v>591</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>523</v>
-      </c>
-      <c r="D15" s="94" t="s">
-        <v>462</v>
+        <v>592</v>
+      </c>
+      <c r="D15" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="93" t="s">
-        <v>524</v>
+      <c r="B16" s="109" t="s">
+        <v>593</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>525</v>
-      </c>
-      <c r="D16" s="94" t="s">
-        <v>462</v>
+        <v>594</v>
+      </c>
+      <c r="D16" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="93" t="s">
-        <v>526</v>
+      <c r="B17" s="109" t="s">
+        <v>595</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>527</v>
+        <v>596</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>528</v>
+        <v>597</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="93" t="s">
-        <v>529</v>
+      <c r="B18" s="109" t="s">
+        <v>598</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>530</v>
-      </c>
-      <c r="D18" s="94" t="s">
-        <v>462</v>
+        <v>599</v>
+      </c>
+      <c r="D18" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="109" t="s">
+        <v>600</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>601</v>
+      </c>
+      <c r="D19" s="110" t="s">
         <v>531</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>532</v>
-      </c>
-      <c r="D19" s="94" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="93" t="s">
-        <v>533</v>
+      <c r="B20" s="109" t="s">
+        <v>602</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="94" t="s">
-        <v>462</v>
+        <v>261</v>
+      </c>
+      <c r="D20" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="93" t="s">
-        <v>534</v>
+      <c r="B21" s="109" t="s">
+        <v>603</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>535</v>
-      </c>
-      <c r="D21" s="94" t="s">
-        <v>462</v>
+        <v>604</v>
+      </c>
+      <c r="D21" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="93" t="s">
-        <v>536</v>
+      <c r="B22" s="109" t="s">
+        <v>605</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>537</v>
-      </c>
-      <c r="D22" s="94" t="s">
-        <v>462</v>
+        <v>606</v>
+      </c>
+      <c r="D22" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="93" t="s">
-        <v>538</v>
+      <c r="B23" s="109" t="s">
+        <v>607</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>539</v>
-      </c>
-      <c r="D23" s="94" t="s">
-        <v>462</v>
+        <v>608</v>
+      </c>
+      <c r="D23" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="93" t="s">
-        <v>540</v>
+      <c r="B24" s="109" t="s">
+        <v>609</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>541</v>
-      </c>
-      <c r="D24" s="91" t="s">
-        <v>485</v>
+        <v>610</v>
+      </c>
+      <c r="D24" s="107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="93" t="s">
-        <v>542</v>
+      <c r="B25" s="109" t="s">
+        <v>611</v>
       </c>
       <c r="C25" s="27" t="s">
+        <v>612</v>
+      </c>
+      <c r="D25" s="107" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="109" t="s">
+        <v>613</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>614</v>
+      </c>
+      <c r="D26" s="106" t="s">
         <v>543</v>
       </c>
-      <c r="D25" s="91" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="93" t="s">
-        <v>544</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>545</v>
-      </c>
-      <c r="D26" s="90" t="s">
-        <v>474</v>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="93" t="s">
-        <v>546</v>
+      <c r="B27" s="109" t="s">
+        <v>615</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="D27" s="90" t="s">
-        <v>474</v>
+        <v>616</v>
+      </c>
+      <c r="D27" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="93" t="s">
-        <v>548</v>
+      <c r="B28" s="109" t="s">
+        <v>617</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>549</v>
-      </c>
-      <c r="D28" s="94" t="s">
-        <v>462</v>
+        <v>618</v>
+      </c>
+      <c r="D28" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="93" t="s">
-        <v>550</v>
+      <c r="B29" s="109" t="s">
+        <v>619</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="D29" s="90" t="s">
-        <v>474</v>
+        <v>620</v>
+      </c>
+      <c r="D29" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="93" t="s">
-        <v>552</v>
+      <c r="B30" s="109" t="s">
+        <v>621</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>553</v>
-      </c>
-      <c r="D30" s="91" t="s">
-        <v>485</v>
+        <v>622</v>
+      </c>
+      <c r="D30" s="107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="109" t="s">
+        <v>623</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>624</v>
+      </c>
+      <c r="D31" s="110" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="109" t="s">
+        <v>625</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>626</v>
+      </c>
+      <c r="D32" s="107" t="s">
         <v>554</v>
       </c>
-      <c r="C31" s="27" t="s">
-        <v>555</v>
-      </c>
-      <c r="D31" s="94" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="93" t="s">
-        <v>556</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>557</v>
-      </c>
-      <c r="D32" s="91" t="s">
-        <v>485</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="93" t="s">
-        <v>558</v>
+      <c r="B33" s="109" t="s">
+        <v>627</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>559</v>
-      </c>
-      <c r="D33" s="91" t="s">
-        <v>485</v>
+        <v>628</v>
+      </c>
+      <c r="D33" s="107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="93" t="s">
-        <v>560</v>
+      <c r="B34" s="109" t="s">
+        <v>629</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>561</v>
-      </c>
-      <c r="D34" s="91" t="s">
-        <v>485</v>
+        <v>630</v>
+      </c>
+      <c r="D34" s="107" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="93" t="s">
-        <v>562</v>
+      <c r="B35" s="109" t="s">
+        <v>631</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>563</v>
-      </c>
-      <c r="D35" s="94" t="s">
-        <v>462</v>
+        <v>632</v>
+      </c>
+      <c r="D35" s="110" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="93" t="s">
-        <v>564</v>
+      <c r="B36" s="109" t="s">
+        <v>633</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="D36" s="90" t="s">
-        <v>474</v>
+        <v>634</v>
+      </c>
+      <c r="D36" s="106" t="s">
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -7759,7 +8535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFC00000"/>
@@ -7778,1132 +8554,1132 @@
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>566</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="92" t="s">
-        <v>567</v>
+      <c r="B3" s="108" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>568</v>
+        <v>637</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>457</v>
+        <v>526</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>569</v>
+        <v>638</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>570</v>
+        <v>639</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>571</v>
+        <v>640</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>572</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="95" t="s">
-        <v>573</v>
-      </c>
-      <c r="C6" s="90" t="s">
-        <v>474</v>
+      <c r="B6" s="111" t="s">
+        <v>642</v>
+      </c>
+      <c r="C6" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>576</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="95" t="s">
-        <v>577</v>
-      </c>
-      <c r="C7" s="90" t="s">
-        <v>474</v>
+      <c r="B7" s="111" t="s">
+        <v>646</v>
+      </c>
+      <c r="C7" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>578</v>
+        <v>647</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>579</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="95" t="s">
-        <v>580</v>
-      </c>
-      <c r="C8" s="90" t="s">
-        <v>474</v>
+      <c r="B8" s="111" t="s">
+        <v>649</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>582</v>
+        <v>651</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="95" t="s">
-        <v>583</v>
-      </c>
-      <c r="C9" s="90" t="s">
-        <v>474</v>
+      <c r="B9" s="111" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>584</v>
+        <v>652</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>585</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="95" t="s">
-        <v>586</v>
-      </c>
-      <c r="C10" s="90" t="s">
-        <v>474</v>
+      <c r="B10" s="111" t="s">
+        <v>654</v>
+      </c>
+      <c r="C10" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>587</v>
+        <v>655</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>588</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="95" t="s">
-        <v>589</v>
-      </c>
-      <c r="C11" s="90" t="s">
-        <v>474</v>
+      <c r="B11" s="111" t="s">
+        <v>657</v>
+      </c>
+      <c r="C11" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>590</v>
+        <v>658</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>591</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="95" t="s">
-        <v>592</v>
-      </c>
-      <c r="C12" s="90" t="s">
-        <v>474</v>
+      <c r="B12" s="111" t="s">
+        <v>660</v>
+      </c>
+      <c r="C12" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>593</v>
+        <v>661</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>594</v>
+        <v>662</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>595</v>
+        <v>663</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="95" t="s">
-        <v>596</v>
-      </c>
-      <c r="C13" s="90" t="s">
-        <v>474</v>
+      <c r="B13" s="111" t="s">
+        <v>664</v>
+      </c>
+      <c r="C13" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>593</v>
+        <v>661</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>597</v>
+        <v>665</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>598</v>
+        <v>666</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="95" t="s">
-        <v>599</v>
-      </c>
-      <c r="C14" s="90" t="s">
-        <v>474</v>
+      <c r="B14" s="111" t="s">
+        <v>667</v>
+      </c>
+      <c r="C14" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>593</v>
+        <v>661</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>600</v>
+        <v>668</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>601</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="95" t="s">
-        <v>602</v>
-      </c>
-      <c r="C15" s="90" t="s">
-        <v>474</v>
+      <c r="B15" s="111" t="s">
+        <v>670</v>
+      </c>
+      <c r="C15" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>593</v>
+        <v>661</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>603</v>
+        <v>671</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>604</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="95" t="s">
-        <v>605</v>
-      </c>
-      <c r="C16" s="90" t="s">
-        <v>474</v>
+      <c r="B16" s="111" t="s">
+        <v>673</v>
+      </c>
+      <c r="C16" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>593</v>
+        <v>661</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>606</v>
+        <v>674</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>607</v>
+        <v>675</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="95" t="s">
-        <v>608</v>
-      </c>
-      <c r="C17" s="90" t="s">
-        <v>474</v>
+      <c r="B17" s="111" t="s">
+        <v>676</v>
+      </c>
+      <c r="C17" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>609</v>
+        <v>677</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>610</v>
+        <v>678</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>611</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="95" t="s">
-        <v>612</v>
-      </c>
-      <c r="C18" s="90" t="s">
-        <v>474</v>
+      <c r="B18" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="C18" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>609</v>
+        <v>677</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>613</v>
+        <v>681</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>614</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="95" t="s">
-        <v>615</v>
-      </c>
-      <c r="C19" s="90" t="s">
-        <v>474</v>
+      <c r="B19" s="111" t="s">
+        <v>683</v>
+      </c>
+      <c r="C19" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>609</v>
+        <v>677</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>616</v>
+        <v>684</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>617</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="95" t="s">
-        <v>618</v>
-      </c>
-      <c r="C20" s="90" t="s">
-        <v>474</v>
+      <c r="B20" s="111" t="s">
+        <v>686</v>
+      </c>
+      <c r="C20" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>609</v>
+        <v>677</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>620</v>
+        <v>688</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="95" t="s">
-        <v>621</v>
-      </c>
-      <c r="C21" s="90" t="s">
-        <v>474</v>
+      <c r="B21" s="111" t="s">
+        <v>689</v>
+      </c>
+      <c r="C21" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>609</v>
+        <v>677</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>622</v>
+        <v>690</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>623</v>
+        <v>691</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="95" t="s">
-        <v>624</v>
-      </c>
-      <c r="C22" s="90" t="s">
-        <v>474</v>
+      <c r="B22" s="111" t="s">
+        <v>692</v>
+      </c>
+      <c r="C22" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>609</v>
+        <v>677</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>625</v>
+        <v>693</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>626</v>
+        <v>694</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="95" t="s">
-        <v>627</v>
-      </c>
-      <c r="C23" s="90" t="s">
-        <v>474</v>
+      <c r="B23" s="111" t="s">
+        <v>695</v>
+      </c>
+      <c r="C23" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>629</v>
+        <v>697</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>630</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="95" t="s">
-        <v>631</v>
-      </c>
-      <c r="C24" s="91" t="s">
-        <v>485</v>
+      <c r="B24" s="111" t="s">
+        <v>699</v>
+      </c>
+      <c r="C24" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>632</v>
+        <v>700</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>576</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="95" t="s">
-        <v>633</v>
-      </c>
-      <c r="C25" s="91" t="s">
-        <v>485</v>
+      <c r="B25" s="111" t="s">
+        <v>701</v>
+      </c>
+      <c r="C25" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>634</v>
+        <v>702</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>635</v>
+        <v>703</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="95" t="s">
-        <v>636</v>
-      </c>
-      <c r="C26" s="91" t="s">
-        <v>485</v>
+      <c r="B26" s="111" t="s">
+        <v>704</v>
+      </c>
+      <c r="C26" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>637</v>
+        <v>705</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>638</v>
+        <v>706</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="95" t="s">
-        <v>639</v>
-      </c>
-      <c r="C27" s="91" t="s">
-        <v>485</v>
+      <c r="B27" s="111" t="s">
+        <v>707</v>
+      </c>
+      <c r="C27" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>582</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="95" t="s">
-        <v>640</v>
-      </c>
-      <c r="C28" s="91" t="s">
-        <v>485</v>
+      <c r="B28" s="111" t="s">
+        <v>708</v>
+      </c>
+      <c r="C28" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>641</v>
+        <v>709</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>642</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="95" t="s">
-        <v>643</v>
-      </c>
-      <c r="C29" s="91" t="s">
-        <v>485</v>
+      <c r="B29" s="111" t="s">
+        <v>711</v>
+      </c>
+      <c r="C29" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>628</v>
+        <v>696</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>587</v>
+        <v>655</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>588</v>
+        <v>656</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="95" t="s">
-        <v>644</v>
-      </c>
-      <c r="C30" s="91" t="s">
-        <v>485</v>
+      <c r="B30" s="111" t="s">
+        <v>712</v>
+      </c>
+      <c r="C30" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>646</v>
+        <v>714</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>647</v>
+        <v>715</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="95" t="s">
-        <v>648</v>
-      </c>
-      <c r="C31" s="91" t="s">
-        <v>485</v>
+      <c r="B31" s="111" t="s">
+        <v>716</v>
+      </c>
+      <c r="C31" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>649</v>
+        <v>717</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>595</v>
+        <v>663</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="95" t="s">
-        <v>650</v>
-      </c>
-      <c r="C32" s="91" t="s">
-        <v>485</v>
+      <c r="B32" s="111" t="s">
+        <v>718</v>
+      </c>
+      <c r="C32" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>651</v>
+        <v>719</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>598</v>
+        <v>666</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="95" t="s">
-        <v>652</v>
-      </c>
-      <c r="C33" s="91" t="s">
-        <v>485</v>
+      <c r="B33" s="111" t="s">
+        <v>720</v>
+      </c>
+      <c r="C33" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>653</v>
+        <v>721</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>601</v>
+        <v>669</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="95" t="s">
-        <v>654</v>
-      </c>
-      <c r="C34" s="91" t="s">
-        <v>485</v>
+      <c r="B34" s="111" t="s">
+        <v>722</v>
+      </c>
+      <c r="C34" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>655</v>
+        <v>723</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>604</v>
+        <v>672</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="95" t="s">
-        <v>656</v>
-      </c>
-      <c r="C35" s="91" t="s">
-        <v>485</v>
+      <c r="B35" s="111" t="s">
+        <v>724</v>
+      </c>
+      <c r="C35" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>657</v>
+        <v>725</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>607</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="95" t="s">
-        <v>658</v>
-      </c>
-      <c r="C36" s="91" t="s">
-        <v>485</v>
+      <c r="B36" s="111" t="s">
+        <v>726</v>
+      </c>
+      <c r="C36" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>610</v>
+        <v>678</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>611</v>
+        <v>679</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="95" t="s">
-        <v>659</v>
-      </c>
-      <c r="C37" s="91" t="s">
-        <v>485</v>
+      <c r="B37" s="111" t="s">
+        <v>727</v>
+      </c>
+      <c r="C37" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>660</v>
+        <v>728</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>661</v>
+        <v>729</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>614</v>
+        <v>682</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="95" t="s">
-        <v>662</v>
-      </c>
-      <c r="C38" s="91" t="s">
-        <v>485</v>
+      <c r="B38" s="111" t="s">
+        <v>730</v>
+      </c>
+      <c r="C38" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>660</v>
+        <v>728</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>663</v>
+        <v>731</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>617</v>
+        <v>685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="95" t="s">
-        <v>664</v>
-      </c>
-      <c r="C39" s="91" t="s">
-        <v>485</v>
+      <c r="B39" s="111" t="s">
+        <v>732</v>
+      </c>
+      <c r="C39" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>660</v>
+        <v>728</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>665</v>
+        <v>733</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="95" t="s">
-        <v>666</v>
-      </c>
-      <c r="C40" s="91" t="s">
-        <v>485</v>
+      <c r="B40" s="111" t="s">
+        <v>734</v>
+      </c>
+      <c r="C40" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>660</v>
+        <v>728</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>667</v>
+        <v>735</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>668</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="95" t="s">
-        <v>669</v>
-      </c>
-      <c r="C41" s="90" t="s">
-        <v>474</v>
+      <c r="B41" s="111" t="s">
+        <v>737</v>
+      </c>
+      <c r="C41" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>670</v>
+        <v>738</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>671</v>
+        <v>739</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>672</v>
+        <v>740</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="95" t="s">
-        <v>673</v>
-      </c>
-      <c r="C42" s="90" t="s">
-        <v>474</v>
+      <c r="B42" s="111" t="s">
+        <v>741</v>
+      </c>
+      <c r="C42" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>670</v>
+        <v>738</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>674</v>
+        <v>742</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>675</v>
+        <v>743</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="95" t="s">
-        <v>676</v>
-      </c>
-      <c r="C43" s="90" t="s">
-        <v>474</v>
+      <c r="B43" s="111" t="s">
+        <v>744</v>
+      </c>
+      <c r="C43" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>677</v>
+        <v>745</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>678</v>
+        <v>746</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>679</v>
+        <v>747</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="95" t="s">
-        <v>680</v>
-      </c>
-      <c r="C44" s="90" t="s">
-        <v>474</v>
+      <c r="B44" s="111" t="s">
+        <v>748</v>
+      </c>
+      <c r="C44" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>677</v>
+        <v>745</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>681</v>
+        <v>749</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>679</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="95" t="s">
-        <v>682</v>
-      </c>
-      <c r="C45" s="90" t="s">
-        <v>474</v>
+      <c r="B45" s="111" t="s">
+        <v>750</v>
+      </c>
+      <c r="C45" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>677</v>
+        <v>745</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>683</v>
+        <v>751</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>684</v>
+        <v>752</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="95" t="s">
-        <v>685</v>
-      </c>
-      <c r="C46" s="90" t="s">
-        <v>474</v>
+      <c r="B46" s="111" t="s">
+        <v>753</v>
+      </c>
+      <c r="C46" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>9</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>686</v>
+        <v>754</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>687</v>
+        <v>755</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>688</v>
+        <v>756</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="95" t="s">
-        <v>689</v>
-      </c>
-      <c r="C47" s="91" t="s">
-        <v>485</v>
+      <c r="B47" s="111" t="s">
+        <v>757</v>
+      </c>
+      <c r="C47" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>690</v>
+        <v>758</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>691</v>
+        <v>759</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>692</v>
+        <v>760</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="95" t="s">
-        <v>693</v>
-      </c>
-      <c r="C48" s="91" t="s">
-        <v>485</v>
+      <c r="B48" s="111" t="s">
+        <v>761</v>
+      </c>
+      <c r="C48" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>690</v>
+        <v>758</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>675</v>
+        <v>743</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="95" t="s">
-        <v>695</v>
-      </c>
-      <c r="C49" s="91" t="s">
-        <v>485</v>
+      <c r="B49" s="111" t="s">
+        <v>763</v>
+      </c>
+      <c r="C49" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>690</v>
+        <v>758</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>696</v>
+        <v>764</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>684</v>
+        <v>752</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="95" t="s">
-        <v>697</v>
-      </c>
-      <c r="C50" s="91" t="s">
-        <v>485</v>
+      <c r="B50" s="111" t="s">
+        <v>765</v>
+      </c>
+      <c r="C50" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>11</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>698</v>
+        <v>766</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>699</v>
+        <v>767</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>700</v>
+        <v>768</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="95" t="s">
-        <v>701</v>
-      </c>
-      <c r="C51" s="91" t="s">
-        <v>485</v>
+      <c r="B51" s="111" t="s">
+        <v>769</v>
+      </c>
+      <c r="C51" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>702</v>
+        <v>770</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>703</v>
+        <v>771</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>700</v>
+        <v>768</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="95" t="s">
-        <v>704</v>
-      </c>
-      <c r="C52" s="94" t="s">
-        <v>462</v>
+      <c r="B52" s="111" t="s">
+        <v>772</v>
+      </c>
+      <c r="C52" s="110" t="s">
+        <v>531</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>702</v>
+        <v>770</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>705</v>
+        <v>773</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>706</v>
+        <v>774</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="95" t="s">
-        <v>707</v>
-      </c>
-      <c r="C53" s="94" t="s">
-        <v>462</v>
+      <c r="B53" s="111" t="s">
+        <v>775</v>
+      </c>
+      <c r="C53" s="110" t="s">
+        <v>531</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>702</v>
+        <v>770</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>708</v>
+        <v>776</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>709</v>
+        <v>777</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="95" t="s">
-        <v>710</v>
-      </c>
-      <c r="C54" s="94" t="s">
-        <v>462</v>
+      <c r="B54" s="111" t="s">
+        <v>778</v>
+      </c>
+      <c r="C54" s="110" t="s">
+        <v>531</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>13</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>711</v>
+        <v>779</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>712</v>
+        <v>780</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>713</v>
+        <v>781</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="95" t="s">
-        <v>714</v>
-      </c>
-      <c r="C55" s="90" t="s">
-        <v>474</v>
+      <c r="B55" s="111" t="s">
+        <v>782</v>
+      </c>
+      <c r="C55" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>13</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>711</v>
+        <v>779</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>715</v>
+        <v>783</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>716</v>
+        <v>784</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="95" t="s">
-        <v>717</v>
-      </c>
-      <c r="C56" s="90" t="s">
-        <v>474</v>
+      <c r="B56" s="111" t="s">
+        <v>785</v>
+      </c>
+      <c r="C56" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>14</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>718</v>
+        <v>786</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>719</v>
+        <v>787</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>720</v>
+        <v>788</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="95" t="s">
-        <v>721</v>
-      </c>
-      <c r="C57" s="90" t="s">
-        <v>474</v>
+      <c r="B57" s="111" t="s">
+        <v>789</v>
+      </c>
+      <c r="C57" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>722</v>
+        <v>790</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>723</v>
+        <v>791</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>724</v>
+        <v>792</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="95" t="s">
-        <v>725</v>
-      </c>
-      <c r="C58" s="90" t="s">
-        <v>474</v>
+      <c r="B58" s="111" t="s">
+        <v>793</v>
+      </c>
+      <c r="C58" s="106" t="s">
+        <v>543</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>722</v>
+        <v>790</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>726</v>
+        <v>794</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>727</v>
+        <v>795</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="95" t="s">
-        <v>728</v>
-      </c>
-      <c r="C59" s="91" t="s">
-        <v>485</v>
+      <c r="B59" s="111" t="s">
+        <v>796</v>
+      </c>
+      <c r="C59" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>722</v>
+        <v>790</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>729</v>
+        <v>797</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>724</v>
+        <v>792</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="95" t="s">
-        <v>730</v>
-      </c>
-      <c r="C60" s="91" t="s">
-        <v>485</v>
+      <c r="B60" s="111" t="s">
+        <v>798</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>554</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>722</v>
+        <v>790</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>731</v>
+        <v>799</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>727</v>
+        <v>795</v>
       </c>
     </row>
   </sheetData>

--- a/資料/TB杭とSB杭の違い_SS7.xlsx
+++ b/資料/TB杭とSB杭の違い_SS7.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="886">
   <si>
     <t xml:space="preserve">TB杭とSB杭の違い ― 要点まとめ</t>
   </si>
@@ -613,10 +613,310 @@
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">○：負担する（緑）　×：負担しない（赤）　「PDF赤枠」は赤枠入りPDFの枠ID（T＝TB杭、S＝SB杭）</t>
+    <t xml:space="preserve">○：負担する（緑）　×：負担しない（赤）　「PDF赤枠」は赤枠入りPDFの枠ID（T＝TB杭、S＝SB杭）　※記号と式の読み方はこの表のすぐ下にあります</t>
   </si>
   <si>
     <t xml:space="preserve">※「リブの有無 → 軸力を負担するか」の対応は、SS7の式の組み立てからの解釈です。SB杭の鋼管にリブが無いとはマニュアルに明記されていません。実際の仕様は各協会の設計・施工指針で確認してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 記号の意味（まず添字のルールを押さえると読みやすい）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左下の添字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r ＝ 鉄筋コンクリート部（鋼管の中のRC）　／　s ＝ 鋼管　／　c ＝ コンクリート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">右下の添字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c・0 ＝ 圧縮だけを受けるとき　／　t ＝ 引張だけを受けるとき　／　A ＝ 許容値（Allowable）　／　D ＝ 設計用（Design）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">符号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">軸力は 圧縮を＋、引張（引抜き）を− として扱う（そのため rNt は負の値になる）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt ＝「r：RC部の」「N：軸力で」「t：引張だけを受けるときの許容値」　　sM0 ＝「s：鋼管の」「M：曲げで」「0：軸力0のときの許容値」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意味（ひとことで）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どこで使うか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N、ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設計用軸方向力。杭頭に作用する軸力（圧縮＋、引張−）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">検定の左辺。TBは N、SBは ND と書く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">共通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M、MD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設計用曲げモーメント。杭頭に作用する曲げ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">検定の左辺。TBは M、SBは MD と書く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部が圧縮だけを受けるときの許容軸力＝RC部が負担できる圧縮側の上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：ケース分けの境目、N ≦ rNc＋sN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rN0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部が圧縮だけを受けるときの許容軸力＝RC部が負担できる圧縮側の上限（TBの rNc と同じ意味）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB：rN0 ≧ ND ≧ rNt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部が引張だけを受けるときの許容軸力＝RC部が負担できる引張側の限界（負の値）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB・SB：ケース分けと適用範囲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rN、rNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部の許容軸力（ある軸力レベルで、RC部に持たせる軸力）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N＝rN、ND＝rNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB／SB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rM、rMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部の許容曲げモーメント（その軸力を受けた状態でRC部が持てる曲げ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M ≦ sM0＋rM、MD ≦ sM0＋rMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管が負担する許容軸力（圧縮側。引張側は sN'）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：N ≦ rNc＋sN など</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管が軸力 sN を負担した状態で持てる許容曲げモーメント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB：M＝sM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管が曲げだけを受けるとき（軸力0）の許容曲げモーメント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM0＝sZ・sf（TB）、sZ・sft（SB）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄筋の許容応力度（圧縮または引張）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt＝−rf・rA など</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄筋の全断面積（主筋の断面積の合計）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf、cfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コンクリートの許容圧縮応力度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNc、rN0 の式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コンクリートの断面積</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヤング係数比（鉄筋のヤング係数 ÷ コンクリートのヤング係数）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sA、sZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管の断面積・断面係数（腐食しろを控除）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sN、sM、sM0 の式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sf、sft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管の許容圧縮応力度（TB）・許容引張応力度（SB）。どちらも F/1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM0 の式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 式の読み方（言葉に直すと）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">読み方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt＝−rf・rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部が負担できる引張軸力の限界 ＝ 鉄筋の許容応力度 × 鉄筋の全断面積（引張なのでマイナス）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引張ではコンクリートを無視し、鉄筋だけで抵抗させる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt＝−0.75・rf・rA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上の式を0.75倍に低減したもの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBは引張側の限界が25％小さい → 引抜きで不利</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNc（rN0）＝cf(cA＋n・rA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC部が負担できる圧縮軸力の上限 ＝ コンクリートの許容圧縮応力度 ×（コンクリート断面積 ＋ 鉄筋をコンクリートに換算した断面積）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n ≦ rf/cf のとき。n＞rf/cf のときは rf(rA＋cA/n)（鉄筋側で決まる）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ND＝rNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設計軸力 ND を、そのまま全部 RC部 に持たせる（鋼管の軸力は0）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBの考え方そのもの。この軸力のときの RC部の許容曲げ rMA を求めて、次の曲げの検定に使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rN0 ≧ ND ≧ rNt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設計軸力 ND が、RC部の圧縮側の上限 rN0 と引張側の限界 rNt の間に入っていること</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＝RC部だけで軸力を負担できる範囲。外れるとSBでは成り立たない（鋼管の余裕なし）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD ≦ sM0＋rMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設計曲げ MD ≦ 鋼管の許容曲げ（軸力0）＋ その軸力でのRC部の許容曲げ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">曲げは鋼管とRCで足し合わせて負担（単純累加）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N＞rNc のとき
+N ≦ rNc＋sN、M＝sM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">軸力がRC部の圧縮上限 rNc を超えた。RC部は rNc まで負担し、超えた分（N−rNc）は鋼管が負担。合計が rNc＋sN 以下なら OK。曲げは鋼管が受け持つ（M＝sM）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管は sN/sA＋sM/sZ＝sf（軸力と曲げを合わせた応力が許容応力度以内）で確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNc ≧ N ≧ rNt のとき
+N＝rN、M ≦ sM0＋rM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">軸力がRC部の範囲内。軸力は全部RC部が負担し、曲げは 鋼管（軸力0）＋RC部 で負担</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBの ND＝rNA、MD ≦ sM0＋rMA と同じ考え方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rNt＞N のとき
+N ≧ rNt＋sN、M＝sM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引張軸力がRC部の引張限界 rNt を超えた。超えた引張分は鋼管が負担。合計が rNt＋sN 以上（引張側で許容以内）なら OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管は sN'/sA−sM/sZ＝−sf（引張側の組合せ応力）で確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM0＝sZ・sf（sZ・sft）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼管が曲げだけを受けるときの許容曲げ ＝ 鋼管の断面係数 × 鋼管の許容応力度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sf＝sft＝F/1.5 なので TB・SB で同じ値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出典：SS7マニュアル 式(7.121)〜(7.132)（TB杭）、式(7.135)〜(7.140)（SB杭）。rN・rM・rNA・rMA の求め方は 7.7.4（場所打ちコンクリート杭）による。</t>
   </si>
   <si>
     <t xml:space="preserve">■ 比較図</t>
@@ -1748,9 +2048,6 @@
     <t xml:space="preserve">メモ</t>
   </si>
   <si>
-    <t xml:space="preserve">共通</t>
-  </si>
-  <si>
     <t xml:space="preserve">打設状態（空掘り・泥水中）の設定が施工計画と合っているか</t>
   </si>
   <si>
@@ -1784,9 +2081,6 @@
     <t xml:space="preserve">仮想コンクリート断面のオフセット（既定100mm）が妥当か</t>
   </si>
   <si>
-    <t xml:space="preserve">TB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fc が協会の範囲（18〜45 N/mm²）に入っているか（SS7は制限しない）</t>
   </si>
   <si>
@@ -1817,9 +2111,6 @@
     <t xml:space="preserve">式(10.254)</t>
   </si>
   <si>
-    <t xml:space="preserve">SB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fc が協会の範囲（18〜36 N/mm²）に入っているか、メッセージが出ていないか</t>
   </si>
   <si>
@@ -1865,9 +2156,6 @@
     <t xml:space="preserve">SS7 マニュアルの記号をそのまま使っています（添字の r：鉄筋コンクリート部、s：鋼管、c：コンクリート）。</t>
   </si>
   <si>
-    <t xml:space="preserve">記号</t>
-  </si>
-  <si>
     <t xml:space="preserve">意味</t>
   </si>
   <si>
@@ -1886,21 +2174,12 @@
     <t xml:space="preserve">設計用曲げモーメント</t>
   </si>
   <si>
-    <t xml:space="preserve">rNc</t>
-  </si>
-  <si>
     <t xml:space="preserve">鋼管内（鉄筋）コンクリート部が圧縮力だけを受ける場合の許容軸方向力</t>
   </si>
   <si>
-    <t xml:space="preserve">rN0</t>
-  </si>
-  <si>
     <t xml:space="preserve">鉄筋コンクリート部が圧縮力だけを受ける場合の許容軸方向力</t>
   </si>
   <si>
-    <t xml:space="preserve">rNt</t>
-  </si>
-  <si>
     <t xml:space="preserve">（鋼管内）鉄筋コンクリート部が引張力だけを受ける場合の許容軸方向力（TB：−rf・rA、SB：−0.75・rf・rA）</t>
   </si>
   <si>
@@ -1922,15 +2201,9 @@
     <t xml:space="preserve">鋼管部の許容軸方向圧縮力・許容軸方向引張力</t>
   </si>
   <si>
-    <t xml:space="preserve">sM</t>
-  </si>
-  <si>
     <t xml:space="preserve">鋼管部の許容曲げモーメント</t>
   </si>
   <si>
-    <t xml:space="preserve">sM0</t>
-  </si>
-  <si>
     <t xml:space="preserve">鋼管部が曲げモーメントだけを受ける場合の許容曲げモーメント</t>
   </si>
   <si>
@@ -1946,9 +2219,6 @@
     <t xml:space="preserve">鋼管の許容圧縮応力度（TB）・許容引張応力度（SB）</t>
   </si>
   <si>
-    <t xml:space="preserve">TB／SB</t>
-  </si>
-  <si>
     <t xml:space="preserve">sfs</t>
   </si>
   <si>
@@ -1961,16 +2231,7 @@
     <t xml:space="preserve">コンクリートの断面積・鉄筋の全断面積</t>
   </si>
   <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
     <t xml:space="preserve">cf、cfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コンクリートの許容圧縮応力度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rf</t>
   </si>
   <si>
     <t xml:space="preserve">鉄筋の許容圧縮応力度（SBの rN0・rNt では許容圧縮または許容引張応力度）</t>
@@ -2567,7 +2828,7 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="52">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2791,6 +3052,54 @@
       <charset val="128"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F75B5"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC65911"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
       <name val="Meiryo UI"/>
@@ -2907,29 +3216,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF2F75B5"/>
-      <name val="Meiryo UI"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC65911"/>
-      <name val="Meiryo UI"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Meiryo UI"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2951,7 +3244,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -2988,6 +3281,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CBAD"/>
         <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -3058,7 +3357,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="118">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3275,19 +3574,55 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3295,15 +3630,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3311,15 +3646,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3327,7 +3662,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3343,15 +3678,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="37" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="43" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3367,11 +3702,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="44" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3379,7 +3714,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3387,7 +3722,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3403,11 +3738,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="42" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3415,7 +3750,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="42" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3435,7 +3770,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3455,40 +3790,32 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="46" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="47" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="47" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="46" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -3499,11 +3826,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3712,7 +4035,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -3725,7 +4048,7 @@
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFE699"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF8CBAD"/>
@@ -3756,13 +4079,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>201960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>729720</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>144360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3776,7 +4099,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="177840" y="9001080"/>
+          <a:off x="177840" y="21326400"/>
           <a:ext cx="10953360" cy="6886080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4607,7 +4930,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G27"/>
+  <dimension ref="B2:G66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4967,13 +5290,552 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C28" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C29" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C30" s="54" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+    </row>
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C31" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="9"/>
+      <c r="C33" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="G35" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C37" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C38" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="G38" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C39" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C40" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C41" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E41" s="27"/>
+      <c r="F41" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="G41" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C42" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="E42" s="27"/>
+      <c r="F42" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="G42" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C43" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="E43" s="27"/>
+      <c r="F43" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G43" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C44" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="E44" s="27"/>
+      <c r="F44" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C45" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="E45" s="27"/>
+      <c r="F45" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G45" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C46" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" s="27"/>
+      <c r="F46" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G46" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C47" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" s="27"/>
+      <c r="F47" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G47" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C48" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="27"/>
+      <c r="F48" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G48" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C49" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" s="27"/>
+      <c r="F49" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C50" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="E50" s="27"/>
+      <c r="F50" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="9"/>
+      <c r="C53" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C54" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="53"/>
+      <c r="F54" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="G54" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C55" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E55" s="44"/>
+      <c r="F55" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="G55" s="58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C56" s="61" t="s">
+        <v>257</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="G56" s="62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C57" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" s="44"/>
+      <c r="F57" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="G57" s="58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C58" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="G58" s="58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C59" s="60" t="s">
+        <v>266</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="G59" s="58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C60" s="59" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="G60" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C61" s="59" t="s">
+        <v>272</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>273</v>
+      </c>
+      <c r="E61" s="44"/>
+      <c r="F61" s="53" t="s">
+        <v>274</v>
+      </c>
+      <c r="G61" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C62" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="G62" s="57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C63" s="61" t="s">
+        <v>278</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="E63" s="44"/>
+      <c r="F63" s="53" t="s">
+        <v>280</v>
+      </c>
+      <c r="G63" s="62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="38">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="B25:G25"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D63:E63"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4983,7 +5845,7 @@
     <oddFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="26" man="true" max="16383" min="0"/>
+    <brk id="65" man="true" max="16383" min="0"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5010,7 +5872,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5019,85 +5881,85 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
+      <c r="A3" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>186</v>
+        <v>285</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>187</v>
+        <v>286</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>190</v>
+        <v>289</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>191</v>
+        <v>290</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>192</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="55" t="s">
-        <v>193</v>
+      <c r="B5" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>195</v>
+        <v>294</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>197</v>
+        <v>295</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="I5" s="58" t="s">
-        <v>200</v>
+        <v>297</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="I5" s="67" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="55" t="s">
-        <v>193</v>
+      <c r="B6" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>15</v>
@@ -5105,567 +5967,567 @@
       <c r="E6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="59" t="s">
-        <v>202</v>
+      <c r="F6" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="I6" s="58" t="s">
-        <v>205</v>
+        <v>302</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>303</v>
+      </c>
+      <c r="I6" s="67" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="55" t="s">
-        <v>193</v>
+      <c r="B7" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>202</v>
+        <v>307</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="H7" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>211</v>
+        <v>308</v>
+      </c>
+      <c r="H7" s="66" t="s">
+        <v>309</v>
+      </c>
+      <c r="I7" s="67" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="55" t="s">
-        <v>193</v>
+      <c r="B8" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>212</v>
+        <v>311</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>213</v>
+        <v>312</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="56" t="s">
-        <v>197</v>
+        <v>312</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G8" s="18"/>
-      <c r="H8" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="I8" s="58" t="s">
-        <v>200</v>
+      <c r="H8" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="I8" s="67" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="55" t="s">
-        <v>193</v>
+      <c r="B9" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>215</v>
+        <v>314</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>216</v>
+        <v>315</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F9" s="56" t="s">
-        <v>197</v>
+        <v>315</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G9" s="18"/>
-      <c r="H9" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="I9" s="58" t="s">
-        <v>200</v>
+      <c r="H9" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="I9" s="67" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="55" t="s">
-        <v>193</v>
+      <c r="B10" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>217</v>
+        <v>316</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="F10" s="56" t="s">
-        <v>197</v>
+        <v>317</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G10" s="18"/>
-      <c r="H10" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="I10" s="58" t="s">
-        <v>200</v>
+      <c r="H10" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="I10" s="67" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="55" t="s">
-        <v>193</v>
+      <c r="B11" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>219</v>
+        <v>318</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>220</v>
+        <v>319</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="F11" s="59" t="s">
-        <v>202</v>
+        <v>320</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="H11" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>205</v>
+        <v>321</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>303</v>
+      </c>
+      <c r="I11" s="67" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="55" t="s">
-        <v>193</v>
+      <c r="B12" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>223</v>
+        <v>322</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="F12" s="59" t="s">
-        <v>202</v>
+        <v>323</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>227</v>
+        <v>324</v>
+      </c>
+      <c r="H12" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="I12" s="67" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="55" t="s">
-        <v>228</v>
+      <c r="B13" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>229</v>
+        <v>328</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>230</v>
+        <v>329</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="F13" s="59" t="s">
-        <v>202</v>
+        <v>330</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="H13" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="I13" s="58" t="s">
-        <v>234</v>
+        <v>331</v>
+      </c>
+      <c r="H13" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="I13" s="67" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="55" t="s">
-        <v>228</v>
+      <c r="B14" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>236</v>
+        <v>335</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F14" s="59" t="s">
-        <v>202</v>
+        <v>336</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="H14" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="I14" s="58" t="s">
-        <v>234</v>
+        <v>337</v>
+      </c>
+      <c r="H14" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="I14" s="67" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="55" t="s">
-        <v>228</v>
+      <c r="B15" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>239</v>
+        <v>338</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>240</v>
+        <v>339</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="F15" s="60" t="s">
-        <v>242</v>
+        <v>340</v>
+      </c>
+      <c r="F15" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="H15" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="I15" s="58" t="s">
-        <v>234</v>
+        <v>342</v>
+      </c>
+      <c r="H15" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="I15" s="67" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="55" t="s">
-        <v>228</v>
+      <c r="B16" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>244</v>
+        <v>343</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>245</v>
+        <v>344</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="F16" s="56" t="s">
-        <v>197</v>
+        <v>344</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="H16" s="57" t="s">
-        <v>247</v>
-      </c>
-      <c r="I16" s="58" t="s">
-        <v>234</v>
+        <v>345</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>346</v>
+      </c>
+      <c r="I16" s="67" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="55" t="s">
-        <v>228</v>
+      <c r="B17" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>248</v>
+        <v>347</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="F17" s="56" t="s">
-        <v>197</v>
+        <v>348</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="57" t="s">
-        <v>247</v>
-      </c>
-      <c r="I17" s="58" t="s">
-        <v>250</v>
+      <c r="H17" s="66" t="s">
+        <v>346</v>
+      </c>
+      <c r="I17" s="67" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="55" t="s">
-        <v>228</v>
+      <c r="B18" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>251</v>
+        <v>350</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="F18" s="56" t="s">
-        <v>197</v>
+        <v>352</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="H18" s="55" t="s">
-        <v>255</v>
-      </c>
-      <c r="I18" s="58" t="s">
-        <v>256</v>
+        <v>353</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>354</v>
+      </c>
+      <c r="I18" s="67" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="55" t="s">
-        <v>228</v>
+      <c r="B19" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>257</v>
+        <v>356</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>258</v>
+        <v>357</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="56" t="s">
-        <v>197</v>
+        <v>357</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G19" s="18"/>
-      <c r="H19" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="I19" s="58" t="s">
-        <v>260</v>
+      <c r="H19" s="66" t="s">
+        <v>358</v>
+      </c>
+      <c r="I19" s="67" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="55" t="s">
-        <v>228</v>
+      <c r="B20" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>261</v>
+        <v>360</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="F20" s="56" t="s">
-        <v>197</v>
+        <v>361</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="57" t="s">
-        <v>263</v>
-      </c>
-      <c r="I20" s="58" t="s">
-        <v>260</v>
+      <c r="H20" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="I20" s="67" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="55" t="s">
-        <v>264</v>
+      <c r="B21" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>265</v>
+        <v>364</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>266</v>
+        <v>365</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="F21" s="60" t="s">
-        <v>242</v>
+        <v>366</v>
+      </c>
+      <c r="F21" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="H21" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="I21" s="58" t="s">
-        <v>270</v>
+        <v>367</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>368</v>
+      </c>
+      <c r="I21" s="67" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="55" t="s">
-        <v>264</v>
+      <c r="B22" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>271</v>
+        <v>370</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="F22" s="59" t="s">
-        <v>202</v>
+        <v>371</v>
+      </c>
+      <c r="F22" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="H22" s="55" t="s">
-        <v>274</v>
-      </c>
-      <c r="I22" s="58" t="s">
-        <v>275</v>
+        <v>372</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>373</v>
+      </c>
+      <c r="I22" s="67" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="55" t="s">
-        <v>264</v>
+      <c r="B23" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>158</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>276</v>
+        <v>375</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="F23" s="59" t="s">
-        <v>202</v>
+        <v>376</v>
+      </c>
+      <c r="F23" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="H23" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="I23" s="58" t="s">
-        <v>275</v>
+        <v>377</v>
+      </c>
+      <c r="H23" s="64" t="s">
+        <v>378</v>
+      </c>
+      <c r="I23" s="67" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="55" t="s">
-        <v>264</v>
+      <c r="B24" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>280</v>
+        <v>379</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>281</v>
+        <v>380</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="F24" s="60" t="s">
-        <v>242</v>
+        <v>381</v>
+      </c>
+      <c r="F24" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="H24" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="I24" s="58" t="s">
-        <v>285</v>
+        <v>382</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>383</v>
+      </c>
+      <c r="I24" s="67" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="55" t="s">
-        <v>264</v>
+      <c r="B25" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>286</v>
+        <v>385</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="F25" s="56" t="s">
-        <v>197</v>
+        <v>387</v>
+      </c>
+      <c r="F25" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="H25" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="I25" s="58" t="s">
-        <v>291</v>
+        <v>388</v>
+      </c>
+      <c r="H25" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="I25" s="67" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="55" t="s">
-        <v>264</v>
+      <c r="B26" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>292</v>
+        <v>391</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>35</v>
@@ -5673,720 +6535,720 @@
       <c r="E26" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="59" t="s">
-        <v>202</v>
+      <c r="F26" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="H26" s="55" t="s">
-        <v>294</v>
-      </c>
-      <c r="I26" s="58" t="s">
-        <v>295</v>
+        <v>392</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>393</v>
+      </c>
+      <c r="I26" s="67" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="55" t="s">
-        <v>264</v>
+      <c r="B27" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C27" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="F27" s="65" t="s">
         <v>296</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F27" s="56" t="s">
-        <v>197</v>
-      </c>
       <c r="G27" s="18"/>
-      <c r="H27" s="57" t="s">
-        <v>298</v>
-      </c>
-      <c r="I27" s="58" t="s">
-        <v>299</v>
+      <c r="H27" s="66" t="s">
+        <v>397</v>
+      </c>
+      <c r="I27" s="67" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="55" t="s">
-        <v>264</v>
+      <c r="B28" s="64" t="s">
+        <v>363</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F28" s="56" t="s">
-        <v>197</v>
+        <v>396</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G28" s="18"/>
-      <c r="H28" s="57" t="s">
-        <v>301</v>
-      </c>
-      <c r="I28" s="58" t="s">
-        <v>302</v>
+      <c r="H28" s="66" t="s">
+        <v>400</v>
+      </c>
+      <c r="I28" s="67" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="55" t="s">
-        <v>303</v>
+      <c r="B29" s="64" t="s">
+        <v>402</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>304</v>
+        <v>403</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="F29" s="56" t="s">
-        <v>197</v>
+        <v>405</v>
+      </c>
+      <c r="F29" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="H29" s="55" t="s">
-        <v>308</v>
-      </c>
-      <c r="I29" s="58" t="s">
-        <v>309</v>
+        <v>406</v>
+      </c>
+      <c r="H29" s="64" t="s">
+        <v>407</v>
+      </c>
+      <c r="I29" s="67" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="55" t="s">
-        <v>303</v>
+      <c r="B30" s="64" t="s">
+        <v>402</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>310</v>
+        <v>409</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="F30" s="60" t="s">
-        <v>242</v>
+        <v>410</v>
+      </c>
+      <c r="F30" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G30" s="18"/>
-      <c r="H30" s="57" t="s">
-        <v>312</v>
-      </c>
-      <c r="I30" s="58" t="s">
-        <v>313</v>
+      <c r="H30" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="I30" s="67" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="55" t="s">
-        <v>303</v>
+      <c r="B31" s="64" t="s">
+        <v>402</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>314</v>
+        <v>413</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="F31" s="59" t="s">
-        <v>202</v>
+        <v>414</v>
+      </c>
+      <c r="F31" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="H31" s="55" t="s">
-        <v>317</v>
-      </c>
-      <c r="I31" s="58" t="s">
-        <v>313</v>
+        <v>415</v>
+      </c>
+      <c r="H31" s="64" t="s">
+        <v>416</v>
+      </c>
+      <c r="I31" s="67" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="55" t="s">
-        <v>303</v>
+      <c r="B32" s="64" t="s">
+        <v>402</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>318</v>
+        <v>417</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="F32" s="56" t="s">
-        <v>197</v>
+        <v>418</v>
+      </c>
+      <c r="F32" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G32" s="18"/>
-      <c r="H32" s="57" t="s">
-        <v>312</v>
-      </c>
-      <c r="I32" s="58" t="s">
-        <v>313</v>
+      <c r="H32" s="66" t="s">
+        <v>411</v>
+      </c>
+      <c r="I32" s="67" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="55" t="s">
-        <v>320</v>
+      <c r="B33" s="64" t="s">
+        <v>419</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>321</v>
+        <v>420</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>322</v>
+        <v>421</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="F33" s="56" t="s">
-        <v>197</v>
+        <v>421</v>
+      </c>
+      <c r="F33" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G33" s="18"/>
-      <c r="H33" s="55" t="s">
-        <v>323</v>
-      </c>
-      <c r="I33" s="58" t="s">
-        <v>324</v>
+      <c r="H33" s="64" t="s">
+        <v>422</v>
+      </c>
+      <c r="I33" s="67" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="55" t="s">
-        <v>320</v>
+      <c r="B34" s="64" t="s">
+        <v>419</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>325</v>
+        <v>424</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>326</v>
+        <v>425</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="F34" s="59" t="s">
-        <v>202</v>
+        <v>426</v>
+      </c>
+      <c r="F34" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="H34" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="I34" s="58" t="s">
-        <v>330</v>
+        <v>427</v>
+      </c>
+      <c r="H34" s="66" t="s">
+        <v>428</v>
+      </c>
+      <c r="I34" s="67" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="55" t="s">
-        <v>320</v>
+      <c r="B35" s="64" t="s">
+        <v>419</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>331</v>
+        <v>430</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>332</v>
+        <v>431</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>333</v>
-      </c>
-      <c r="F35" s="60" t="s">
-        <v>242</v>
+        <v>432</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G35" s="18"/>
-      <c r="H35" s="57" t="s">
-        <v>334</v>
-      </c>
-      <c r="I35" s="58" t="s">
-        <v>335</v>
+      <c r="H35" s="66" t="s">
+        <v>433</v>
+      </c>
+      <c r="I35" s="67" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="55" t="s">
-        <v>320</v>
+      <c r="B36" s="64" t="s">
+        <v>419</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>336</v>
+        <v>435</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>337</v>
+        <v>436</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="F36" s="60" t="s">
-        <v>242</v>
+        <v>437</v>
+      </c>
+      <c r="F36" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="H36" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="I36" s="58" t="s">
-        <v>330</v>
+        <v>438</v>
+      </c>
+      <c r="H36" s="66" t="s">
+        <v>428</v>
+      </c>
+      <c r="I36" s="67" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="55" t="s">
-        <v>320</v>
+      <c r="B37" s="64" t="s">
+        <v>419</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>340</v>
+        <v>439</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>341</v>
+        <v>440</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="60" t="s">
-        <v>242</v>
+      <c r="F37" s="69" t="s">
+        <v>341</v>
       </c>
       <c r="G37" s="18"/>
-      <c r="H37" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="I37" s="58" t="s">
-        <v>343</v>
+      <c r="H37" s="66" t="s">
+        <v>441</v>
+      </c>
+      <c r="I37" s="67" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="55" t="s">
-        <v>320</v>
+      <c r="B38" s="64" t="s">
+        <v>419</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>345</v>
+        <v>444</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="59" t="s">
-        <v>202</v>
+      <c r="F38" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="H38" s="55" t="s">
-        <v>347</v>
-      </c>
-      <c r="I38" s="58" t="s">
-        <v>348</v>
+        <v>445</v>
+      </c>
+      <c r="H38" s="64" t="s">
+        <v>446</v>
+      </c>
+      <c r="I38" s="67" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>349</v>
+        <v>448</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>350</v>
+        <v>449</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="F39" s="59" t="s">
-        <v>202</v>
+        <v>450</v>
+      </c>
+      <c r="F39" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="H39" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="I39" s="58" t="s">
-        <v>354</v>
+        <v>451</v>
+      </c>
+      <c r="H39" s="66" t="s">
+        <v>452</v>
+      </c>
+      <c r="I39" s="67" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>355</v>
+        <v>454</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>356</v>
+        <v>455</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="F40" s="59" t="s">
-        <v>202</v>
+        <v>456</v>
+      </c>
+      <c r="F40" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G40" s="18"/>
-      <c r="H40" s="57" t="s">
-        <v>358</v>
-      </c>
-      <c r="I40" s="58" t="s">
-        <v>359</v>
+      <c r="H40" s="66" t="s">
+        <v>457</v>
+      </c>
+      <c r="I40" s="67" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>360</v>
+        <v>459</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>361</v>
+        <v>460</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="F41" s="59" t="s">
-        <v>202</v>
+        <v>461</v>
+      </c>
+      <c r="F41" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G41" s="18"/>
-      <c r="H41" s="55" t="s">
-        <v>363</v>
-      </c>
-      <c r="I41" s="58" t="s">
-        <v>364</v>
+      <c r="H41" s="64" t="s">
+        <v>462</v>
+      </c>
+      <c r="I41" s="67" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="55" t="s">
+      <c r="B42" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>365</v>
+        <v>464</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>366</v>
+        <v>465</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="F42" s="59" t="s">
-        <v>202</v>
+        <v>466</v>
+      </c>
+      <c r="F42" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G42" s="18"/>
-      <c r="H42" s="55" t="s">
-        <v>368</v>
-      </c>
-      <c r="I42" s="58" t="s">
-        <v>369</v>
+      <c r="H42" s="64" t="s">
+        <v>467</v>
+      </c>
+      <c r="I42" s="67" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>370</v>
+        <v>469</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>371</v>
+        <v>470</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="F43" s="59" t="s">
-        <v>202</v>
+        <v>471</v>
+      </c>
+      <c r="F43" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G43" s="18"/>
-      <c r="H43" s="55" t="s">
-        <v>373</v>
-      </c>
-      <c r="I43" s="58" t="s">
-        <v>374</v>
+      <c r="H43" s="64" t="s">
+        <v>472</v>
+      </c>
+      <c r="I43" s="67" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>375</v>
+        <v>474</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>376</v>
+        <v>475</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>377</v>
-      </c>
-      <c r="F44" s="59" t="s">
-        <v>202</v>
+        <v>476</v>
+      </c>
+      <c r="F44" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="H44" s="55" t="s">
-        <v>379</v>
-      </c>
-      <c r="I44" s="58" t="s">
-        <v>380</v>
+        <v>477</v>
+      </c>
+      <c r="H44" s="64" t="s">
+        <v>478</v>
+      </c>
+      <c r="I44" s="67" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="55" t="s">
-        <v>381</v>
+      <c r="B45" s="64" t="s">
+        <v>480</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>382</v>
+        <v>481</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>383</v>
+        <v>482</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="F45" s="56" t="s">
-        <v>197</v>
+        <v>482</v>
+      </c>
+      <c r="F45" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G45" s="18"/>
-      <c r="H45" s="57" t="s">
-        <v>384</v>
+      <c r="H45" s="66" t="s">
+        <v>483</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>385</v>
+        <v>484</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="55" t="s">
-        <v>381</v>
+      <c r="B46" s="64" t="s">
+        <v>480</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>386</v>
+        <v>485</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>387</v>
+        <v>486</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="F46" s="56" t="s">
-        <v>197</v>
+        <v>486</v>
+      </c>
+      <c r="F46" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G46" s="18"/>
-      <c r="H46" s="57" t="s">
-        <v>388</v>
+      <c r="H46" s="66" t="s">
+        <v>487</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="55" t="s">
-        <v>381</v>
+      <c r="B47" s="64" t="s">
+        <v>480</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>391</v>
+        <v>490</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="F47" s="56" t="s">
-        <v>197</v>
+        <v>490</v>
+      </c>
+      <c r="F47" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G47" s="18"/>
-      <c r="H47" s="55" t="s">
-        <v>392</v>
+      <c r="H47" s="64" t="s">
+        <v>491</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>393</v>
+        <v>492</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="55" t="s">
-        <v>381</v>
+      <c r="B48" s="64" t="s">
+        <v>480</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>394</v>
+        <v>493</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>395</v>
+        <v>494</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="F48" s="59" t="s">
-        <v>202</v>
+        <v>495</v>
+      </c>
+      <c r="F48" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>397</v>
-      </c>
-      <c r="H48" s="55" t="s">
-        <v>398</v>
-      </c>
-      <c r="I48" s="58" t="s">
-        <v>399</v>
+        <v>496</v>
+      </c>
+      <c r="H48" s="64" t="s">
+        <v>497</v>
+      </c>
+      <c r="I48" s="67" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="55" t="s">
-        <v>381</v>
+      <c r="B49" s="64" t="s">
+        <v>480</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>400</v>
+        <v>499</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>401</v>
+        <v>500</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="F49" s="59" t="s">
-        <v>202</v>
+        <v>501</v>
+      </c>
+      <c r="F49" s="68" t="s">
+        <v>301</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="H49" s="55" t="s">
-        <v>404</v>
-      </c>
-      <c r="I49" s="58" t="s">
-        <v>405</v>
+        <v>502</v>
+      </c>
+      <c r="H49" s="64" t="s">
+        <v>503</v>
+      </c>
+      <c r="I49" s="67" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="55" t="s">
-        <v>381</v>
+      <c r="B50" s="64" t="s">
+        <v>480</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>406</v>
+        <v>505</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="F50" s="56" t="s">
-        <v>197</v>
+        <v>317</v>
+      </c>
+      <c r="F50" s="65" t="s">
+        <v>296</v>
       </c>
       <c r="G50" s="18"/>
-      <c r="H50" s="57" t="s">
-        <v>407</v>
-      </c>
-      <c r="I50" s="58" t="s">
-        <v>408</v>
+      <c r="H50" s="66" t="s">
+        <v>506</v>
+      </c>
+      <c r="I50" s="67" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="32" t="s">
-        <v>409</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="D53" s="62" t="str">
+      <c r="C53" s="70" t="s">
+        <v>301</v>
+      </c>
+      <c r="D53" s="71" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C53)&amp;" 項目"</f>
         <v>20 項目</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="D54" s="62" t="str">
+      <c r="C54" s="72" t="s">
+        <v>341</v>
+      </c>
+      <c r="D54" s="71" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C54)&amp;" 項目"</f>
         <v>7 項目</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="64" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" s="62" t="str">
+      <c r="C55" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="D55" s="71" t="str">
         <f aca="false">COUNTIF($F$5:$F$50,C55)&amp;" 項目"</f>
         <v>19 項目</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="35" t="s">
-        <v>410</v>
+        <v>509</v>
       </c>
       <c r="B57" s="35"/>
       <c r="C57" s="35"/>
@@ -6431,22 +7293,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="36" t="s">
-        <v>411</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>412</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="65" t="s">
-        <v>413</v>
+      <c r="B4" s="74" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>414</v>
+        <v>513</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -6457,36 +7319,36 @@
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="C7" s="67" t="n">
+      <c r="B7" s="75" t="s">
+        <v>514</v>
+      </c>
+      <c r="C7" s="76" t="n">
         <v>24</v>
       </c>
-      <c r="D7" s="68" t="s">
-        <v>416</v>
+      <c r="D7" s="77" t="s">
+        <v>515</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>417</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="C8" s="67" t="n">
+      <c r="B8" s="75" t="s">
+        <v>517</v>
+      </c>
+      <c r="C8" s="76" t="n">
         <v>235</v>
       </c>
-      <c r="D8" s="68" t="s">
-        <v>416</v>
+      <c r="D8" s="77" t="s">
+        <v>515</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>419</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>420</v>
+        <v>519</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -6504,13 +7366,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>421</v>
+        <v>520</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>423</v>
+        <v>522</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -6518,143 +7380,143 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="C12" s="69" t="n">
+        <v>523</v>
+      </c>
+      <c r="C12" s="78" t="n">
         <f aca="false">$C$7/4</f>
         <v>6</v>
       </c>
-      <c r="D12" s="70" t="n">
+      <c r="D12" s="79" t="n">
         <f aca="false">$C$7/4</f>
         <v>6</v>
       </c>
-      <c r="E12" s="70" t="n">
+      <c r="E12" s="79" t="n">
         <f aca="false">$C$7/4.5</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F12" s="71" t="s">
-        <v>425</v>
-      </c>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
+      <c r="F12" s="80" t="s">
+        <v>524</v>
+      </c>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="C13" s="69" t="n">
+        <v>525</v>
+      </c>
+      <c r="C13" s="78" t="n">
         <f aca="false">2*C12</f>
         <v>12</v>
       </c>
-      <c r="D13" s="70" t="n">
+      <c r="D13" s="79" t="n">
         <f aca="false">2*D12</f>
         <v>12</v>
       </c>
-      <c r="E13" s="70" t="n">
+      <c r="E13" s="79" t="n">
         <f aca="false">2*E12</f>
         <v>10.6666666666667</v>
       </c>
-      <c r="F13" s="72" t="s">
-        <v>427</v>
-      </c>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
+      <c r="F13" s="81" t="s">
+        <v>526</v>
+      </c>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="C14" s="73" t="s">
-        <v>429</v>
-      </c>
-      <c r="D14" s="70" t="n">
+        <v>527</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>528</v>
+      </c>
+      <c r="D14" s="79" t="n">
         <f aca="false">MIN($C$7/40,3/4*(0.49+$C$7/100))</f>
         <v>0.5475</v>
       </c>
-      <c r="E14" s="70" t="n">
+      <c r="E14" s="79" t="n">
         <f aca="false">MIN($C$7/45,3/4*(0.49+$C$7/100))</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="F14" s="71" t="s">
-        <v>430</v>
-      </c>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
+      <c r="F14" s="80" t="s">
+        <v>529</v>
+      </c>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>431</v>
-      </c>
-      <c r="C15" s="73" t="s">
-        <v>429</v>
-      </c>
-      <c r="D15" s="70" t="n">
+        <v>530</v>
+      </c>
+      <c r="C15" s="82" t="s">
+        <v>528</v>
+      </c>
+      <c r="D15" s="79" t="n">
         <f aca="false">1.5*D14</f>
         <v>0.82125</v>
       </c>
-      <c r="E15" s="70" t="n">
+      <c r="E15" s="79" t="n">
         <f aca="false">1.5*E14</f>
         <v>0.8</v>
       </c>
-      <c r="F15" s="71" t="s">
-        <v>432</v>
-      </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="80" t="s">
+        <v>531</v>
+      </c>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="74" t="s">
-        <v>433</v>
-      </c>
-      <c r="C16" s="75" t="n">
+      <c r="B16" s="83" t="s">
+        <v>532</v>
+      </c>
+      <c r="C16" s="84" t="n">
         <f aca="false">C12/C12</f>
         <v>1</v>
       </c>
-      <c r="D16" s="76" t="n">
+      <c r="D16" s="85" t="n">
         <f aca="false">D12/C12</f>
         <v>1</v>
       </c>
-      <c r="E16" s="76" t="n">
+      <c r="E16" s="85" t="n">
         <f aca="false">E12/C12</f>
         <v>0.888888888888889</v>
       </c>
-      <c r="F16" s="71" t="s">
-        <v>434</v>
-      </c>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
+      <c r="F16" s="80" t="s">
+        <v>533</v>
+      </c>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="74" t="s">
-        <v>435</v>
-      </c>
-      <c r="C17" s="77" t="str">
+      <c r="B17" s="83" t="s">
+        <v>534</v>
+      </c>
+      <c r="C17" s="86" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=45),"範囲内（18〜45）","範囲外：SS7は計算を続けるので要確認")</f>
         <v>範囲内（18〜45）</v>
       </c>
-      <c r="D17" s="78" t="str">
+      <c r="D17" s="87" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=36),"範囲内（18〜36）","範囲外：SS7がメッセージを出力")</f>
         <v>範囲内（18〜36）</v>
       </c>
-      <c r="E17" s="78" t="str">
+      <c r="E17" s="87" t="str">
         <f aca="false">IF(AND($C$7&gt;=18,$C$7&lt;=36),"範囲内（18〜36）","範囲外：SS7がメッセージを出力")</f>
         <v>範囲内（18〜36）</v>
       </c>
-      <c r="F17" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
+      <c r="F17" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>436</v>
+        <v>535</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -6669,13 +7531,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>437</v>
+        <v>536</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>438</v>
+        <v>537</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>423</v>
+        <v>522</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -6684,47 +7546,47 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="C21" s="79" t="n">
+        <v>538</v>
+      </c>
+      <c r="C21" s="88" t="n">
         <f aca="false">$C$8/1.5</f>
         <v>156.666666666667</v>
       </c>
-      <c r="D21" s="79" t="n">
+      <c r="D21" s="88" t="n">
         <f aca="false">1.5*C21</f>
         <v>235</v>
       </c>
-      <c r="E21" s="80" t="s">
-        <v>440</v>
-      </c>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
+      <c r="E21" s="89" t="s">
+        <v>539</v>
+      </c>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="C22" s="79" t="n">
+        <v>540</v>
+      </c>
+      <c r="C22" s="88" t="n">
         <f aca="false">$C$8/(1.5*SQRT(3))</f>
         <v>90.4515421730414</v>
       </c>
-      <c r="D22" s="79" t="n">
+      <c r="D22" s="88" t="n">
         <f aca="false">1.5*C22</f>
         <v>135.677313259562</v>
       </c>
-      <c r="E22" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
+      <c r="E22" s="89" t="s">
+        <v>541</v>
+      </c>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="89"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="81" t="s">
-        <v>443</v>
+      <c r="B24" s="90" t="s">
+        <v>542</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -6736,330 +7598,330 @@
     </row>
     <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>444</v>
+        <v>543</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>445</v>
+        <v>544</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>446</v>
+        <v>545</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>447</v>
+        <v>546</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>448</v>
+        <v>547</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>449</v>
+        <v>548</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>451</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="82" t="n">
+      <c r="B26" s="91" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="83" t="n">
+      <c r="C26" s="92" t="n">
         <f aca="false">B26/4</f>
         <v>4.5</v>
       </c>
-      <c r="D26" s="84" t="n">
+      <c r="D26" s="93" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",B26/4)</f>
         <v>4.5</v>
       </c>
-      <c r="E26" s="84" t="n">
+      <c r="E26" s="93" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",B26/4.5)</f>
         <v>4</v>
       </c>
-      <c r="F26" s="85" t="n">
+      <c r="F26" s="94" t="n">
         <f aca="false">IF(B26&gt;36,"—",C26-E26)</f>
         <v>0.5</v>
       </c>
-      <c r="G26" s="84" t="n">
+      <c r="G26" s="93" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",MIN(B26/40,3/4*(0.49+B26/100)))</f>
         <v>0.45</v>
       </c>
-      <c r="H26" s="84" t="n">
+      <c r="H26" s="93" t="n">
         <f aca="false">IF(B26&gt;36,"範囲外",MIN(B26/45,3/4*(0.49+B26/100)))</f>
         <v>0.4</v>
       </c>
-      <c r="I26" s="86" t="str">
+      <c r="I26" s="95" t="str">
         <f aca="false">IF(B26&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B26/40&lt;=3/4*(0.49+B26/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B26/45&lt;=3/4*(0.49+B26/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：Fc/40　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="82" t="n">
+      <c r="B27" s="91" t="n">
         <v>21</v>
       </c>
-      <c r="C27" s="83" t="n">
+      <c r="C27" s="92" t="n">
         <f aca="false">B27/4</f>
         <v>5.25</v>
       </c>
-      <c r="D27" s="84" t="n">
+      <c r="D27" s="93" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",B27/4)</f>
         <v>5.25</v>
       </c>
-      <c r="E27" s="84" t="n">
+      <c r="E27" s="93" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",B27/4.5)</f>
         <v>4.66666666666667</v>
       </c>
-      <c r="F27" s="85" t="n">
+      <c r="F27" s="94" t="n">
         <f aca="false">IF(B27&gt;36,"—",C27-E27)</f>
         <v>0.583333333333333</v>
       </c>
-      <c r="G27" s="84" t="n">
+      <c r="G27" s="93" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",MIN(B27/40,3/4*(0.49+B27/100)))</f>
         <v>0.525</v>
       </c>
-      <c r="H27" s="84" t="n">
+      <c r="H27" s="93" t="n">
         <f aca="false">IF(B27&gt;36,"範囲外",MIN(B27/45,3/4*(0.49+B27/100)))</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="I27" s="86" t="str">
+      <c r="I27" s="95" t="str">
         <f aca="false">IF(B27&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B27/40&lt;=3/4*(0.49+B27/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B27/45&lt;=3/4*(0.49+B27/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：Fc/40　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="82" t="n">
+      <c r="B28" s="91" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="83" t="n">
+      <c r="C28" s="92" t="n">
         <f aca="false">B28/4</f>
         <v>6</v>
       </c>
-      <c r="D28" s="84" t="n">
+      <c r="D28" s="93" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",B28/4)</f>
         <v>6</v>
       </c>
-      <c r="E28" s="84" t="n">
+      <c r="E28" s="93" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",B28/4.5)</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F28" s="85" t="n">
+      <c r="F28" s="94" t="n">
         <f aca="false">IF(B28&gt;36,"—",C28-E28)</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="G28" s="84" t="n">
+      <c r="G28" s="93" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",MIN(B28/40,3/4*(0.49+B28/100)))</f>
         <v>0.5475</v>
       </c>
-      <c r="H28" s="84" t="n">
+      <c r="H28" s="93" t="n">
         <f aca="false">IF(B28&gt;36,"範囲外",MIN(B28/45,3/4*(0.49+B28/100)))</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="I28" s="86" t="str">
+      <c r="I28" s="95" t="str">
         <f aca="false">IF(B28&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B28/40&lt;=3/4*(0.49+B28/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B28/45&lt;=3/4*(0.49+B28/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：Fc/45</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="82" t="n">
+      <c r="B29" s="91" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="83" t="n">
+      <c r="C29" s="92" t="n">
         <f aca="false">B29/4</f>
         <v>6.75</v>
       </c>
-      <c r="D29" s="84" t="n">
+      <c r="D29" s="93" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",B29/4)</f>
         <v>6.75</v>
       </c>
-      <c r="E29" s="84" t="n">
+      <c r="E29" s="93" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",B29/4.5)</f>
         <v>6</v>
       </c>
-      <c r="F29" s="85" t="n">
+      <c r="F29" s="94" t="n">
         <f aca="false">IF(B29&gt;36,"—",C29-E29)</f>
         <v>0.75</v>
       </c>
-      <c r="G29" s="84" t="n">
+      <c r="G29" s="93" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",MIN(B29/40,3/4*(0.49+B29/100)))</f>
         <v>0.57</v>
       </c>
-      <c r="H29" s="84" t="n">
+      <c r="H29" s="93" t="n">
         <f aca="false">IF(B29&gt;36,"範囲外",MIN(B29/45,3/4*(0.49+B29/100)))</f>
         <v>0.57</v>
       </c>
-      <c r="I29" s="86" t="str">
+      <c r="I29" s="95" t="str">
         <f aca="false">IF(B29&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B29/40&lt;=3/4*(0.49+B29/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B29/45&lt;=3/4*(0.49+B29/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="82" t="n">
+      <c r="B30" s="91" t="n">
         <v>30</v>
       </c>
-      <c r="C30" s="83" t="n">
+      <c r="C30" s="92" t="n">
         <f aca="false">B30/4</f>
         <v>7.5</v>
       </c>
-      <c r="D30" s="84" t="n">
+      <c r="D30" s="93" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",B30/4)</f>
         <v>7.5</v>
       </c>
-      <c r="E30" s="84" t="n">
+      <c r="E30" s="93" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",B30/4.5)</f>
         <v>6.66666666666667</v>
       </c>
-      <c r="F30" s="85" t="n">
+      <c r="F30" s="94" t="n">
         <f aca="false">IF(B30&gt;36,"—",C30-E30)</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G30" s="84" t="n">
+      <c r="G30" s="93" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",MIN(B30/40,3/4*(0.49+B30/100)))</f>
         <v>0.5925</v>
       </c>
-      <c r="H30" s="84" t="n">
+      <c r="H30" s="93" t="n">
         <f aca="false">IF(B30&gt;36,"範囲外",MIN(B30/45,3/4*(0.49+B30/100)))</f>
         <v>0.5925</v>
       </c>
-      <c r="I30" s="86" t="str">
+      <c r="I30" s="95" t="str">
         <f aca="false">IF(B30&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B30/40&lt;=3/4*(0.49+B30/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B30/45&lt;=3/4*(0.49+B30/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="82" t="n">
+      <c r="B31" s="91" t="n">
         <v>33</v>
       </c>
-      <c r="C31" s="83" t="n">
+      <c r="C31" s="92" t="n">
         <f aca="false">B31/4</f>
         <v>8.25</v>
       </c>
-      <c r="D31" s="84" t="n">
+      <c r="D31" s="93" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",B31/4)</f>
         <v>8.25</v>
       </c>
-      <c r="E31" s="84" t="n">
+      <c r="E31" s="93" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",B31/4.5)</f>
         <v>7.33333333333333</v>
       </c>
-      <c r="F31" s="85" t="n">
+      <c r="F31" s="94" t="n">
         <f aca="false">IF(B31&gt;36,"—",C31-E31)</f>
         <v>0.916666666666667</v>
       </c>
-      <c r="G31" s="84" t="n">
+      <c r="G31" s="93" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",MIN(B31/40,3/4*(0.49+B31/100)))</f>
         <v>0.615</v>
       </c>
-      <c r="H31" s="84" t="n">
+      <c r="H31" s="93" t="n">
         <f aca="false">IF(B31&gt;36,"範囲外",MIN(B31/45,3/4*(0.49+B31/100)))</f>
         <v>0.615</v>
       </c>
-      <c r="I31" s="86" t="str">
+      <c r="I31" s="95" t="str">
         <f aca="false">IF(B31&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B31/40&lt;=3/4*(0.49+B31/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B31/45&lt;=3/4*(0.49+B31/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="82" t="n">
+      <c r="B32" s="91" t="n">
         <v>36</v>
       </c>
-      <c r="C32" s="83" t="n">
+      <c r="C32" s="92" t="n">
         <f aca="false">B32/4</f>
         <v>9</v>
       </c>
-      <c r="D32" s="84" t="n">
+      <c r="D32" s="93" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",B32/4)</f>
         <v>9</v>
       </c>
-      <c r="E32" s="84" t="n">
+      <c r="E32" s="93" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",B32/4.5)</f>
         <v>8</v>
       </c>
-      <c r="F32" s="85" t="n">
+      <c r="F32" s="94" t="n">
         <f aca="false">IF(B32&gt;36,"—",C32-E32)</f>
         <v>1</v>
       </c>
-      <c r="G32" s="84" t="n">
+      <c r="G32" s="93" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",MIN(B32/40,3/4*(0.49+B32/100)))</f>
         <v>0.6375</v>
       </c>
-      <c r="H32" s="84" t="n">
+      <c r="H32" s="93" t="n">
         <f aca="false">IF(B32&gt;36,"範囲外",MIN(B32/45,3/4*(0.49+B32/100)))</f>
         <v>0.6375</v>
       </c>
-      <c r="I32" s="86" t="str">
+      <c r="I32" s="95" t="str">
         <f aca="false">IF(B32&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B32/40&lt;=3/4*(0.49+B32/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B32/45&lt;=3/4*(0.49+B32/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>空掘り：3/4(0.49＋Fc/100)　／　泥水中：3/4(0.49＋Fc/100)</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="82" t="n">
+      <c r="B33" s="91" t="n">
         <v>40</v>
       </c>
-      <c r="C33" s="83" t="n">
+      <c r="C33" s="92" t="n">
         <f aca="false">B33/4</f>
         <v>10</v>
       </c>
-      <c r="D33" s="84" t="str">
+      <c r="D33" s="93" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",B33/4)</f>
         <v>範囲外</v>
       </c>
-      <c r="E33" s="84" t="str">
+      <c r="E33" s="93" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",B33/4.5)</f>
         <v>範囲外</v>
       </c>
-      <c r="F33" s="85" t="str">
+      <c r="F33" s="94" t="str">
         <f aca="false">IF(B33&gt;36,"—",C33-E33)</f>
         <v>—</v>
       </c>
-      <c r="G33" s="84" t="str">
+      <c r="G33" s="93" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",MIN(B33/40,3/4*(0.49+B33/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="H33" s="84" t="str">
+      <c r="H33" s="93" t="str">
         <f aca="false">IF(B33&gt;36,"範囲外",MIN(B33/45,3/4*(0.49+B33/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="I33" s="86" t="str">
+      <c r="I33" s="95" t="str">
         <f aca="false">IF(B33&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B33/40&lt;=3/4*(0.49+B33/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B33/45&lt;=3/4*(0.49+B33/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>SB協会の範囲外（Fc＞36）</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="82" t="n">
+      <c r="B34" s="91" t="n">
         <v>45</v>
       </c>
-      <c r="C34" s="83" t="n">
+      <c r="C34" s="92" t="n">
         <f aca="false">B34/4</f>
         <v>11.25</v>
       </c>
-      <c r="D34" s="84" t="str">
+      <c r="D34" s="93" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",B34/4)</f>
         <v>範囲外</v>
       </c>
-      <c r="E34" s="84" t="str">
+      <c r="E34" s="93" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",B34/4.5)</f>
         <v>範囲外</v>
       </c>
-      <c r="F34" s="85" t="str">
+      <c r="F34" s="94" t="str">
         <f aca="false">IF(B34&gt;36,"—",C34-E34)</f>
         <v>—</v>
       </c>
-      <c r="G34" s="84" t="str">
+      <c r="G34" s="93" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",MIN(B34/40,3/4*(0.49+B34/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="H34" s="84" t="str">
+      <c r="H34" s="93" t="str">
         <f aca="false">IF(B34&gt;36,"範囲外",MIN(B34/45,3/4*(0.49+B34/100)))</f>
         <v>範囲外</v>
       </c>
-      <c r="I34" s="86" t="str">
+      <c r="I34" s="95" t="str">
         <f aca="false">IF(B34&gt;36,"SB協会の範囲外（Fc＞36）","空掘り："&amp;IF(B34/40&lt;=3/4*(0.49+B34/100),"Fc/40","3/4(0.49＋Fc/100)")&amp;"　／　泥水中："&amp;IF(B34/45&lt;=3/4*(0.49+B34/100),"Fc/45","3/4(0.49＋Fc/100)"))</f>
         <v>SB協会の範囲外（Fc＞36）</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>452</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -7114,22 +7976,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="36" t="s">
-        <v>453</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>454</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="65" t="s">
-        <v>455</v>
+      <c r="B4" s="74" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>414</v>
+        <v>513</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -7138,126 +8000,126 @@
       <c r="G6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="66" t="s">
-        <v>456</v>
-      </c>
-      <c r="C7" s="87" t="n">
+      <c r="B7" s="75" t="s">
+        <v>555</v>
+      </c>
+      <c r="C7" s="96" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="68" t="s">
-        <v>457</v>
-      </c>
-      <c r="F7" s="88" t="s">
-        <v>458</v>
-      </c>
-      <c r="G7" s="88"/>
+      <c r="D7" s="77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F7" s="97" t="s">
+        <v>557</v>
+      </c>
+      <c r="G7" s="97"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="66" t="s">
-        <v>459</v>
-      </c>
-      <c r="C8" s="87" t="n">
+      <c r="B8" s="75" t="s">
+        <v>558</v>
+      </c>
+      <c r="C8" s="96" t="n">
         <v>16</v>
       </c>
-      <c r="D8" s="68" t="s">
-        <v>457</v>
-      </c>
-      <c r="F8" s="88" t="s">
-        <v>458</v>
-      </c>
-      <c r="G8" s="88"/>
+      <c r="D8" s="77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F8" s="97" t="s">
+        <v>557</v>
+      </c>
+      <c r="G8" s="97"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="66" t="s">
-        <v>460</v>
-      </c>
-      <c r="C9" s="89" t="n">
+      <c r="B9" s="75" t="s">
+        <v>559</v>
+      </c>
+      <c r="C9" s="98" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="68" t="s">
-        <v>457</v>
-      </c>
-      <c r="F9" s="88" t="s">
-        <v>461</v>
-      </c>
-      <c r="G9" s="88"/>
+      <c r="D9" s="77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F9" s="97" t="s">
+        <v>560</v>
+      </c>
+      <c r="G9" s="97"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="C10" s="87" t="n">
+      <c r="B10" s="75" t="s">
+        <v>517</v>
+      </c>
+      <c r="C10" s="96" t="n">
         <v>235</v>
       </c>
-      <c r="D10" s="68" t="s">
-        <v>416</v>
-      </c>
-      <c r="F10" s="88" t="s">
-        <v>462</v>
-      </c>
-      <c r="G10" s="88"/>
+      <c r="D10" s="77" t="s">
+        <v>515</v>
+      </c>
+      <c r="F10" s="97" t="s">
+        <v>561</v>
+      </c>
+      <c r="G10" s="97"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="66" t="s">
-        <v>463</v>
-      </c>
-      <c r="C11" s="89" t="n">
+      <c r="B11" s="75" t="s">
+        <v>562</v>
+      </c>
+      <c r="C11" s="98" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="90" t="s">
-        <v>464</v>
-      </c>
-      <c r="F11" s="88" t="s">
-        <v>465</v>
-      </c>
-      <c r="G11" s="88"/>
+      <c r="D11" s="99" t="s">
+        <v>563</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>564</v>
+      </c>
+      <c r="G11" s="97"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="66" t="s">
-        <v>466</v>
-      </c>
-      <c r="C12" s="87" t="n">
+      <c r="B12" s="75" t="s">
+        <v>565</v>
+      </c>
+      <c r="C12" s="96" t="n">
         <v>24</v>
       </c>
-      <c r="D12" s="68" t="s">
-        <v>416</v>
-      </c>
-      <c r="F12" s="88" t="s">
-        <v>467</v>
-      </c>
-      <c r="G12" s="88"/>
+      <c r="D12" s="77" t="s">
+        <v>515</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>566</v>
+      </c>
+      <c r="G12" s="97"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="66" t="s">
-        <v>468</v>
-      </c>
-      <c r="C13" s="87" t="n">
+      <c r="B13" s="75" t="s">
+        <v>567</v>
+      </c>
+      <c r="C13" s="96" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="68" t="s">
-        <v>457</v>
-      </c>
-      <c r="F13" s="88" t="s">
-        <v>467</v>
-      </c>
-      <c r="G13" s="88"/>
+      <c r="D13" s="77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F13" s="97" t="s">
+        <v>566</v>
+      </c>
+      <c r="G13" s="97"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="91" t="s">
-        <v>469</v>
-      </c>
-      <c r="C14" s="89" t="n">
+      <c r="B14" s="100" t="s">
+        <v>568</v>
+      </c>
+      <c r="C14" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="68"/>
-      <c r="F14" s="92" t="s">
-        <v>470</v>
-      </c>
-      <c r="G14" s="92"/>
+      <c r="D14" s="77"/>
+      <c r="F14" s="101" t="s">
+        <v>569</v>
+      </c>
+      <c r="G14" s="101"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>471</v>
+        <v>570</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -7270,10 +8132,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>472</v>
+        <v>571</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>473</v>
+        <v>572</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -7281,143 +8143,143 @@
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="27" t="s">
-        <v>474</v>
-      </c>
-      <c r="C17" s="93" t="n">
+        <v>573</v>
+      </c>
+      <c r="C17" s="102" t="n">
         <f aca="false">C7-2*C9</f>
         <v>1198</v>
       </c>
-      <c r="D17" s="62" t="s">
-        <v>457</v>
-      </c>
-      <c r="E17" s="94" t="s">
-        <v>475</v>
-      </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
+      <c r="D17" s="71" t="s">
+        <v>556</v>
+      </c>
+      <c r="E17" s="103" t="s">
+        <v>574</v>
+      </c>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="C18" s="93" t="n">
+        <v>575</v>
+      </c>
+      <c r="C18" s="102" t="n">
         <f aca="false">C8-C9</f>
         <v>15</v>
       </c>
-      <c r="D18" s="62" t="s">
-        <v>457</v>
-      </c>
-      <c r="E18" s="94" t="s">
-        <v>477</v>
-      </c>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
+      <c r="D18" s="71" t="s">
+        <v>556</v>
+      </c>
+      <c r="E18" s="103" t="s">
+        <v>576</v>
+      </c>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="27" t="s">
-        <v>478</v>
-      </c>
-      <c r="C19" s="93" t="n">
+        <v>577</v>
+      </c>
+      <c r="C19" s="102" t="n">
         <f aca="false">C17-2*C18</f>
         <v>1168</v>
       </c>
-      <c r="D19" s="62" t="s">
-        <v>457</v>
-      </c>
-      <c r="E19" s="94" t="s">
-        <v>479</v>
-      </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
+      <c r="D19" s="71" t="s">
+        <v>556</v>
+      </c>
+      <c r="E19" s="103" t="s">
+        <v>578</v>
+      </c>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="27" t="s">
-        <v>480</v>
-      </c>
-      <c r="C20" s="95" t="n">
+        <v>579</v>
+      </c>
+      <c r="C20" s="104" t="n">
         <f aca="false">PI()/4*(C17^2-C19^2)</f>
         <v>55747.5616379509</v>
       </c>
-      <c r="D20" s="62" t="s">
-        <v>481</v>
-      </c>
-      <c r="E20" s="94" t="s">
-        <v>482</v>
-      </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
+      <c r="D20" s="71" t="s">
+        <v>580</v>
+      </c>
+      <c r="E20" s="103" t="s">
+        <v>581</v>
+      </c>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="27" t="s">
-        <v>483</v>
-      </c>
-      <c r="C21" s="95" t="n">
+        <v>582</v>
+      </c>
+      <c r="C21" s="104" t="n">
         <f aca="false">PI()/32*(C17^4-C19^4)/C17</f>
         <v>16283523.0572836</v>
       </c>
-      <c r="D21" s="62" t="s">
-        <v>484</v>
-      </c>
-      <c r="E21" s="94" t="s">
-        <v>485</v>
-      </c>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
+      <c r="D21" s="71" t="s">
+        <v>583</v>
+      </c>
+      <c r="E21" s="103" t="s">
+        <v>584</v>
+      </c>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="27" t="s">
-        <v>486</v>
-      </c>
-      <c r="C22" s="96" t="n">
+        <v>585</v>
+      </c>
+      <c r="C22" s="105" t="n">
         <f aca="false">C10/1.5</f>
         <v>156.666666666667</v>
       </c>
-      <c r="D22" s="62" t="s">
-        <v>416</v>
-      </c>
-      <c r="E22" s="94" t="s">
-        <v>487</v>
-      </c>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
+      <c r="D22" s="71" t="s">
+        <v>515</v>
+      </c>
+      <c r="E22" s="103" t="s">
+        <v>586</v>
+      </c>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="C23" s="96" t="n">
+        <v>587</v>
+      </c>
+      <c r="C23" s="105" t="n">
         <f aca="false">C10/(1.5*SQRT(3))</f>
         <v>90.4515421730414</v>
       </c>
-      <c r="D23" s="62" t="s">
-        <v>416</v>
-      </c>
-      <c r="E23" s="94" t="s">
-        <v>489</v>
-      </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94"/>
+      <c r="D23" s="71" t="s">
+        <v>515</v>
+      </c>
+      <c r="E23" s="103" t="s">
+        <v>588</v>
+      </c>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="27" t="s">
-        <v>490</v>
-      </c>
-      <c r="C24" s="96" t="n">
+        <v>589</v>
+      </c>
+      <c r="C24" s="105" t="n">
         <f aca="false">C10*C11</f>
         <v>235</v>
       </c>
-      <c r="D24" s="62" t="s">
-        <v>416</v>
-      </c>
-      <c r="E24" s="94" t="s">
-        <v>491</v>
-      </c>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
+      <c r="D24" s="71" t="s">
+        <v>515</v>
+      </c>
+      <c r="E24" s="103" t="s">
+        <v>590</v>
+      </c>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>492</v>
+        <v>591</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7436,233 +8298,233 @@
         <v>11</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>473</v>
+        <v>572</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>493</v>
+        <v>592</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>494</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="C28" s="97" t="n">
+        <v>594</v>
+      </c>
+      <c r="C28" s="106" t="n">
         <f aca="false">C21*C22/1000000</f>
         <v>2551.08527897442</v>
       </c>
-      <c r="D28" s="98" t="n">
+      <c r="D28" s="107" t="n">
         <f aca="false">C21*C22/1000000</f>
         <v>2551.08527897442</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="F28" s="71" t="s">
-        <v>497</v>
-      </c>
-      <c r="G28" s="71" t="s">
-        <v>498</v>
+        <v>595</v>
+      </c>
+      <c r="F28" s="80" t="s">
+        <v>596</v>
+      </c>
+      <c r="G28" s="80" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="24" t="s">
-        <v>499</v>
-      </c>
-      <c r="C29" s="97" t="n">
+        <v>598</v>
+      </c>
+      <c r="C29" s="106" t="n">
         <f aca="false">1.5*C28</f>
         <v>3826.62791846163</v>
       </c>
-      <c r="D29" s="98" t="n">
+      <c r="D29" s="107" t="n">
         <f aca="false">1.5*D28</f>
         <v>3826.62791846163</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="F29" s="72" t="s">
-        <v>500</v>
-      </c>
-      <c r="G29" s="72" t="s">
-        <v>501</v>
+        <v>595</v>
+      </c>
+      <c r="F29" s="81" t="s">
+        <v>599</v>
+      </c>
+      <c r="G29" s="81" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="C30" s="97" t="n">
+        <v>601</v>
+      </c>
+      <c r="C30" s="106" t="n">
         <f aca="false">C20/2*C23/1000</f>
         <v>2521.22646126967</v>
       </c>
-      <c r="D30" s="98" t="n">
+      <c r="D30" s="107" t="n">
         <f aca="false">C20/2*C23/1000</f>
         <v>2521.22646126967</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="F30" s="71" t="s">
-        <v>504</v>
-      </c>
-      <c r="G30" s="72" t="s">
+        <v>602</v>
+      </c>
+      <c r="F30" s="80" t="s">
+        <v>603</v>
+      </c>
+      <c r="G30" s="81" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="24" t="s">
-        <v>505</v>
-      </c>
-      <c r="C31" s="97" t="n">
+        <v>604</v>
+      </c>
+      <c r="C31" s="106" t="n">
         <f aca="false">1.5*C30</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="D31" s="98" t="n">
+      <c r="D31" s="107" t="n">
         <f aca="false">1.5*D30</f>
         <v>3781.8396919045</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="F31" s="72" t="s">
-        <v>500</v>
-      </c>
-      <c r="G31" s="72" t="s">
+        <v>602</v>
+      </c>
+      <c r="F31" s="81" t="s">
+        <v>599</v>
+      </c>
+      <c r="G31" s="81" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="24" t="s">
-        <v>506</v>
-      </c>
-      <c r="C32" s="97" t="n">
+        <v>605</v>
+      </c>
+      <c r="C32" s="106" t="n">
         <f aca="false">C20/2*C24/SQRT(3)/1000</f>
         <v>3781.8396919045</v>
       </c>
-      <c r="D32" s="98" t="n">
+      <c r="D32" s="107" t="n">
         <f aca="false">C20*(C24/SQRT(3))*(1/C14)/1000</f>
         <v>3781.8396919045</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="F32" s="71" t="s">
-        <v>507</v>
-      </c>
-      <c r="G32" s="71" t="s">
-        <v>508</v>
+        <v>602</v>
+      </c>
+      <c r="F32" s="80" t="s">
+        <v>606</v>
+      </c>
+      <c r="G32" s="80" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="C33" s="97" t="n">
+        <v>608</v>
+      </c>
+      <c r="C33" s="106" t="n">
         <f aca="false">C12*C7*C13/1000</f>
         <v>2880</v>
       </c>
-      <c r="D33" s="99" t="s">
-        <v>429</v>
+      <c r="D33" s="108" t="s">
+        <v>528</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="F33" s="71" t="s">
-        <v>510</v>
-      </c>
-      <c r="G33" s="71" t="s">
-        <v>511</v>
+        <v>602</v>
+      </c>
+      <c r="F33" s="80" t="s">
+        <v>609</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="24" t="s">
-        <v>512</v>
-      </c>
-      <c r="C34" s="100" t="n">
+        <v>611</v>
+      </c>
+      <c r="C34" s="109" t="n">
         <f aca="false">MIN(C32,C33)</f>
         <v>2880</v>
       </c>
-      <c r="D34" s="101" t="n">
+      <c r="D34" s="110" t="n">
         <f aca="false">D32</f>
         <v>3781.8396919045</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="F34" s="71" t="s">
-        <v>513</v>
-      </c>
-      <c r="G34" s="72"/>
+        <v>602</v>
+      </c>
+      <c r="F34" s="80" t="s">
+        <v>612</v>
+      </c>
+      <c r="G34" s="81"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="74" t="s">
-        <v>514</v>
-      </c>
-      <c r="C35" s="97" t="str">
+      <c r="B35" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="C35" s="106" t="str">
         <f aca="false">IF(C33&lt;C32,"杭頭接合部で決定","鋼管で決定")</f>
         <v>杭頭接合部で決定</v>
       </c>
-      <c r="D35" s="99" t="s">
-        <v>515</v>
+      <c r="D35" s="108" t="s">
+        <v>614</v>
       </c>
       <c r="E35" s="14"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="71" t="s">
-        <v>516</v>
+      <c r="F35" s="81"/>
+      <c r="G35" s="80" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="24" t="s">
-        <v>517</v>
-      </c>
-      <c r="C36" s="102" t="s">
-        <v>518</v>
-      </c>
-      <c r="D36" s="98" t="n">
+        <v>616</v>
+      </c>
+      <c r="C36" s="111" t="s">
+        <v>617</v>
+      </c>
+      <c r="D36" s="107" t="n">
         <f aca="false">(C17-C18)^2*C18*C24/1000000</f>
         <v>4933.198725</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="F36" s="71" t="s">
-        <v>519</v>
-      </c>
-      <c r="G36" s="71" t="s">
-        <v>520</v>
+        <v>595</v>
+      </c>
+      <c r="F36" s="80" t="s">
+        <v>618</v>
+      </c>
+      <c r="G36" s="80" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="88" t="s">
-        <v>521</v>
-      </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88"/>
+      <c r="B38" s="97" t="s">
+        <v>620</v>
+      </c>
+      <c r="C38" s="97"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="97"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="92" t="s">
-        <v>522</v>
-      </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="92"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
+      <c r="B39" s="101" t="s">
+        <v>621</v>
+      </c>
+      <c r="C39" s="101"/>
+      <c r="D39" s="101"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="101"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="92" t="s">
-        <v>523</v>
-      </c>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
+      <c r="B40" s="101" t="s">
+        <v>622</v>
+      </c>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="101"/>
+      <c r="F40" s="101"/>
+      <c r="G40" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -7721,7 +8583,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="36" t="s">
-        <v>524</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7730,8 +8592,8 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="65" t="s">
-        <v>525</v>
+      <c r="A3" s="74" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7745,382 +8607,382 @@
         <v>8</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>526</v>
+        <v>625</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>527</v>
+        <v>626</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>528</v>
+        <v>627</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>529</v>
+        <v>628</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>530</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="103" t="s">
-        <v>531</v>
+      <c r="B6" s="112" t="s">
+        <v>199</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>532</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="104" t="s">
-        <v>533</v>
-      </c>
-      <c r="F6" s="105" t="s">
-        <v>534</v>
+        <v>630</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>332</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>631</v>
+      </c>
+      <c r="F6" s="114" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="103" t="s">
-        <v>531</v>
+      <c r="B7" s="112" t="s">
+        <v>199</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>535</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>536</v>
-      </c>
-      <c r="E7" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F7" s="105"/>
+        <v>633</v>
+      </c>
+      <c r="D7" s="80" t="s">
+        <v>634</v>
+      </c>
+      <c r="E7" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F7" s="114"/>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="103" t="s">
-        <v>531</v>
+      <c r="B8" s="112" t="s">
+        <v>199</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>538</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>247</v>
-      </c>
-      <c r="E8" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F8" s="105"/>
+        <v>636</v>
+      </c>
+      <c r="D8" s="80" t="s">
+        <v>346</v>
+      </c>
+      <c r="E8" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F8" s="114"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="103" t="s">
-        <v>531</v>
+      <c r="B9" s="112" t="s">
+        <v>199</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>539</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>540</v>
-      </c>
-      <c r="E9" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F9" s="105"/>
+        <v>637</v>
+      </c>
+      <c r="D9" s="81" t="s">
+        <v>638</v>
+      </c>
+      <c r="E9" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F9" s="114"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="103" t="s">
-        <v>531</v>
+      <c r="B10" s="112" t="s">
+        <v>199</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>541</v>
-      </c>
-      <c r="D10" s="71" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F10" s="105"/>
+        <v>639</v>
+      </c>
+      <c r="D10" s="80" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F10" s="114"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="103" t="s">
-        <v>531</v>
+      <c r="B11" s="112" t="s">
+        <v>199</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>542</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>323</v>
-      </c>
-      <c r="E11" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F11" s="105"/>
+        <v>640</v>
+      </c>
+      <c r="D11" s="81" t="s">
+        <v>422</v>
+      </c>
+      <c r="E11" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F11" s="114"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="106" t="s">
-        <v>543</v>
+      <c r="B12" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D12" s="71" t="s">
-        <v>545</v>
-      </c>
-      <c r="E12" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F12" s="105"/>
+        <v>641</v>
+      </c>
+      <c r="D12" s="80" t="s">
+        <v>642</v>
+      </c>
+      <c r="E12" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F12" s="114"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="106" t="s">
-        <v>543</v>
+      <c r="B13" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>546</v>
-      </c>
-      <c r="D13" s="71" t="s">
-        <v>547</v>
-      </c>
-      <c r="E13" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F13" s="105"/>
+        <v>643</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>644</v>
+      </c>
+      <c r="E13" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F13" s="114"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="106" t="s">
-        <v>543</v>
+      <c r="B14" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>548</v>
-      </c>
-      <c r="D14" s="71" t="s">
-        <v>342</v>
-      </c>
-      <c r="E14" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F14" s="105"/>
+        <v>645</v>
+      </c>
+      <c r="D14" s="80" t="s">
+        <v>441</v>
+      </c>
+      <c r="E14" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F14" s="114"/>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="106" t="s">
-        <v>543</v>
+      <c r="B15" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>549</v>
-      </c>
-      <c r="D15" s="71" t="s">
-        <v>550</v>
-      </c>
-      <c r="E15" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F15" s="105"/>
+        <v>646</v>
+      </c>
+      <c r="D15" s="80" t="s">
+        <v>647</v>
+      </c>
+      <c r="E15" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F15" s="114"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="106" t="s">
-        <v>543</v>
+      <c r="B16" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="D16" s="72" t="s">
-        <v>347</v>
-      </c>
-      <c r="E16" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F16" s="105"/>
+        <v>648</v>
+      </c>
+      <c r="D16" s="81" t="s">
+        <v>446</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F16" s="114"/>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="106" t="s">
-        <v>543</v>
+      <c r="B17" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>552</v>
-      </c>
-      <c r="D17" s="72" t="s">
-        <v>553</v>
-      </c>
-      <c r="E17" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F17" s="105"/>
+        <v>649</v>
+      </c>
+      <c r="D17" s="81" t="s">
+        <v>650</v>
+      </c>
+      <c r="E17" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F17" s="114"/>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="107" t="s">
-        <v>554</v>
+      <c r="B18" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>555</v>
-      </c>
-      <c r="D18" s="71" t="s">
-        <v>226</v>
-      </c>
-      <c r="E18" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F18" s="105"/>
+        <v>651</v>
+      </c>
+      <c r="D18" s="80" t="s">
+        <v>325</v>
+      </c>
+      <c r="E18" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F18" s="114"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="107" t="s">
-        <v>554</v>
+      <c r="B19" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>556</v>
-      </c>
-      <c r="D19" s="71" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F19" s="105"/>
+        <v>652</v>
+      </c>
+      <c r="D19" s="80" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F19" s="114"/>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="107" t="s">
-        <v>554</v>
+      <c r="B20" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>557</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>558</v>
-      </c>
-      <c r="E20" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F20" s="105"/>
+        <v>653</v>
+      </c>
+      <c r="D20" s="81" t="s">
+        <v>654</v>
+      </c>
+      <c r="E20" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F20" s="114"/>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="107" t="s">
-        <v>554</v>
+      <c r="B21" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>559</v>
-      </c>
-      <c r="D21" s="72" t="s">
-        <v>560</v>
-      </c>
-      <c r="E21" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F21" s="105"/>
+        <v>655</v>
+      </c>
+      <c r="D21" s="81" t="s">
+        <v>656</v>
+      </c>
+      <c r="E21" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F21" s="114"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="107" t="s">
-        <v>554</v>
+      <c r="B22" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>561</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>562</v>
-      </c>
-      <c r="E22" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F22" s="105"/>
+        <v>657</v>
+      </c>
+      <c r="D22" s="81" t="s">
+        <v>658</v>
+      </c>
+      <c r="E22" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F22" s="114"/>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="107" t="s">
-        <v>554</v>
+      <c r="B23" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>563</v>
-      </c>
-      <c r="D23" s="71" t="s">
-        <v>564</v>
-      </c>
-      <c r="E23" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F23" s="105"/>
+        <v>659</v>
+      </c>
+      <c r="D23" s="80" t="s">
+        <v>660</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F23" s="114"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="107" t="s">
-        <v>554</v>
+      <c r="B24" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>565</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>566</v>
-      </c>
-      <c r="E24" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F24" s="105"/>
+        <v>661</v>
+      </c>
+      <c r="D24" s="80" t="s">
+        <v>662</v>
+      </c>
+      <c r="E24" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F24" s="114"/>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="107" t="s">
-        <v>554</v>
+      <c r="B25" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>567</v>
-      </c>
-      <c r="D25" s="72" t="s">
-        <v>568</v>
-      </c>
-      <c r="E25" s="104" t="s">
-        <v>537</v>
-      </c>
-      <c r="F25" s="105"/>
+        <v>663</v>
+      </c>
+      <c r="D25" s="81" t="s">
+        <v>664</v>
+      </c>
+      <c r="E25" s="113" t="s">
+        <v>635</v>
+      </c>
+      <c r="F25" s="114"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E6:E25">
@@ -8168,360 +9030,360 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="108" t="s">
-        <v>569</v>
+      <c r="B3" s="115" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>571</v>
+        <v>666</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>572</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="109" t="s">
-        <v>573</v>
+      <c r="B6" s="116" t="s">
+        <v>668</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>574</v>
-      </c>
-      <c r="D6" s="110" t="s">
-        <v>531</v>
+        <v>669</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="109" t="s">
-        <v>575</v>
+      <c r="B7" s="116" t="s">
+        <v>670</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>576</v>
-      </c>
-      <c r="D7" s="110" t="s">
-        <v>531</v>
+        <v>671</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="109" t="s">
-        <v>577</v>
+      <c r="B8" s="116" t="s">
+        <v>203</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="D8" s="106" t="s">
-        <v>543</v>
+        <v>672</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="109" t="s">
-        <v>579</v>
+      <c r="B9" s="116" t="s">
+        <v>207</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>580</v>
-      </c>
-      <c r="D9" s="107" t="s">
-        <v>554</v>
+        <v>673</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="109" t="s">
-        <v>581</v>
+      <c r="B10" s="116" t="s">
+        <v>211</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>582</v>
-      </c>
-      <c r="D10" s="110" t="s">
-        <v>531</v>
+        <v>674</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="109" t="s">
-        <v>583</v>
+      <c r="B11" s="116" t="s">
+        <v>675</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>584</v>
-      </c>
-      <c r="D11" s="106" t="s">
-        <v>543</v>
+        <v>676</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="109" t="s">
-        <v>585</v>
+      <c r="B12" s="116" t="s">
+        <v>677</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>586</v>
-      </c>
-      <c r="D12" s="107" t="s">
-        <v>554</v>
+        <v>678</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="109" t="s">
-        <v>587</v>
+      <c r="B13" s="116" t="s">
+        <v>679</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>588</v>
-      </c>
-      <c r="D13" s="106" t="s">
-        <v>543</v>
+        <v>680</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="109" t="s">
-        <v>589</v>
+      <c r="B14" s="116" t="s">
+        <v>224</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>590</v>
-      </c>
-      <c r="D14" s="106" t="s">
-        <v>543</v>
+        <v>681</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="109" t="s">
-        <v>591</v>
+      <c r="B15" s="116" t="s">
+        <v>227</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>592</v>
-      </c>
-      <c r="D15" s="110" t="s">
-        <v>531</v>
+        <v>682</v>
+      </c>
+      <c r="D15" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="109" t="s">
-        <v>593</v>
+      <c r="B16" s="116" t="s">
+        <v>683</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>594</v>
-      </c>
-      <c r="D16" s="110" t="s">
-        <v>531</v>
+        <v>684</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="109" t="s">
-        <v>595</v>
+      <c r="B17" s="116" t="s">
+        <v>685</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>596</v>
+        <v>686</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>597</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="109" t="s">
-        <v>598</v>
+      <c r="B18" s="116" t="s">
+        <v>687</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>599</v>
-      </c>
-      <c r="D18" s="110" t="s">
-        <v>531</v>
+        <v>688</v>
+      </c>
+      <c r="D18" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="109" t="s">
-        <v>600</v>
+      <c r="B19" s="116" t="s">
+        <v>689</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>601</v>
-      </c>
-      <c r="D19" s="110" t="s">
-        <v>531</v>
+        <v>690</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="109" t="s">
-        <v>602</v>
+      <c r="B20" s="116" t="s">
+        <v>240</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="110" t="s">
-        <v>531</v>
+        <v>360</v>
+      </c>
+      <c r="D20" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="109" t="s">
-        <v>603</v>
+      <c r="B21" s="116" t="s">
+        <v>691</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>604</v>
-      </c>
-      <c r="D21" s="110" t="s">
-        <v>531</v>
+        <v>236</v>
+      </c>
+      <c r="D21" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="109" t="s">
-        <v>605</v>
+      <c r="B22" s="116" t="s">
+        <v>230</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>606</v>
-      </c>
-      <c r="D22" s="110" t="s">
-        <v>531</v>
+        <v>692</v>
+      </c>
+      <c r="D22" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="109" t="s">
-        <v>607</v>
+      <c r="B23" s="116" t="s">
+        <v>693</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="D23" s="110" t="s">
-        <v>531</v>
+        <v>694</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="109" t="s">
-        <v>609</v>
+      <c r="B24" s="116" t="s">
+        <v>695</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>610</v>
-      </c>
-      <c r="D24" s="107" t="s">
-        <v>554</v>
+        <v>696</v>
+      </c>
+      <c r="D24" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="109" t="s">
-        <v>611</v>
+      <c r="B25" s="116" t="s">
+        <v>697</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="D25" s="107" t="s">
-        <v>554</v>
+        <v>698</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="109" t="s">
-        <v>613</v>
+      <c r="B26" s="116" t="s">
+        <v>699</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="D26" s="106" t="s">
-        <v>543</v>
+        <v>700</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="109" t="s">
-        <v>615</v>
+      <c r="B27" s="116" t="s">
+        <v>701</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>616</v>
-      </c>
-      <c r="D27" s="106" t="s">
-        <v>543</v>
+        <v>702</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="109" t="s">
-        <v>617</v>
+      <c r="B28" s="116" t="s">
+        <v>703</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>618</v>
-      </c>
-      <c r="D28" s="110" t="s">
-        <v>531</v>
+        <v>704</v>
+      </c>
+      <c r="D28" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="109" t="s">
-        <v>619</v>
+      <c r="B29" s="116" t="s">
+        <v>705</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>620</v>
-      </c>
-      <c r="D29" s="106" t="s">
-        <v>543</v>
+        <v>706</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="109" t="s">
-        <v>621</v>
+      <c r="B30" s="116" t="s">
+        <v>707</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>622</v>
-      </c>
-      <c r="D30" s="107" t="s">
-        <v>554</v>
+        <v>708</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="109" t="s">
-        <v>623</v>
+      <c r="B31" s="116" t="s">
+        <v>709</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>624</v>
-      </c>
-      <c r="D31" s="110" t="s">
-        <v>531</v>
+        <v>710</v>
+      </c>
+      <c r="D31" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="109" t="s">
-        <v>625</v>
+      <c r="B32" s="116" t="s">
+        <v>711</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>626</v>
-      </c>
-      <c r="D32" s="107" t="s">
-        <v>554</v>
+        <v>712</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="109" t="s">
-        <v>627</v>
+      <c r="B33" s="116" t="s">
+        <v>713</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>628</v>
-      </c>
-      <c r="D33" s="107" t="s">
-        <v>554</v>
+        <v>714</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="109" t="s">
-        <v>629</v>
+      <c r="B34" s="116" t="s">
+        <v>715</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>630</v>
-      </c>
-      <c r="D34" s="107" t="s">
-        <v>554</v>
+        <v>716</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="109" t="s">
-        <v>631</v>
+      <c r="B35" s="116" t="s">
+        <v>717</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>632</v>
-      </c>
-      <c r="D35" s="110" t="s">
-        <v>531</v>
+        <v>718</v>
+      </c>
+      <c r="D35" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="109" t="s">
-        <v>633</v>
+      <c r="B36" s="116" t="s">
+        <v>719</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="D36" s="106" t="s">
-        <v>543</v>
+        <v>720</v>
+      </c>
+      <c r="D36" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -8554,1132 +9416,1132 @@
   <sheetData>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>635</v>
+        <v>721</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="108" t="s">
-        <v>636</v>
+      <c r="B3" s="115" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>637</v>
+        <v>723</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>526</v>
+        <v>625</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>639</v>
+        <v>725</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>640</v>
+        <v>726</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>641</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="111" t="s">
-        <v>642</v>
-      </c>
-      <c r="C6" s="106" t="s">
-        <v>543</v>
+      <c r="B6" s="117" t="s">
+        <v>728</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>644</v>
+        <v>730</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>645</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="111" t="s">
-        <v>646</v>
-      </c>
-      <c r="C7" s="106" t="s">
-        <v>543</v>
+      <c r="B7" s="117" t="s">
+        <v>732</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>647</v>
+        <v>733</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>648</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="111" t="s">
-        <v>649</v>
-      </c>
-      <c r="C8" s="106" t="s">
-        <v>543</v>
+      <c r="B8" s="117" t="s">
+        <v>735</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>650</v>
+        <v>736</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>651</v>
+        <v>737</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="111" t="s">
+      <c r="B9" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="106" t="s">
-        <v>543</v>
+      <c r="C9" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>652</v>
+        <v>738</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>653</v>
+        <v>739</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="111" t="s">
-        <v>654</v>
-      </c>
-      <c r="C10" s="106" t="s">
-        <v>543</v>
+      <c r="B10" s="117" t="s">
+        <v>740</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>655</v>
+        <v>741</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>656</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="111" t="s">
-        <v>657</v>
-      </c>
-      <c r="C11" s="106" t="s">
-        <v>543</v>
+      <c r="B11" s="117" t="s">
+        <v>743</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>658</v>
+        <v>744</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>659</v>
+        <v>745</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="111" t="s">
-        <v>660</v>
-      </c>
-      <c r="C12" s="106" t="s">
-        <v>543</v>
+      <c r="B12" s="117" t="s">
+        <v>746</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>661</v>
+        <v>747</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>662</v>
+        <v>748</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>663</v>
+        <v>749</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="111" t="s">
-        <v>664</v>
-      </c>
-      <c r="C13" s="106" t="s">
-        <v>543</v>
+      <c r="B13" s="117" t="s">
+        <v>750</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>661</v>
+        <v>747</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>665</v>
+        <v>751</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>666</v>
+        <v>752</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="111" t="s">
-        <v>667</v>
-      </c>
-      <c r="C14" s="106" t="s">
-        <v>543</v>
+      <c r="B14" s="117" t="s">
+        <v>753</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>661</v>
+        <v>747</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>668</v>
+        <v>754</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>669</v>
+        <v>755</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="111" t="s">
-        <v>670</v>
-      </c>
-      <c r="C15" s="106" t="s">
-        <v>543</v>
+      <c r="B15" s="117" t="s">
+        <v>756</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>661</v>
+        <v>747</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>671</v>
+        <v>757</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>672</v>
+        <v>758</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="111" t="s">
-        <v>673</v>
-      </c>
-      <c r="C16" s="106" t="s">
-        <v>543</v>
+      <c r="B16" s="117" t="s">
+        <v>759</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>661</v>
+        <v>747</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>674</v>
+        <v>760</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>675</v>
+        <v>761</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="111" t="s">
-        <v>676</v>
-      </c>
-      <c r="C17" s="106" t="s">
-        <v>543</v>
+      <c r="B17" s="117" t="s">
+        <v>762</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>678</v>
+        <v>764</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>679</v>
+        <v>765</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="111" t="s">
-        <v>680</v>
-      </c>
-      <c r="C18" s="106" t="s">
-        <v>543</v>
+      <c r="B18" s="117" t="s">
+        <v>766</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>681</v>
+        <v>767</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>682</v>
+        <v>768</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="111" t="s">
-        <v>683</v>
-      </c>
-      <c r="C19" s="106" t="s">
-        <v>543</v>
+      <c r="B19" s="117" t="s">
+        <v>769</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>684</v>
+        <v>770</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>685</v>
+        <v>771</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="111" t="s">
-        <v>686</v>
-      </c>
-      <c r="C20" s="106" t="s">
-        <v>543</v>
+      <c r="B20" s="117" t="s">
+        <v>772</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>687</v>
+        <v>773</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>688</v>
+        <v>774</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="111" t="s">
-        <v>689</v>
-      </c>
-      <c r="C21" s="106" t="s">
-        <v>543</v>
+      <c r="B21" s="117" t="s">
+        <v>775</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>690</v>
+        <v>776</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>691</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="111" t="s">
-        <v>692</v>
-      </c>
-      <c r="C22" s="106" t="s">
-        <v>543</v>
+      <c r="B22" s="117" t="s">
+        <v>778</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>693</v>
+        <v>779</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>694</v>
+        <v>780</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="111" t="s">
-        <v>695</v>
-      </c>
-      <c r="C23" s="106" t="s">
-        <v>543</v>
+      <c r="B23" s="117" t="s">
+        <v>781</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>697</v>
+        <v>783</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>698</v>
+        <v>784</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="111" t="s">
-        <v>699</v>
-      </c>
-      <c r="C24" s="107" t="s">
-        <v>554</v>
+      <c r="B24" s="117" t="s">
+        <v>785</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>700</v>
+        <v>786</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>645</v>
+        <v>731</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="111" t="s">
-        <v>701</v>
-      </c>
-      <c r="C25" s="107" t="s">
-        <v>554</v>
+      <c r="B25" s="117" t="s">
+        <v>787</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>702</v>
+        <v>788</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>703</v>
+        <v>789</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="111" t="s">
-        <v>704</v>
-      </c>
-      <c r="C26" s="107" t="s">
-        <v>554</v>
+      <c r="B26" s="117" t="s">
+        <v>790</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>705</v>
+        <v>791</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>706</v>
+        <v>792</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="111" t="s">
-        <v>707</v>
-      </c>
-      <c r="C27" s="107" t="s">
-        <v>554</v>
+      <c r="B27" s="117" t="s">
+        <v>793</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>650</v>
+        <v>736</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>651</v>
+        <v>737</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="111" t="s">
-        <v>708</v>
-      </c>
-      <c r="C28" s="107" t="s">
-        <v>554</v>
+      <c r="B28" s="117" t="s">
+        <v>794</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>709</v>
+        <v>795</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>710</v>
+        <v>796</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="111" t="s">
-        <v>711</v>
-      </c>
-      <c r="C29" s="107" t="s">
-        <v>554</v>
+      <c r="B29" s="117" t="s">
+        <v>797</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>655</v>
+        <v>741</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>656</v>
+        <v>742</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="111" t="s">
-        <v>712</v>
-      </c>
-      <c r="C30" s="107" t="s">
-        <v>554</v>
+      <c r="B30" s="117" t="s">
+        <v>798</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>714</v>
+        <v>800</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>715</v>
+        <v>801</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="111" t="s">
-        <v>716</v>
-      </c>
-      <c r="C31" s="107" t="s">
-        <v>554</v>
+      <c r="B31" s="117" t="s">
+        <v>802</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>717</v>
+        <v>803</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>663</v>
+        <v>749</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="111" t="s">
-        <v>718</v>
-      </c>
-      <c r="C32" s="107" t="s">
-        <v>554</v>
+      <c r="B32" s="117" t="s">
+        <v>804</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>666</v>
+        <v>752</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="111" t="s">
-        <v>720</v>
-      </c>
-      <c r="C33" s="107" t="s">
-        <v>554</v>
+      <c r="B33" s="117" t="s">
+        <v>806</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>721</v>
+        <v>807</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>669</v>
+        <v>755</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="111" t="s">
-        <v>722</v>
-      </c>
-      <c r="C34" s="107" t="s">
-        <v>554</v>
+      <c r="B34" s="117" t="s">
+        <v>808</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>723</v>
+        <v>809</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>672</v>
+        <v>758</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="111" t="s">
-        <v>724</v>
-      </c>
-      <c r="C35" s="107" t="s">
-        <v>554</v>
+      <c r="B35" s="117" t="s">
+        <v>810</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>725</v>
+        <v>811</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>675</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="111" t="s">
-        <v>726</v>
-      </c>
-      <c r="C36" s="107" t="s">
-        <v>554</v>
+      <c r="B36" s="117" t="s">
+        <v>812</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>678</v>
+        <v>764</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>679</v>
+        <v>765</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="111" t="s">
-        <v>727</v>
-      </c>
-      <c r="C37" s="107" t="s">
-        <v>554</v>
+      <c r="B37" s="117" t="s">
+        <v>813</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>728</v>
+        <v>814</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>729</v>
+        <v>815</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>682</v>
+        <v>768</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="111" t="s">
-        <v>730</v>
-      </c>
-      <c r="C38" s="107" t="s">
-        <v>554</v>
+      <c r="B38" s="117" t="s">
+        <v>816</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>728</v>
+        <v>814</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>731</v>
+        <v>817</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>685</v>
+        <v>771</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="111" t="s">
-        <v>732</v>
-      </c>
-      <c r="C39" s="107" t="s">
-        <v>554</v>
+      <c r="B39" s="117" t="s">
+        <v>818</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>728</v>
+        <v>814</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>687</v>
+        <v>773</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>733</v>
+        <v>819</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="111" t="s">
-        <v>734</v>
-      </c>
-      <c r="C40" s="107" t="s">
-        <v>554</v>
+      <c r="B40" s="117" t="s">
+        <v>820</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>728</v>
+        <v>814</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>735</v>
+        <v>821</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>736</v>
+        <v>822</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="111" t="s">
-        <v>737</v>
-      </c>
-      <c r="C41" s="106" t="s">
-        <v>543</v>
+      <c r="B41" s="117" t="s">
+        <v>823</v>
+      </c>
+      <c r="C41" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>738</v>
+        <v>824</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>739</v>
+        <v>825</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>740</v>
+        <v>826</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="111" t="s">
-        <v>741</v>
-      </c>
-      <c r="C42" s="106" t="s">
-        <v>543</v>
+      <c r="B42" s="117" t="s">
+        <v>827</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>738</v>
+        <v>824</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>742</v>
+        <v>828</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>743</v>
+        <v>829</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="111" t="s">
-        <v>744</v>
-      </c>
-      <c r="C43" s="106" t="s">
-        <v>543</v>
+      <c r="B43" s="117" t="s">
+        <v>830</v>
+      </c>
+      <c r="C43" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>745</v>
+        <v>831</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>746</v>
+        <v>832</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>747</v>
+        <v>833</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="111" t="s">
-        <v>748</v>
-      </c>
-      <c r="C44" s="106" t="s">
-        <v>543</v>
+      <c r="B44" s="117" t="s">
+        <v>834</v>
+      </c>
+      <c r="C44" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>745</v>
+        <v>831</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>749</v>
+        <v>835</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>747</v>
+        <v>833</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="111" t="s">
-        <v>750</v>
-      </c>
-      <c r="C45" s="106" t="s">
-        <v>543</v>
+      <c r="B45" s="117" t="s">
+        <v>836</v>
+      </c>
+      <c r="C45" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>745</v>
+        <v>831</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>751</v>
+        <v>837</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>752</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="111" t="s">
-        <v>753</v>
-      </c>
-      <c r="C46" s="106" t="s">
-        <v>543</v>
+      <c r="B46" s="117" t="s">
+        <v>839</v>
+      </c>
+      <c r="C46" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>9</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>754</v>
+        <v>840</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>755</v>
+        <v>841</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>756</v>
+        <v>842</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="111" t="s">
-        <v>757</v>
-      </c>
-      <c r="C47" s="107" t="s">
-        <v>554</v>
+      <c r="B47" s="117" t="s">
+        <v>843</v>
+      </c>
+      <c r="C47" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>758</v>
+        <v>844</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>759</v>
+        <v>845</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>760</v>
+        <v>846</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="111" t="s">
-        <v>761</v>
-      </c>
-      <c r="C48" s="107" t="s">
-        <v>554</v>
+      <c r="B48" s="117" t="s">
+        <v>847</v>
+      </c>
+      <c r="C48" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>758</v>
+        <v>844</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>762</v>
+        <v>848</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>743</v>
+        <v>829</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="111" t="s">
-        <v>763</v>
-      </c>
-      <c r="C49" s="107" t="s">
-        <v>554</v>
+      <c r="B49" s="117" t="s">
+        <v>849</v>
+      </c>
+      <c r="C49" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>758</v>
+        <v>844</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>764</v>
+        <v>850</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>752</v>
+        <v>838</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="111" t="s">
-        <v>765</v>
-      </c>
-      <c r="C50" s="107" t="s">
-        <v>554</v>
+      <c r="B50" s="117" t="s">
+        <v>851</v>
+      </c>
+      <c r="C50" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>11</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>766</v>
+        <v>852</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>767</v>
+        <v>853</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>768</v>
+        <v>854</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="111" t="s">
-        <v>769</v>
-      </c>
-      <c r="C51" s="107" t="s">
-        <v>554</v>
+      <c r="B51" s="117" t="s">
+        <v>855</v>
+      </c>
+      <c r="C51" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>770</v>
+        <v>856</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>771</v>
+        <v>857</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>768</v>
+        <v>854</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="111" t="s">
-        <v>772</v>
-      </c>
-      <c r="C52" s="110" t="s">
-        <v>531</v>
+      <c r="B52" s="117" t="s">
+        <v>858</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>199</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>770</v>
+        <v>856</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>773</v>
+        <v>859</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>774</v>
+        <v>860</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="111" t="s">
-        <v>775</v>
-      </c>
-      <c r="C53" s="110" t="s">
-        <v>531</v>
+      <c r="B53" s="117" t="s">
+        <v>861</v>
+      </c>
+      <c r="C53" s="56" t="s">
+        <v>199</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>770</v>
+        <v>856</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>776</v>
+        <v>862</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>777</v>
+        <v>863</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="111" t="s">
-        <v>778</v>
-      </c>
-      <c r="C54" s="110" t="s">
-        <v>531</v>
+      <c r="B54" s="117" t="s">
+        <v>864</v>
+      </c>
+      <c r="C54" s="56" t="s">
+        <v>199</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>13</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>779</v>
+        <v>865</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>780</v>
+        <v>866</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>781</v>
+        <v>867</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="111" t="s">
-        <v>782</v>
-      </c>
-      <c r="C55" s="106" t="s">
-        <v>543</v>
+      <c r="B55" s="117" t="s">
+        <v>868</v>
+      </c>
+      <c r="C55" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>13</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>779</v>
+        <v>865</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>783</v>
+        <v>869</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>784</v>
+        <v>870</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="111" t="s">
-        <v>785</v>
-      </c>
-      <c r="C56" s="106" t="s">
-        <v>543</v>
+      <c r="B56" s="117" t="s">
+        <v>871</v>
+      </c>
+      <c r="C56" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>14</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>786</v>
+        <v>872</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>787</v>
+        <v>873</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>788</v>
+        <v>874</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="111" t="s">
-        <v>789</v>
-      </c>
-      <c r="C57" s="106" t="s">
-        <v>543</v>
+      <c r="B57" s="117" t="s">
+        <v>875</v>
+      </c>
+      <c r="C57" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>790</v>
+        <v>876</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>791</v>
+        <v>877</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>792</v>
+        <v>878</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="111" t="s">
-        <v>793</v>
-      </c>
-      <c r="C58" s="106" t="s">
-        <v>543</v>
+      <c r="B58" s="117" t="s">
+        <v>879</v>
+      </c>
+      <c r="C58" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>790</v>
+        <v>876</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>794</v>
+        <v>880</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>795</v>
+        <v>881</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="111" t="s">
-        <v>796</v>
-      </c>
-      <c r="C59" s="107" t="s">
-        <v>554</v>
+      <c r="B59" s="117" t="s">
+        <v>882</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>790</v>
+        <v>876</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>797</v>
+        <v>883</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>792</v>
+        <v>878</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="111" t="s">
-        <v>798</v>
-      </c>
-      <c r="C60" s="107" t="s">
-        <v>554</v>
+      <c r="B60" s="117" t="s">
+        <v>884</v>
+      </c>
+      <c r="C60" s="58" t="s">
+        <v>210</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>790</v>
+        <v>876</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>799</v>
+        <v>885</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>795</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
